--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124715043</v>
+        <v>124715943</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454203</v>
+        <v>454281</v>
       </c>
       <c r="R2" t="n">
-        <v>6991872</v>
+        <v>6991629</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124716073</v>
+        <v>124715903</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,30 +799,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454289</v>
+        <v>454272</v>
       </c>
       <c r="R3" t="n">
-        <v>6991650</v>
+        <v>6991636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124712828</v>
+        <v>124716366</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -924,14 +940,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454150</v>
+        <v>454349</v>
       </c>
       <c r="R4" t="n">
-        <v>6991620</v>
+        <v>6991623</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124716063</v>
+        <v>124714299</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454289</v>
+        <v>454102</v>
       </c>
       <c r="R5" t="n">
-        <v>6991647</v>
+        <v>6991834</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,11 +1087,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124716113</v>
+        <v>124713664</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,39 +1129,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454311</v>
+        <v>454129</v>
       </c>
       <c r="R6" t="n">
-        <v>6991632</v>
+        <v>6991741</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,11 +1189,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124715915</v>
+        <v>124712512</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1260,14 +1256,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454272</v>
+        <v>454093</v>
       </c>
       <c r="R7" t="n">
-        <v>6991637</v>
+        <v>6991632</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124714775</v>
+        <v>124716073</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,38 +1339,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454161</v>
+        <v>454289</v>
       </c>
       <c r="R8" t="n">
-        <v>6991910</v>
+        <v>6991650</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124714299</v>
+        <v>124716123</v>
       </c>
       <c r="B9" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,34 +1449,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454102</v>
+        <v>454310</v>
       </c>
       <c r="R9" t="n">
-        <v>6991834</v>
+        <v>6991630</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,6 +1514,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124711120</v>
+        <v>124713606</v>
       </c>
       <c r="B10" t="n">
-        <v>78889</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,21 +1561,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1575,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454041</v>
+        <v>454129</v>
       </c>
       <c r="R10" t="n">
-        <v>6991635</v>
+        <v>6991741</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124716317</v>
+        <v>124714580</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>74892</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,43 +1659,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454349</v>
+        <v>454124</v>
       </c>
       <c r="R11" t="n">
-        <v>6991623</v>
+        <v>6991906</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,11 +1723,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,10 +1749,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124716123</v>
+        <v>124714775</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,39 +1765,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454310</v>
+        <v>454161</v>
       </c>
       <c r="R12" t="n">
-        <v>6991630</v>
+        <v>6991910</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,11 +1825,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,7 +1851,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124712512</v>
+        <v>124712610</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1906,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454093</v>
+        <v>454099</v>
       </c>
       <c r="R13" t="n">
-        <v>6991632</v>
+        <v>6991631</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1973,7 +1963,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124712610</v>
+        <v>124716063</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2014,14 +2004,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454099</v>
+        <v>454289</v>
       </c>
       <c r="R14" t="n">
-        <v>6991631</v>
+        <v>6991647</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,10 +2075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124714230</v>
+        <v>124712828</v>
       </c>
       <c r="B15" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,34 +2091,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454102</v>
+        <v>454150</v>
       </c>
       <c r="R15" t="n">
-        <v>6991834</v>
+        <v>6991620</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,6 +2156,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124713664</v>
+        <v>124714230</v>
       </c>
       <c r="B16" t="n">
-        <v>79892</v>
+        <v>91299</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,21 +2203,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454129</v>
+        <v>454102</v>
       </c>
       <c r="R16" t="n">
-        <v>6991741</v>
+        <v>6991834</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124713188</v>
+        <v>124712709</v>
       </c>
       <c r="B17" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,21 +2305,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454120</v>
+        <v>454108</v>
       </c>
       <c r="R17" t="n">
-        <v>6991707</v>
+        <v>6991616</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124712709</v>
+        <v>124711120</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>78889</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454108</v>
+        <v>454041</v>
       </c>
       <c r="R18" t="n">
-        <v>6991616</v>
+        <v>6991635</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124712085</v>
+        <v>124713829</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,39 +2509,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454054</v>
+        <v>454078</v>
       </c>
       <c r="R19" t="n">
-        <v>6991662</v>
+        <v>6991761</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,11 +2569,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124712037</v>
+        <v>124715915</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,34 +2611,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454053</v>
+        <v>454272</v>
       </c>
       <c r="R20" t="n">
-        <v>6991664</v>
+        <v>6991637</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,6 +2676,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2707,10 +2707,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124715943</v>
+        <v>124712037</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2723,39 +2723,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454281</v>
+        <v>454053</v>
       </c>
       <c r="R21" t="n">
-        <v>6991629</v>
+        <v>6991664</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,11 +2783,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2819,10 +2809,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124715903</v>
+        <v>124715043</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2835,39 +2825,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454272</v>
+        <v>454203</v>
       </c>
       <c r="R22" t="n">
-        <v>6991636</v>
+        <v>6991872</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,11 +2885,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2931,10 +2911,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124713617</v>
+        <v>124716057</v>
       </c>
       <c r="B23" t="n">
-        <v>79851</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2943,38 +2923,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454129</v>
+        <v>454290</v>
       </c>
       <c r="R23" t="n">
-        <v>6991741</v>
+        <v>6991649</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,6 +2992,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3033,10 +3023,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124713606</v>
+        <v>124712085</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3049,34 +3039,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454129</v>
+        <v>454054</v>
       </c>
       <c r="R24" t="n">
-        <v>6991741</v>
+        <v>6991662</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,6 +3104,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3135,10 +3135,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124713829</v>
+        <v>124714283</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3151,21 +3151,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454078</v>
+        <v>454102</v>
       </c>
       <c r="R25" t="n">
-        <v>6991761</v>
+        <v>6991834</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3349,10 +3349,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124714283</v>
+        <v>124716113</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3365,34 +3365,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454102</v>
+        <v>454311</v>
       </c>
       <c r="R27" t="n">
-        <v>6991834</v>
+        <v>6991632</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,6 +3430,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3451,10 +3461,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124716057</v>
+        <v>124713617</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>79851</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3463,43 +3473,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454290</v>
+        <v>454129</v>
       </c>
       <c r="R28" t="n">
-        <v>6991649</v>
+        <v>6991741</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,11 +3537,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3563,10 +3563,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124714580</v>
+        <v>124713188</v>
       </c>
       <c r="B29" t="n">
-        <v>74892</v>
+        <v>82597</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3575,25 +3575,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>492</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3603,10 +3603,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454124</v>
+        <v>454120</v>
       </c>
       <c r="R29" t="n">
-        <v>6991906</v>
+        <v>6991707</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3662,6 +3662,2854 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>124753602</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Häggsåsen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>454105</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6991740</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>124756697</v>
+      </c>
+      <c r="B31" t="n">
+        <v>74892</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>492</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Smalskaftslav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tjärnflon Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>454177</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6991911</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>124756706</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tjärnflon Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>454071</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6991672</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>124753598</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Häggsåsen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>454169</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6991914</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>124753590</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Häggsåsen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>454096</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6991720</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Bohål 5m upp i död gran</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>124753601</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Häggsåsen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>454103</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6991735</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124756701</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Tjärnflon Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>454115</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6991653</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>124753573</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Häggsåsen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>454135</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6991889</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>124753589</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91700</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Häggsåsen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>454148</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6991844</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>124756693</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Tjärnflon Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>454196</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6991703</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124753574</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Häggsåsen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>454086</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6991732</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>124756691</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Tjärnflon Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>454339</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6991639</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Min antal</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>124756702</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Tjärnflon Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>454100</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6991668</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>124753596</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Häggsåsen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>454245</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6991630</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>124756700</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Tjärnflon Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>454086</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6991750</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>124753600</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Häggsåsen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>454147</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6991908</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>124753597</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Häggsåsen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>454208</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6991866</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>124756692</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Tjärnflon Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>454256</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6991683</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>124753594</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Häggsåsen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>454351</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6991627</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>124753593</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Häggsåsen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>454406</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6991545</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>124756709</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Tjärnflon Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>454040</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6991636</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>124753636</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Häggsåsen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>454089</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6991655</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>124753603</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91705</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>67</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Häggsåsen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>454234</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6991643</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>124753572</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Häggsåsen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>454156</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6991902</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>124756698</v>
+      </c>
+      <c r="B54" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Tjärnflon Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>454144</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6991886</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>124756703</v>
+      </c>
+      <c r="B55" t="n">
+        <v>77743</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Tjärnflon Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>454100</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6991668</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124715903</v>
+        <v>124713617</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>79851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454272</v>
+        <v>454129</v>
       </c>
       <c r="R3" t="n">
-        <v>6991636</v>
+        <v>6991741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124716366</v>
+        <v>124714299</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454349</v>
+        <v>454102</v>
       </c>
       <c r="R4" t="n">
-        <v>6991623</v>
+        <v>6991834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124714299</v>
+        <v>124713188</v>
       </c>
       <c r="B5" t="n">
         <v>82597</v>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454102</v>
+        <v>454120</v>
       </c>
       <c r="R5" t="n">
-        <v>6991834</v>
+        <v>6991707</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124713664</v>
+        <v>124714894</v>
       </c>
       <c r="B6" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,34 +1109,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454129</v>
+        <v>454168</v>
       </c>
       <c r="R6" t="n">
-        <v>6991741</v>
+        <v>6991883</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124712512</v>
+        <v>124716366</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1251,19 +1241,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454093</v>
+        <v>454349</v>
       </c>
       <c r="R7" t="n">
-        <v>6991632</v>
+        <v>6991623</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124716073</v>
+        <v>124712610</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,42 +1329,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454289</v>
+        <v>454099</v>
       </c>
       <c r="R8" t="n">
-        <v>6991650</v>
+        <v>6991631</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,6 +1398,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124716123</v>
+        <v>124712828</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1469,19 +1465,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454310</v>
+        <v>454150</v>
       </c>
       <c r="R9" t="n">
-        <v>6991630</v>
+        <v>6991620</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124713606</v>
+        <v>124714230</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1561,21 +1557,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454129</v>
+        <v>454102</v>
       </c>
       <c r="R10" t="n">
-        <v>6991741</v>
+        <v>6991834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124714580</v>
+        <v>124716113</v>
       </c>
       <c r="B11" t="n">
-        <v>74892</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,38 +1655,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454124</v>
+        <v>454311</v>
       </c>
       <c r="R11" t="n">
-        <v>6991906</v>
+        <v>6991632</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,6 +1724,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124714775</v>
+        <v>124712037</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,21 +1771,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1789,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454161</v>
+        <v>454053</v>
       </c>
       <c r="R12" t="n">
-        <v>6991910</v>
+        <v>6991664</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124712610</v>
+        <v>124716063</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1892,14 +1898,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454099</v>
+        <v>454289</v>
       </c>
       <c r="R13" t="n">
-        <v>6991631</v>
+        <v>6991647</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124716063</v>
+        <v>124716073</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,31 +1981,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2011,7 +2016,7 @@
         <v>454289</v>
       </c>
       <c r="R14" t="n">
-        <v>6991647</v>
+        <v>6991650</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,11 +2049,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,7 +2075,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124712828</v>
+        <v>124716162</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2111,19 +2111,19 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454150</v>
+        <v>454310</v>
       </c>
       <c r="R15" t="n">
-        <v>6991620</v>
+        <v>6991630</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rinfhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124714230</v>
+        <v>124712085</v>
       </c>
       <c r="B16" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,34 +2203,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454102</v>
+        <v>454054</v>
       </c>
       <c r="R16" t="n">
-        <v>6991834</v>
+        <v>6991662</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,6 +2268,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2289,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124712709</v>
+        <v>124715915</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,34 +2315,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454108</v>
+        <v>454272</v>
       </c>
       <c r="R17" t="n">
-        <v>6991616</v>
+        <v>6991637</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,6 +2380,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2391,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124711120</v>
+        <v>124713606</v>
       </c>
       <c r="B18" t="n">
-        <v>78889</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,21 +2427,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454041</v>
+        <v>454129</v>
       </c>
       <c r="R18" t="n">
-        <v>6991635</v>
+        <v>6991741</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124713829</v>
+        <v>124715043</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,21 +2529,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2533,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454078</v>
+        <v>454203</v>
       </c>
       <c r="R19" t="n">
-        <v>6991761</v>
+        <v>6991872</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124715915</v>
+        <v>124713829</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2611,39 +2631,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454272</v>
+        <v>454078</v>
       </c>
       <c r="R20" t="n">
-        <v>6991637</v>
+        <v>6991761</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,11 +2691,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2707,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124712037</v>
+        <v>124713664</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>79892</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2723,21 +2733,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2747,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454053</v>
+        <v>454129</v>
       </c>
       <c r="R21" t="n">
-        <v>6991664</v>
+        <v>6991741</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2809,10 +2819,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124715043</v>
+        <v>124716057</v>
       </c>
       <c r="B22" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2825,34 +2835,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454203</v>
+        <v>454290</v>
       </c>
       <c r="R22" t="n">
-        <v>6991872</v>
+        <v>6991649</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,6 +2900,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2911,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124716057</v>
+        <v>124711120</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2927,39 +2947,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454290</v>
+        <v>454041</v>
       </c>
       <c r="R23" t="n">
-        <v>6991649</v>
+        <v>6991635</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,11 +3007,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3023,7 +3033,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124712085</v>
+        <v>124712512</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3068,10 +3078,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454054</v>
+        <v>454093</v>
       </c>
       <c r="R24" t="n">
-        <v>6991662</v>
+        <v>6991632</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3135,10 +3145,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124714283</v>
+        <v>124714775</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3151,21 +3161,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3175,10 +3185,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454102</v>
+        <v>454161</v>
       </c>
       <c r="R25" t="n">
-        <v>6991834</v>
+        <v>6991910</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,7 +3247,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124714894</v>
+        <v>124715903</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3278,14 +3288,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454168</v>
+        <v>454272</v>
       </c>
       <c r="R26" t="n">
-        <v>6991883</v>
+        <v>6991636</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3349,10 +3359,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124716113</v>
+        <v>124712709</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3365,39 +3375,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454311</v>
+        <v>454108</v>
       </c>
       <c r="R27" t="n">
-        <v>6991632</v>
+        <v>6991616</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,11 +3435,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3461,10 +3461,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124713617</v>
+        <v>124714580</v>
       </c>
       <c r="B28" t="n">
-        <v>79851</v>
+        <v>74892</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3473,25 +3473,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229497</v>
+        <v>492</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454129</v>
+        <v>454124</v>
       </c>
       <c r="R28" t="n">
-        <v>6991741</v>
+        <v>6991906</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3563,10 +3563,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124713188</v>
+        <v>124714283</v>
       </c>
       <c r="B29" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3579,21 +3579,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3603,10 +3603,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454120</v>
+        <v>454102</v>
       </c>
       <c r="R29" t="n">
-        <v>6991707</v>
+        <v>6991834</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3665,7 +3665,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124753602</v>
+        <v>124753601</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454105</v>
+        <v>454103</v>
       </c>
       <c r="R30" t="n">
-        <v>6991740</v>
+        <v>6991735</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124756697</v>
+        <v>124753596</v>
       </c>
       <c r="B31" t="n">
-        <v>74892</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3784,38 +3784,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454177</v>
+        <v>454245</v>
       </c>
       <c r="R31" t="n">
-        <v>6991911</v>
+        <v>6991630</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3845,19 +3845,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:55</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3868,41 +3863,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124756706</v>
+        <v>124753602</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3915,34 +3895,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454071</v>
+        <v>454105</v>
       </c>
       <c r="R32" t="n">
-        <v>6991672</v>
+        <v>6991740</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3972,19 +3952,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>17:00</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3999,22 +3974,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124753598</v>
+        <v>124756700</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4027,34 +4002,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454169</v>
+        <v>454086</v>
       </c>
       <c r="R33" t="n">
-        <v>6991914</v>
+        <v>6991750</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4084,14 +4059,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4106,22 +4086,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124753590</v>
+        <v>124756701</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4134,42 +4114,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454096</v>
+        <v>454115</v>
       </c>
       <c r="R34" t="n">
-        <v>6991720</v>
+        <v>6991653</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4199,14 +4171,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Bohål 5m upp i död gran</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4221,22 +4198,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124753601</v>
+        <v>124753589</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>91700</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4245,25 +4222,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4273,10 +4250,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454103</v>
+        <v>454148</v>
       </c>
       <c r="R35" t="n">
-        <v>6991735</v>
+        <v>6991844</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4309,11 +4286,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4340,10 +4312,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124756701</v>
+        <v>124753590</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4356,34 +4328,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454115</v>
+        <v>454096</v>
       </c>
       <c r="R36" t="n">
-        <v>6991653</v>
+        <v>6991720</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4413,19 +4393,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>17:09</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>17:09</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Bohål 5m upp i död gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4440,19 +4415,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124753573</v>
+        <v>124756709</v>
       </c>
       <c r="B37" t="n">
         <v>91012</v>
@@ -4488,14 +4463,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454135</v>
+        <v>454040</v>
       </c>
       <c r="R37" t="n">
-        <v>6991889</v>
+        <v>6991636</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4525,9 +4500,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4542,22 +4527,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124753589</v>
+        <v>124756698</v>
       </c>
       <c r="B38" t="n">
-        <v>91700</v>
+        <v>82597</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4566,38 +4551,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454148</v>
+        <v>454144</v>
       </c>
       <c r="R38" t="n">
-        <v>6991844</v>
+        <v>6991886</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4627,9 +4612,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4644,22 +4639,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124756693</v>
+        <v>124753593</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4672,34 +4667,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454196</v>
+        <v>454406</v>
       </c>
       <c r="R39" t="n">
-        <v>6991703</v>
+        <v>6991545</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4729,19 +4724,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>18:12</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>18:12</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4756,22 +4746,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124753574</v>
+        <v>124753598</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4784,21 +4774,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4808,10 +4798,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454086</v>
+        <v>454169</v>
       </c>
       <c r="R40" t="n">
-        <v>6991732</v>
+        <v>6991914</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4844,6 +4834,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4870,10 +4865,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124756691</v>
+        <v>124756692</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4882,50 +4877,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454339</v>
+        <v>454256</v>
       </c>
       <c r="R41" t="n">
-        <v>6991639</v>
+        <v>6991683</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4957,7 +4940,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4967,12 +4950,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Min antal</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4981,7 +4959,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5000,10 +4977,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124756702</v>
+        <v>124756691</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5012,38 +4989,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454100</v>
+        <v>454339</v>
       </c>
       <c r="R42" t="n">
-        <v>6991668</v>
+        <v>6991639</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5075,7 +5064,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5085,7 +5074,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Min antal</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5094,6 +5088,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5112,10 +5107,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124753596</v>
+        <v>124753603</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5124,25 +5119,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5152,10 +5147,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454245</v>
+        <v>454234</v>
       </c>
       <c r="R43" t="n">
-        <v>6991630</v>
+        <v>6991643</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5188,11 +5183,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5219,10 +5209,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124756700</v>
+        <v>124753597</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5235,34 +5225,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454086</v>
+        <v>454208</v>
       </c>
       <c r="R44" t="n">
-        <v>6991750</v>
+        <v>6991866</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5292,19 +5282,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>17:30</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5319,22 +5304,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124753600</v>
+        <v>124753574</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5347,21 +5332,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5371,10 +5356,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454147</v>
+        <v>454086</v>
       </c>
       <c r="R45" t="n">
-        <v>6991908</v>
+        <v>6991732</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5407,11 +5392,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5438,10 +5418,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124753597</v>
+        <v>124756706</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5454,34 +5434,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454208</v>
+        <v>454071</v>
       </c>
       <c r="R46" t="n">
-        <v>6991866</v>
+        <v>6991672</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5511,14 +5491,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5533,22 +5518,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124756692</v>
+        <v>124753636</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5561,34 +5546,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454256</v>
+        <v>454089</v>
       </c>
       <c r="R47" t="n">
-        <v>6991683</v>
+        <v>6991655</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5618,19 +5603,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>18:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5645,22 +5620,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124753594</v>
+        <v>124756703</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>77743</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5673,34 +5648,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454351</v>
+        <v>454100</v>
       </c>
       <c r="R48" t="n">
-        <v>6991627</v>
+        <v>6991668</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5730,14 +5705,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5752,22 +5732,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124753593</v>
+        <v>124756693</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5780,34 +5760,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454406</v>
+        <v>454196</v>
       </c>
       <c r="R49" t="n">
-        <v>6991545</v>
+        <v>6991703</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5837,14 +5817,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5859,19 +5844,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124756709</v>
+        <v>124753572</v>
       </c>
       <c r="B50" t="n">
         <v>91012</v>
@@ -5907,14 +5892,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454040</v>
+        <v>454156</v>
       </c>
       <c r="R50" t="n">
-        <v>6991636</v>
+        <v>6991902</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5944,19 +5929,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:56</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5971,22 +5946,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124753636</v>
+        <v>124756697</v>
       </c>
       <c r="B51" t="n">
-        <v>91030</v>
+        <v>74892</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5995,38 +5970,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454089</v>
+        <v>454177</v>
       </c>
       <c r="R51" t="n">
-        <v>6991655</v>
+        <v>6991911</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6056,11 +6031,21 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6069,26 +6054,41 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124753603</v>
+        <v>124756702</v>
       </c>
       <c r="B52" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6097,38 +6097,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454234</v>
+        <v>454100</v>
       </c>
       <c r="R52" t="n">
-        <v>6991643</v>
+        <v>6991668</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6158,9 +6158,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6175,22 +6185,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124753572</v>
+        <v>124753594</v>
       </c>
       <c r="B53" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6203,21 +6213,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6227,10 +6237,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454156</v>
+        <v>454351</v>
       </c>
       <c r="R53" t="n">
-        <v>6991902</v>
+        <v>6991627</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6263,6 +6273,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6289,10 +6304,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124756698</v>
+        <v>124753573</v>
       </c>
       <c r="B54" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6305,34 +6320,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454144</v>
+        <v>454135</v>
       </c>
       <c r="R54" t="n">
-        <v>6991886</v>
+        <v>6991889</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6362,19 +6377,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6389,22 +6394,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124756703</v>
+        <v>124753600</v>
       </c>
       <c r="B55" t="n">
-        <v>77743</v>
+        <v>57513</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6417,34 +6422,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454100</v>
+        <v>454147</v>
       </c>
       <c r="R55" t="n">
-        <v>6991668</v>
+        <v>6991908</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6474,19 +6479,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>17:06</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6501,12 +6501,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124715943</v>
+        <v>124712828</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -711,19 +711,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454281</v>
+        <v>454150</v>
       </c>
       <c r="R2" t="n">
-        <v>6991629</v>
+        <v>6991620</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124713617</v>
+        <v>124714894</v>
       </c>
       <c r="B3" t="n">
-        <v>79851</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454129</v>
+        <v>454168</v>
       </c>
       <c r="R3" t="n">
-        <v>6991741</v>
+        <v>6991883</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124714299</v>
+        <v>124713617</v>
       </c>
       <c r="B4" t="n">
-        <v>82597</v>
+        <v>79851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454102</v>
+        <v>454129</v>
       </c>
       <c r="R4" t="n">
-        <v>6991834</v>
+        <v>6991741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124713188</v>
+        <v>124712610</v>
       </c>
       <c r="B5" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1017,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454120</v>
+        <v>454099</v>
       </c>
       <c r="R5" t="n">
-        <v>6991707</v>
+        <v>6991631</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1082,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124714894</v>
+        <v>124715915</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1129,19 +1149,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454168</v>
+        <v>454272</v>
       </c>
       <c r="R6" t="n">
-        <v>6991883</v>
+        <v>6991637</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124716366</v>
+        <v>124713606</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,39 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454349</v>
+        <v>454129</v>
       </c>
       <c r="R7" t="n">
-        <v>6991623</v>
+        <v>6991741</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1301,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124712610</v>
+        <v>124712085</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1362,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454099</v>
+        <v>454054</v>
       </c>
       <c r="R8" t="n">
-        <v>6991631</v>
+        <v>6991662</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124712828</v>
+        <v>124714283</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,39 +1455,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454150</v>
+        <v>454102</v>
       </c>
       <c r="R9" t="n">
-        <v>6991620</v>
+        <v>6991834</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,11 +1515,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124716113</v>
+        <v>124716162</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1679,7 +1679,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454311</v>
+        <v>454310</v>
       </c>
       <c r="R11" t="n">
-        <v>6991632</v>
+        <v>6991630</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rinfhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124712037</v>
+        <v>124714775</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,21 +1771,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454053</v>
+        <v>454161</v>
       </c>
       <c r="R12" t="n">
-        <v>6991664</v>
+        <v>6991910</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124716063</v>
+        <v>124711120</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,39 +1873,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454289</v>
+        <v>454041</v>
       </c>
       <c r="R13" t="n">
-        <v>6991647</v>
+        <v>6991635</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,11 +1933,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124716073</v>
+        <v>124715903</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1981,30 +1971,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2013,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454289</v>
+        <v>454272</v>
       </c>
       <c r="R14" t="n">
-        <v>6991650</v>
+        <v>6991636</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,6 +2040,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,7 +2071,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124716162</v>
+        <v>124716063</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2120,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454310</v>
+        <v>454289</v>
       </c>
       <c r="R15" t="n">
-        <v>6991630</v>
+        <v>6991647</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,7 +2156,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rinfhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124712085</v>
+        <v>124712037</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,39 +2199,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454054</v>
+        <v>454053</v>
       </c>
       <c r="R16" t="n">
-        <v>6991662</v>
+        <v>6991664</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,11 +2259,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2299,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124715915</v>
+        <v>124713664</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,39 +2301,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454272</v>
+        <v>454129</v>
       </c>
       <c r="R17" t="n">
-        <v>6991637</v>
+        <v>6991741</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,11 +2361,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2411,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124713606</v>
+        <v>124713188</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>82597</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2427,21 +2403,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2451,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454129</v>
+        <v>454120</v>
       </c>
       <c r="R18" t="n">
-        <v>6991741</v>
+        <v>6991707</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124715043</v>
+        <v>124714580</v>
       </c>
       <c r="B19" t="n">
-        <v>91299</v>
+        <v>74892</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,25 +2501,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>492</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454203</v>
+        <v>454124</v>
       </c>
       <c r="R19" t="n">
-        <v>6991872</v>
+        <v>6991906</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124713829</v>
+        <v>124715043</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,21 +2607,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2655,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454078</v>
+        <v>454203</v>
       </c>
       <c r="R20" t="n">
-        <v>6991761</v>
+        <v>6991872</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2717,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124713664</v>
+        <v>124716317</v>
       </c>
       <c r="B21" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2733,34 +2709,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454129</v>
+        <v>454349</v>
       </c>
       <c r="R21" t="n">
-        <v>6991741</v>
+        <v>6991623</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,6 +2774,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2819,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124716057</v>
+        <v>124716073</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,31 +2817,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2864,10 +2849,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454290</v>
+        <v>454289</v>
       </c>
       <c r="R22" t="n">
-        <v>6991649</v>
+        <v>6991650</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,11 +2885,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2931,10 +2911,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124711120</v>
+        <v>124712512</v>
       </c>
       <c r="B23" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2947,34 +2927,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454041</v>
+        <v>454093</v>
       </c>
       <c r="R23" t="n">
-        <v>6991635</v>
+        <v>6991632</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,6 +2992,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3033,10 +3023,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124712512</v>
+        <v>124714299</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3049,39 +3039,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454093</v>
+        <v>454102</v>
       </c>
       <c r="R24" t="n">
-        <v>6991632</v>
+        <v>6991834</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3114,11 +3099,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3145,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124714775</v>
+        <v>124712709</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3161,21 +3141,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3185,10 +3165,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454161</v>
+        <v>454108</v>
       </c>
       <c r="R25" t="n">
-        <v>6991910</v>
+        <v>6991616</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3247,7 +3227,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124715903</v>
+        <v>124716057</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3292,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454272</v>
+        <v>454290</v>
       </c>
       <c r="R26" t="n">
-        <v>6991636</v>
+        <v>6991649</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3359,10 +3339,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124712709</v>
+        <v>124716113</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3375,34 +3355,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454108</v>
+        <v>454311</v>
       </c>
       <c r="R27" t="n">
-        <v>6991616</v>
+        <v>6991632</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,6 +3420,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3461,10 +3451,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124714580</v>
+        <v>124715943</v>
       </c>
       <c r="B28" t="n">
-        <v>74892</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3473,38 +3463,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454124</v>
+        <v>454281</v>
       </c>
       <c r="R28" t="n">
-        <v>6991906</v>
+        <v>6991629</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,6 +3532,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3563,10 +3563,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124714283</v>
+        <v>124713829</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3579,21 +3579,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3603,10 +3603,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454102</v>
+        <v>454078</v>
       </c>
       <c r="R29" t="n">
-        <v>6991834</v>
+        <v>6991761</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3665,7 +3665,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124753601</v>
+        <v>124753598</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454103</v>
+        <v>454169</v>
       </c>
       <c r="R30" t="n">
-        <v>6991735</v>
+        <v>6991914</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3772,10 +3772,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124753596</v>
+        <v>124756698</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3788,34 +3788,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454245</v>
+        <v>454144</v>
       </c>
       <c r="R31" t="n">
-        <v>6991630</v>
+        <v>6991886</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3845,14 +3845,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3867,22 +3872,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124753602</v>
+        <v>124753636</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3895,21 +3900,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3919,10 +3924,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454105</v>
+        <v>454089</v>
       </c>
       <c r="R32" t="n">
-        <v>6991740</v>
+        <v>6991655</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,11 +3960,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3986,10 +3986,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124756700</v>
+        <v>124753590</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4002,34 +4002,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454086</v>
+        <v>454096</v>
       </c>
       <c r="R33" t="n">
-        <v>6991750</v>
+        <v>6991720</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4059,19 +4067,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>17:30</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Bohål 5m upp i död gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4086,22 +4089,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124756701</v>
+        <v>124753589</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>91700</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4110,38 +4113,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454115</v>
+        <v>454148</v>
       </c>
       <c r="R34" t="n">
-        <v>6991653</v>
+        <v>6991844</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4171,19 +4174,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>17:09</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>17:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4198,22 +4191,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124753589</v>
+        <v>124756697</v>
       </c>
       <c r="B35" t="n">
-        <v>91700</v>
+        <v>74892</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4222,38 +4215,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>492</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454148</v>
+        <v>454177</v>
       </c>
       <c r="R35" t="n">
-        <v>6991844</v>
+        <v>6991911</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,11 +4276,21 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4296,26 +4299,41 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124753590</v>
+        <v>124756709</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4328,42 +4346,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454096</v>
+        <v>454040</v>
       </c>
       <c r="R36" t="n">
-        <v>6991720</v>
+        <v>6991636</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4393,14 +4403,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Bohål 5m upp i död gran</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4415,22 +4430,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124756709</v>
+        <v>124753597</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4443,34 +4458,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454040</v>
+        <v>454208</v>
       </c>
       <c r="R37" t="n">
-        <v>6991636</v>
+        <v>6991866</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4500,19 +4515,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:56</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,22 +4537,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124756698</v>
+        <v>124753602</v>
       </c>
       <c r="B38" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4555,34 +4565,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454144</v>
+        <v>454105</v>
       </c>
       <c r="R38" t="n">
-        <v>6991886</v>
+        <v>6991740</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4612,19 +4622,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>17:48</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,22 +4644,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124753593</v>
+        <v>124753573</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4667,21 +4672,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4691,10 +4696,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454406</v>
+        <v>454135</v>
       </c>
       <c r="R39" t="n">
-        <v>6991545</v>
+        <v>6991889</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4727,11 +4732,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4758,10 +4758,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124753598</v>
+        <v>124756702</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4774,34 +4774,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454169</v>
+        <v>454100</v>
       </c>
       <c r="R40" t="n">
-        <v>6991914</v>
+        <v>6991668</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4831,14 +4831,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,22 +4858,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124756692</v>
+        <v>124753593</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4881,34 +4886,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454256</v>
+        <v>454406</v>
       </c>
       <c r="R41" t="n">
-        <v>6991683</v>
+        <v>6991545</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4938,19 +4943,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>18:19</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4965,22 +4965,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124756691</v>
+        <v>124753600</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4989,50 +4989,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454339</v>
+        <v>454147</v>
       </c>
       <c r="R42" t="n">
-        <v>6991639</v>
+        <v>6991908</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5062,24 +5050,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Min antal</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5088,29 +5066,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124753603</v>
+        <v>124756703</v>
       </c>
       <c r="B43" t="n">
-        <v>91705</v>
+        <v>77743</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5119,38 +5096,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>67</v>
+        <v>228579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454234</v>
+        <v>454100</v>
       </c>
       <c r="R43" t="n">
-        <v>6991643</v>
+        <v>6991668</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5180,9 +5157,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5197,22 +5184,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124753597</v>
+        <v>124756706</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5225,34 +5212,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454208</v>
+        <v>454071</v>
       </c>
       <c r="R44" t="n">
-        <v>6991866</v>
+        <v>6991672</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5282,14 +5269,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5304,22 +5296,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124753574</v>
+        <v>124753601</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5332,21 +5324,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5356,10 +5348,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454086</v>
+        <v>454103</v>
       </c>
       <c r="R45" t="n">
-        <v>6991732</v>
+        <v>6991735</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5392,6 +5384,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5418,10 +5415,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124756706</v>
+        <v>124756701</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5434,21 +5431,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5458,10 +5455,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454071</v>
+        <v>454115</v>
       </c>
       <c r="R46" t="n">
-        <v>6991672</v>
+        <v>6991653</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5493,7 +5490,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5503,7 +5500,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5530,10 +5527,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124753636</v>
+        <v>124753596</v>
       </c>
       <c r="B47" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5546,21 +5543,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5570,10 +5567,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454089</v>
+        <v>454245</v>
       </c>
       <c r="R47" t="n">
-        <v>6991655</v>
+        <v>6991630</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5606,6 +5603,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,10 +5634,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124756703</v>
+        <v>124753574</v>
       </c>
       <c r="B48" t="n">
-        <v>77743</v>
+        <v>91012</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5648,34 +5650,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454100</v>
+        <v>454086</v>
       </c>
       <c r="R48" t="n">
-        <v>6991668</v>
+        <v>6991732</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5705,19 +5707,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>17:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5732,22 +5724,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124756693</v>
+        <v>124753603</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>91705</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5756,38 +5748,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454196</v>
+        <v>454234</v>
       </c>
       <c r="R49" t="n">
-        <v>6991703</v>
+        <v>6991643</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5817,19 +5809,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>18:12</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>18:12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5844,22 +5826,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124753572</v>
+        <v>124756700</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5872,34 +5854,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454156</v>
+        <v>454086</v>
       </c>
       <c r="R50" t="n">
-        <v>6991902</v>
+        <v>6991750</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5929,9 +5911,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5946,22 +5938,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124756697</v>
+        <v>124753572</v>
       </c>
       <c r="B51" t="n">
-        <v>74892</v>
+        <v>91012</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5970,38 +5962,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454177</v>
+        <v>454156</v>
       </c>
       <c r="R51" t="n">
-        <v>6991911</v>
+        <v>6991902</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6031,21 +6023,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6054,41 +6036,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124756702</v>
+        <v>124756691</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6097,38 +6064,50 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454100</v>
+        <v>454339</v>
       </c>
       <c r="R52" t="n">
-        <v>6991668</v>
+        <v>6991639</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6160,7 +6139,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6170,7 +6149,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Min antal</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6179,6 +6163,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6197,10 +6182,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124753594</v>
+        <v>124756693</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6213,34 +6198,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454351</v>
+        <v>454196</v>
       </c>
       <c r="R53" t="n">
-        <v>6991627</v>
+        <v>6991703</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6270,14 +6255,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6292,22 +6282,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124753573</v>
+        <v>124756692</v>
       </c>
       <c r="B54" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6320,34 +6310,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454135</v>
+        <v>454256</v>
       </c>
       <c r="R54" t="n">
-        <v>6991889</v>
+        <v>6991683</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6377,9 +6367,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6394,19 +6394,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124753600</v>
+        <v>124753594</v>
       </c>
       <c r="B55" t="n">
         <v>57513</v>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454147</v>
+        <v>454351</v>
       </c>
       <c r="R55" t="n">
-        <v>6991908</v>
+        <v>6991627</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124711120</v>
+        <v>124715903</v>
       </c>
       <c r="B13" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,34 +1873,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454041</v>
+        <v>454272</v>
       </c>
       <c r="R13" t="n">
-        <v>6991635</v>
+        <v>6991636</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,6 +1938,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124715903</v>
+        <v>124711120</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,39 +1985,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454272</v>
+        <v>454041</v>
       </c>
       <c r="R14" t="n">
-        <v>6991636</v>
+        <v>6991635</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,11 +2045,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124712828</v>
+        <v>124711120</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454150</v>
+        <v>454041</v>
       </c>
       <c r="R2" t="n">
-        <v>6991620</v>
+        <v>6991635</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124714894</v>
+        <v>124714580</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>74892</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454168</v>
+        <v>454124</v>
       </c>
       <c r="R3" t="n">
-        <v>6991883</v>
+        <v>6991906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124713617</v>
+        <v>124715043</v>
       </c>
       <c r="B4" t="n">
-        <v>79851</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454129</v>
+        <v>454203</v>
       </c>
       <c r="R4" t="n">
-        <v>6991741</v>
+        <v>6991872</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124712610</v>
+        <v>124715943</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1042,14 +1022,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454099</v>
+        <v>454281</v>
       </c>
       <c r="R5" t="n">
-        <v>6991631</v>
+        <v>6991629</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124715915</v>
+        <v>124712610</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1154,14 +1134,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454272</v>
+        <v>454099</v>
       </c>
       <c r="R6" t="n">
-        <v>6991637</v>
+        <v>6991631</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124713606</v>
+        <v>124712828</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,34 +1221,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454129</v>
+        <v>454150</v>
       </c>
       <c r="R7" t="n">
-        <v>6991741</v>
+        <v>6991620</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124712085</v>
+        <v>124713617</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>79851</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,43 +1329,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454054</v>
+        <v>454129</v>
       </c>
       <c r="R8" t="n">
-        <v>6991662</v>
+        <v>6991741</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124714283</v>
+        <v>124713188</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>82597</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1455,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454102</v>
+        <v>454120</v>
       </c>
       <c r="R9" t="n">
-        <v>6991834</v>
+        <v>6991707</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124714230</v>
+        <v>124716366</v>
       </c>
       <c r="B10" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,34 +1537,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454102</v>
+        <v>454349</v>
       </c>
       <c r="R10" t="n">
-        <v>6991834</v>
+        <v>6991623</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124716162</v>
+        <v>124716073</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,31 +1645,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1688,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454310</v>
+        <v>454289</v>
       </c>
       <c r="R11" t="n">
-        <v>6991630</v>
+        <v>6991650</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,11 +1713,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rinfhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124714775</v>
+        <v>124715903</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,34 +1755,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454161</v>
+        <v>454272</v>
       </c>
       <c r="R12" t="n">
-        <v>6991910</v>
+        <v>6991636</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,6 +1820,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,7 +1851,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124715903</v>
+        <v>124714894</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1898,14 +1892,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454272</v>
+        <v>454168</v>
       </c>
       <c r="R13" t="n">
-        <v>6991636</v>
+        <v>6991883</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124711120</v>
+        <v>124715915</v>
       </c>
       <c r="B14" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1985,34 +1979,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454041</v>
+        <v>454272</v>
       </c>
       <c r="R14" t="n">
-        <v>6991635</v>
+        <v>6991637</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,6 +2044,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,7 +2075,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124716063</v>
+        <v>124716123</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2116,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454289</v>
+        <v>454310</v>
       </c>
       <c r="R15" t="n">
-        <v>6991647</v>
+        <v>6991630</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124712037</v>
+        <v>124713829</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,21 +2203,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454053</v>
+        <v>454078</v>
       </c>
       <c r="R16" t="n">
-        <v>6991664</v>
+        <v>6991761</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124713664</v>
+        <v>124714299</v>
       </c>
       <c r="B17" t="n">
-        <v>79892</v>
+        <v>82597</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,21 +2305,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454129</v>
+        <v>454102</v>
       </c>
       <c r="R17" t="n">
-        <v>6991741</v>
+        <v>6991834</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124713188</v>
+        <v>124713664</v>
       </c>
       <c r="B18" t="n">
-        <v>82597</v>
+        <v>79892</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,21 +2407,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2427,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454120</v>
+        <v>454129</v>
       </c>
       <c r="R18" t="n">
-        <v>6991707</v>
+        <v>6991741</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,10 +2493,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124714580</v>
+        <v>124712085</v>
       </c>
       <c r="B19" t="n">
-        <v>74892</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2501,38 +2505,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454124</v>
+        <v>454054</v>
       </c>
       <c r="R19" t="n">
-        <v>6991906</v>
+        <v>6991662</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,6 +2574,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,10 +2605,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124715043</v>
+        <v>124712512</v>
       </c>
       <c r="B20" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2607,34 +2621,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454203</v>
+        <v>454093</v>
       </c>
       <c r="R20" t="n">
-        <v>6991872</v>
+        <v>6991632</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,6 +2686,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124716317</v>
+        <v>124714230</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,39 +2733,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454349</v>
+        <v>454102</v>
       </c>
       <c r="R21" t="n">
-        <v>6991623</v>
+        <v>6991834</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,11 +2793,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,10 +2819,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124716073</v>
+        <v>124714775</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,42 +2831,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454289</v>
+        <v>454161</v>
       </c>
       <c r="R22" t="n">
-        <v>6991650</v>
+        <v>6991910</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2911,10 +2921,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124712512</v>
+        <v>124712709</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2927,39 +2937,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454093</v>
+        <v>454108</v>
       </c>
       <c r="R23" t="n">
-        <v>6991632</v>
+        <v>6991616</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,11 +2997,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3023,10 +3023,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124714299</v>
+        <v>124716057</v>
       </c>
       <c r="B24" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3039,34 +3039,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454102</v>
+        <v>454290</v>
       </c>
       <c r="R24" t="n">
-        <v>6991834</v>
+        <v>6991649</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,6 +3104,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3125,10 +3135,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124712709</v>
+        <v>124716063</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3141,34 +3151,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454108</v>
+        <v>454289</v>
       </c>
       <c r="R25" t="n">
-        <v>6991616</v>
+        <v>6991647</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,6 +3216,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3227,10 +3247,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124716057</v>
+        <v>124712037</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3243,39 +3263,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454290</v>
+        <v>454053</v>
       </c>
       <c r="R26" t="n">
-        <v>6991649</v>
+        <v>6991664</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,11 +3323,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3451,10 +3461,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124715943</v>
+        <v>124714283</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3467,39 +3477,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454281</v>
+        <v>454102</v>
       </c>
       <c r="R28" t="n">
-        <v>6991629</v>
+        <v>6991834</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,11 +3537,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3563,7 +3563,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124713829</v>
+        <v>124713606</v>
       </c>
       <c r="B29" t="n">
         <v>79891</v>
@@ -3603,10 +3603,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454078</v>
+        <v>454129</v>
       </c>
       <c r="R29" t="n">
-        <v>6991761</v>
+        <v>6991741</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124753598</v>
+        <v>124756701</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3681,34 +3681,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454169</v>
+        <v>454115</v>
       </c>
       <c r="R30" t="n">
-        <v>6991914</v>
+        <v>6991653</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3738,14 +3738,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3760,22 +3765,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124756698</v>
+        <v>124756693</v>
       </c>
       <c r="B31" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3788,21 +3793,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3812,10 +3817,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454144</v>
+        <v>454196</v>
       </c>
       <c r="R31" t="n">
-        <v>6991886</v>
+        <v>6991703</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3847,7 +3852,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3857,7 +3862,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3884,10 +3889,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124753636</v>
+        <v>124756706</v>
       </c>
       <c r="B32" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3900,34 +3905,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454089</v>
+        <v>454071</v>
       </c>
       <c r="R32" t="n">
-        <v>6991655</v>
+        <v>6991672</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3957,9 +3962,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3974,19 +3989,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124753590</v>
+        <v>124753594</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -4020,24 +4035,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454096</v>
+        <v>454351</v>
       </c>
       <c r="R33" t="n">
-        <v>6991720</v>
+        <v>6991627</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4074,7 +4081,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Bohål 5m upp i död gran</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4101,10 +4108,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124753589</v>
+        <v>124756703</v>
       </c>
       <c r="B34" t="n">
-        <v>91700</v>
+        <v>77743</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4113,38 +4120,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454148</v>
+        <v>454100</v>
       </c>
       <c r="R34" t="n">
-        <v>6991844</v>
+        <v>6991668</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4174,9 +4181,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4191,22 +4208,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124756697</v>
+        <v>124753601</v>
       </c>
       <c r="B35" t="n">
-        <v>74892</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4215,38 +4232,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454177</v>
+        <v>454103</v>
       </c>
       <c r="R35" t="n">
-        <v>6991911</v>
+        <v>6991735</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4276,19 +4293,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>17:55</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4299,41 +4311,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124756709</v>
+        <v>124753589</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>91700</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4342,38 +4339,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454040</v>
+        <v>454148</v>
       </c>
       <c r="R36" t="n">
-        <v>6991636</v>
+        <v>6991844</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4403,19 +4400,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:56</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4430,22 +4417,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124753597</v>
+        <v>124753572</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4458,21 +4445,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4482,10 +4469,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454208</v>
+        <v>454156</v>
       </c>
       <c r="R37" t="n">
-        <v>6991866</v>
+        <v>6991902</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4518,11 +4505,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4549,7 +4531,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124753602</v>
+        <v>124753596</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4589,10 +4571,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454105</v>
+        <v>454245</v>
       </c>
       <c r="R38" t="n">
-        <v>6991740</v>
+        <v>6991630</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4629,7 +4611,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4656,10 +4638,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124753573</v>
+        <v>124753600</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4672,21 +4654,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4696,10 +4678,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454135</v>
+        <v>454147</v>
       </c>
       <c r="R39" t="n">
-        <v>6991889</v>
+        <v>6991908</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4732,6 +4714,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4758,10 +4745,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124756702</v>
+        <v>124753603</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>91705</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4770,38 +4757,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454100</v>
+        <v>454234</v>
       </c>
       <c r="R40" t="n">
-        <v>6991668</v>
+        <v>6991643</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4831,19 +4818,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>17:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4858,22 +4835,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124753593</v>
+        <v>124753573</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4886,21 +4863,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4910,10 +4887,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454406</v>
+        <v>454135</v>
       </c>
       <c r="R41" t="n">
-        <v>6991545</v>
+        <v>6991889</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4946,11 +4923,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4977,10 +4949,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124753600</v>
+        <v>124753574</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4993,21 +4965,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5017,10 +4989,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454147</v>
+        <v>454086</v>
       </c>
       <c r="R42" t="n">
-        <v>6991908</v>
+        <v>6991732</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5053,11 +5025,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5084,10 +5051,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124756703</v>
+        <v>124756700</v>
       </c>
       <c r="B43" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5100,21 +5067,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5124,10 +5091,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454100</v>
+        <v>454086</v>
       </c>
       <c r="R43" t="n">
-        <v>6991668</v>
+        <v>6991750</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5159,7 +5126,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5169,7 +5136,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5196,10 +5163,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124756706</v>
+        <v>124753636</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5212,34 +5179,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454071</v>
+        <v>454089</v>
       </c>
       <c r="R44" t="n">
-        <v>6991672</v>
+        <v>6991655</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5269,19 +5236,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>17:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5296,19 +5253,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124753601</v>
+        <v>124753598</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5348,10 +5305,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454103</v>
+        <v>454169</v>
       </c>
       <c r="R45" t="n">
-        <v>6991735</v>
+        <v>6991914</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5388,7 +5345,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5415,10 +5372,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124756701</v>
+        <v>124756697</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>74892</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5427,25 +5384,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5455,10 +5412,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454115</v>
+        <v>454177</v>
       </c>
       <c r="R46" t="n">
-        <v>6991653</v>
+        <v>6991911</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5490,7 +5447,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5500,7 +5457,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5511,6 +5468,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5527,10 +5499,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124753596</v>
+        <v>124756709</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5543,34 +5515,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454245</v>
+        <v>454040</v>
       </c>
       <c r="R47" t="n">
-        <v>6991630</v>
+        <v>6991636</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5600,14 +5572,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5622,22 +5599,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124753574</v>
+        <v>124756691</v>
       </c>
       <c r="B48" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5646,38 +5623,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454086</v>
+        <v>454339</v>
       </c>
       <c r="R48" t="n">
-        <v>6991732</v>
+        <v>6991639</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5707,39 +5696,55 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Min antal</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124753603</v>
+        <v>124756692</v>
       </c>
       <c r="B49" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5748,38 +5753,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454234</v>
+        <v>454256</v>
       </c>
       <c r="R49" t="n">
-        <v>6991643</v>
+        <v>6991683</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5809,9 +5814,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5826,22 +5841,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124756700</v>
+        <v>124756698</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5854,21 +5869,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5878,10 +5893,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454086</v>
+        <v>454144</v>
       </c>
       <c r="R50" t="n">
-        <v>6991750</v>
+        <v>6991886</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5913,7 +5928,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5923,7 +5938,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5950,10 +5965,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124753572</v>
+        <v>124753590</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5966,34 +5981,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454156</v>
+        <v>454096</v>
       </c>
       <c r="R51" t="n">
-        <v>6991902</v>
+        <v>6991720</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6026,6 +6049,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Bohål 5m upp i död gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6052,10 +6080,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124756691</v>
+        <v>124753593</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6064,50 +6092,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454339</v>
+        <v>454406</v>
       </c>
       <c r="R52" t="n">
-        <v>6991639</v>
+        <v>6991545</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6137,24 +6153,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Min antal</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6163,29 +6169,28 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124756693</v>
+        <v>124753597</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6198,34 +6203,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454196</v>
+        <v>454208</v>
       </c>
       <c r="R53" t="n">
-        <v>6991703</v>
+        <v>6991866</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6255,19 +6260,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>18:12</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>18:12</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6282,22 +6282,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124756692</v>
+        <v>124753602</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6310,34 +6310,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454256</v>
+        <v>454105</v>
       </c>
       <c r="R54" t="n">
-        <v>6991683</v>
+        <v>6991740</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6367,19 +6367,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>18:19</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6394,22 +6389,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124753594</v>
+        <v>124756702</v>
       </c>
       <c r="B55" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6422,34 +6417,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454351</v>
+        <v>454100</v>
       </c>
       <c r="R55" t="n">
-        <v>6991627</v>
+        <v>6991668</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6479,14 +6474,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6501,12 +6501,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124714894</v>
+        <v>124713829</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,39 +1867,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454168</v>
+        <v>454078</v>
       </c>
       <c r="R13" t="n">
-        <v>6991883</v>
+        <v>6991761</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,11 +1927,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1963,7 +1953,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124715915</v>
+        <v>124714894</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1999,19 +1989,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454272</v>
+        <v>454168</v>
       </c>
       <c r="R14" t="n">
-        <v>6991637</v>
+        <v>6991883</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2075,7 +2065,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124716123</v>
+        <v>124715915</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2120,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454310</v>
+        <v>454272</v>
       </c>
       <c r="R15" t="n">
-        <v>6991630</v>
+        <v>6991637</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2177,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124713829</v>
+        <v>124716123</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,34 +2193,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454078</v>
+        <v>454310</v>
       </c>
       <c r="R16" t="n">
-        <v>6991761</v>
+        <v>6991630</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,6 +2258,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2493,7 +2493,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124712085</v>
+        <v>124712512</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454054</v>
+        <v>454093</v>
       </c>
       <c r="R19" t="n">
-        <v>6991662</v>
+        <v>6991632</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2605,7 +2605,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124712512</v>
+        <v>124712085</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454093</v>
+        <v>454054</v>
       </c>
       <c r="R20" t="n">
-        <v>6991632</v>
+        <v>6991662</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3247,10 +3247,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124712037</v>
+        <v>124714283</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3263,21 +3263,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454053</v>
+        <v>454102</v>
       </c>
       <c r="R26" t="n">
-        <v>6991664</v>
+        <v>6991834</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124714283</v>
+        <v>124712037</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454102</v>
+        <v>454053</v>
       </c>
       <c r="R28" t="n">
-        <v>6991834</v>
+        <v>6991664</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4001,10 +4001,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124753594</v>
+        <v>124756703</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>77743</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4017,34 +4017,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454351</v>
+        <v>454100</v>
       </c>
       <c r="R33" t="n">
-        <v>6991627</v>
+        <v>6991668</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4074,14 +4074,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4096,22 +4101,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124756703</v>
+        <v>124753594</v>
       </c>
       <c r="B34" t="n">
-        <v>77743</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4124,34 +4129,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454100</v>
+        <v>454351</v>
       </c>
       <c r="R34" t="n">
-        <v>6991668</v>
+        <v>6991627</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4181,19 +4186,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>17:06</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4208,22 +4208,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124753601</v>
+        <v>124753589</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>91700</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4232,25 +4232,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454103</v>
+        <v>454148</v>
       </c>
       <c r="R35" t="n">
-        <v>6991735</v>
+        <v>6991844</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4296,11 +4296,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4327,10 +4322,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124753589</v>
+        <v>124753572</v>
       </c>
       <c r="B36" t="n">
-        <v>91700</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4339,25 +4334,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4367,10 +4362,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454148</v>
+        <v>454156</v>
       </c>
       <c r="R36" t="n">
-        <v>6991844</v>
+        <v>6991902</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4429,10 +4424,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124753572</v>
+        <v>124753601</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4445,21 +4440,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4469,10 +4464,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454156</v>
+        <v>454103</v>
       </c>
       <c r="R37" t="n">
-        <v>6991902</v>
+        <v>6991735</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4505,6 +4500,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4531,10 +4531,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124753596</v>
+        <v>124753603</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4543,25 +4543,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454245</v>
+        <v>454234</v>
       </c>
       <c r="R38" t="n">
-        <v>6991630</v>
+        <v>6991643</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4607,11 +4607,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4638,7 +4633,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124753600</v>
+        <v>124753596</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -4678,10 +4673,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454147</v>
+        <v>454245</v>
       </c>
       <c r="R39" t="n">
-        <v>6991908</v>
+        <v>6991630</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4718,7 +4713,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4745,10 +4740,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124753603</v>
+        <v>124753600</v>
       </c>
       <c r="B40" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4757,25 +4752,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4785,10 +4780,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454234</v>
+        <v>454147</v>
       </c>
       <c r="R40" t="n">
-        <v>6991643</v>
+        <v>6991908</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4821,6 +4816,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5051,10 +5051,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124756700</v>
+        <v>124753598</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5067,34 +5067,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454086</v>
+        <v>454169</v>
       </c>
       <c r="R43" t="n">
-        <v>6991750</v>
+        <v>6991914</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5124,19 +5124,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>17:30</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5151,22 +5146,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124753636</v>
+        <v>124756697</v>
       </c>
       <c r="B44" t="n">
-        <v>91030</v>
+        <v>74892</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5175,38 +5170,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454089</v>
+        <v>454177</v>
       </c>
       <c r="R44" t="n">
-        <v>6991655</v>
+        <v>6991911</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5236,11 +5231,21 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5249,26 +5254,41 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124753598</v>
+        <v>124756700</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5281,34 +5301,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454169</v>
+        <v>454086</v>
       </c>
       <c r="R45" t="n">
-        <v>6991914</v>
+        <v>6991750</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5338,14 +5358,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5360,22 +5385,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124756697</v>
+        <v>124753636</v>
       </c>
       <c r="B46" t="n">
-        <v>74892</v>
+        <v>91030</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5384,38 +5409,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>492</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454177</v>
+        <v>454089</v>
       </c>
       <c r="R46" t="n">
-        <v>6991911</v>
+        <v>6991655</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5445,21 +5470,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5468,31 +5483,16 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -2289,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124714299</v>
+        <v>124713664</v>
       </c>
       <c r="B17" t="n">
-        <v>82597</v>
+        <v>79892</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,21 +2305,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454102</v>
+        <v>454129</v>
       </c>
       <c r="R17" t="n">
-        <v>6991834</v>
+        <v>6991741</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124713664</v>
+        <v>124714299</v>
       </c>
       <c r="B18" t="n">
-        <v>79892</v>
+        <v>82597</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454129</v>
+        <v>454102</v>
       </c>
       <c r="R18" t="n">
-        <v>6991741</v>
+        <v>6991834</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3349,10 +3349,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124716113</v>
+        <v>124712037</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3365,39 +3365,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454311</v>
+        <v>454053</v>
       </c>
       <c r="R27" t="n">
-        <v>6991632</v>
+        <v>6991664</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,11 +3425,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3461,10 +3451,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124712037</v>
+        <v>124716113</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3477,34 +3467,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454053</v>
+        <v>454311</v>
       </c>
       <c r="R28" t="n">
-        <v>6991664</v>
+        <v>6991632</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,6 +3532,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3665,10 +3665,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124756701</v>
+        <v>124756693</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3681,21 +3681,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454115</v>
+        <v>454196</v>
       </c>
       <c r="R30" t="n">
-        <v>6991653</v>
+        <v>6991703</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3777,7 +3777,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124756693</v>
+        <v>124756706</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454196</v>
+        <v>454071</v>
       </c>
       <c r="R31" t="n">
-        <v>6991703</v>
+        <v>6991672</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3889,10 +3889,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124756706</v>
+        <v>124756701</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3905,21 +3905,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454071</v>
+        <v>454115</v>
       </c>
       <c r="R32" t="n">
-        <v>6991672</v>
+        <v>6991653</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5741,10 +5741,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124756692</v>
+        <v>124756698</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5757,21 +5757,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454256</v>
+        <v>454144</v>
       </c>
       <c r="R49" t="n">
-        <v>6991683</v>
+        <v>6991886</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5853,10 +5853,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124756698</v>
+        <v>124756692</v>
       </c>
       <c r="B50" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5869,21 +5869,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454144</v>
+        <v>454256</v>
       </c>
       <c r="R50" t="n">
-        <v>6991886</v>
+        <v>6991683</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6080,10 +6080,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124753593</v>
+        <v>124756702</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6096,34 +6096,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454406</v>
+        <v>454100</v>
       </c>
       <c r="R52" t="n">
-        <v>6991545</v>
+        <v>6991668</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6153,14 +6153,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6175,19 +6180,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124753597</v>
+        <v>124753593</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6227,10 +6232,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454208</v>
+        <v>454406</v>
       </c>
       <c r="R53" t="n">
-        <v>6991866</v>
+        <v>6991545</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6294,7 +6299,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124753602</v>
+        <v>124753597</v>
       </c>
       <c r="B54" t="n">
         <v>57513</v>
@@ -6334,10 +6339,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454105</v>
+        <v>454208</v>
       </c>
       <c r="R54" t="n">
-        <v>6991740</v>
+        <v>6991866</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6401,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124756702</v>
+        <v>124753602</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6417,34 +6422,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454100</v>
+        <v>454105</v>
       </c>
       <c r="R55" t="n">
-        <v>6991668</v>
+        <v>6991740</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6474,19 +6479,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>17:07</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6501,12 +6501,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124711120</v>
+        <v>124714580</v>
       </c>
       <c r="B2" t="n">
-        <v>78889</v>
+        <v>74892</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>492</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454041</v>
+        <v>454124</v>
       </c>
       <c r="R2" t="n">
-        <v>6991635</v>
+        <v>6991906</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124714580</v>
+        <v>124714894</v>
       </c>
       <c r="B3" t="n">
-        <v>74892</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454124</v>
+        <v>454168</v>
       </c>
       <c r="R3" t="n">
-        <v>6991906</v>
+        <v>6991883</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124715043</v>
+        <v>124715903</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454203</v>
+        <v>454272</v>
       </c>
       <c r="R4" t="n">
-        <v>6991872</v>
+        <v>6991636</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +970,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1093,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124712610</v>
+        <v>124716057</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1129,19 +1149,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454099</v>
+        <v>454290</v>
       </c>
       <c r="R6" t="n">
-        <v>6991631</v>
+        <v>6991649</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124712828</v>
+        <v>124716073</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,43 +1237,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454150</v>
+        <v>454289</v>
       </c>
       <c r="R7" t="n">
-        <v>6991620</v>
+        <v>6991650</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1305,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124713617</v>
+        <v>124716113</v>
       </c>
       <c r="B8" t="n">
-        <v>79851</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,38 +1343,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454129</v>
+        <v>454311</v>
       </c>
       <c r="R8" t="n">
-        <v>6991741</v>
+        <v>6991632</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1412,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124713188</v>
+        <v>124711120</v>
       </c>
       <c r="B9" t="n">
-        <v>82597</v>
+        <v>78889</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1459,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454120</v>
+        <v>454041</v>
       </c>
       <c r="R9" t="n">
-        <v>6991707</v>
+        <v>6991635</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1545,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124716366</v>
+        <v>124712610</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1557,19 +1581,19 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454349</v>
+        <v>454099</v>
       </c>
       <c r="R10" t="n">
-        <v>6991623</v>
+        <v>6991631</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124716073</v>
+        <v>124715915</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,30 +1669,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1677,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454289</v>
+        <v>454272</v>
       </c>
       <c r="R11" t="n">
-        <v>6991650</v>
+        <v>6991637</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,6 +1738,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1739,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124715903</v>
+        <v>124713617</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>79851</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,43 +1781,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454272</v>
+        <v>454129</v>
       </c>
       <c r="R12" t="n">
-        <v>6991636</v>
+        <v>6991741</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,11 +1845,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124713829</v>
+        <v>124714299</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>82597</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,21 +1887,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454078</v>
+        <v>454102</v>
       </c>
       <c r="R13" t="n">
-        <v>6991761</v>
+        <v>6991834</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,10 +1973,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124714894</v>
+        <v>124712709</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,39 +1989,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454168</v>
+        <v>454108</v>
       </c>
       <c r="R14" t="n">
-        <v>6991883</v>
+        <v>6991616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,11 +2049,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2065,10 +2075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124715915</v>
+        <v>124715043</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,39 +2091,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454272</v>
+        <v>454203</v>
       </c>
       <c r="R15" t="n">
-        <v>6991637</v>
+        <v>6991872</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,11 +2151,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2177,10 +2177,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124716123</v>
+        <v>124713188</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2193,39 +2193,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454310</v>
+        <v>454120</v>
       </c>
       <c r="R16" t="n">
-        <v>6991630</v>
+        <v>6991707</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,11 +2253,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2289,10 +2279,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124713664</v>
+        <v>124712512</v>
       </c>
       <c r="B17" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,34 +2295,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454129</v>
+        <v>454093</v>
       </c>
       <c r="R17" t="n">
-        <v>6991741</v>
+        <v>6991632</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,6 +2360,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2391,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124714299</v>
+        <v>124714283</v>
       </c>
       <c r="B18" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2493,7 +2493,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124712512</v>
+        <v>124716162</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2534,14 +2534,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454093</v>
+        <v>454310</v>
       </c>
       <c r="R19" t="n">
-        <v>6991632</v>
+        <v>6991630</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rinfhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,10 +2605,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124712085</v>
+        <v>124714775</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,39 +2621,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454054</v>
+        <v>454161</v>
       </c>
       <c r="R20" t="n">
-        <v>6991662</v>
+        <v>6991910</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,11 +2681,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2717,10 +2707,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124714230</v>
+        <v>124713664</v>
       </c>
       <c r="B21" t="n">
-        <v>91299</v>
+        <v>79892</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2733,21 +2723,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2757,10 +2747,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454102</v>
+        <v>454129</v>
       </c>
       <c r="R21" t="n">
-        <v>6991834</v>
+        <v>6991741</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2819,7 +2809,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124714775</v>
+        <v>124713829</v>
       </c>
       <c r="B22" t="n">
         <v>79891</v>
@@ -2859,10 +2849,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454161</v>
+        <v>454078</v>
       </c>
       <c r="R22" t="n">
-        <v>6991910</v>
+        <v>6991761</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2921,10 +2911,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124712709</v>
+        <v>124712828</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2937,34 +2927,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454108</v>
+        <v>454150</v>
       </c>
       <c r="R23" t="n">
-        <v>6991616</v>
+        <v>6991620</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,6 +2992,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3023,7 +3023,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124716057</v>
+        <v>124716063</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3059,7 +3059,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454290</v>
+        <v>454289</v>
       </c>
       <c r="R24" t="n">
-        <v>6991649</v>
+        <v>6991647</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124716063</v>
+        <v>124714230</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3151,39 +3151,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454289</v>
+        <v>454102</v>
       </c>
       <c r="R25" t="n">
-        <v>6991647</v>
+        <v>6991834</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,11 +3211,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3247,10 +3237,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124714283</v>
+        <v>124712037</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3263,21 +3253,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3287,10 +3277,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454102</v>
+        <v>454053</v>
       </c>
       <c r="R26" t="n">
-        <v>6991834</v>
+        <v>6991664</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3349,10 +3339,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124712037</v>
+        <v>124716366</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3365,34 +3355,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454053</v>
+        <v>454349</v>
       </c>
       <c r="R27" t="n">
-        <v>6991664</v>
+        <v>6991623</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,6 +3420,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3451,7 +3451,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124716113</v>
+        <v>124712085</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3487,19 +3487,19 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454311</v>
+        <v>454054</v>
       </c>
       <c r="R28" t="n">
-        <v>6991632</v>
+        <v>6991662</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124756693</v>
+        <v>124753602</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3681,34 +3681,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454196</v>
+        <v>454105</v>
       </c>
       <c r="R30" t="n">
-        <v>6991703</v>
+        <v>6991740</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3738,19 +3738,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>18:12</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>18:12</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3765,22 +3760,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124756706</v>
+        <v>124753596</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3793,34 +3788,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454071</v>
+        <v>454245</v>
       </c>
       <c r="R31" t="n">
-        <v>6991672</v>
+        <v>6991630</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3850,19 +3845,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:00</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3877,22 +3867,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124756701</v>
+        <v>124753598</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3905,34 +3895,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454115</v>
+        <v>454169</v>
       </c>
       <c r="R32" t="n">
-        <v>6991653</v>
+        <v>6991914</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3962,19 +3952,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>17:09</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>17:09</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3989,22 +3974,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124756703</v>
+        <v>124756700</v>
       </c>
       <c r="B33" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4017,21 +4002,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4041,10 +4026,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454100</v>
+        <v>454086</v>
       </c>
       <c r="R33" t="n">
-        <v>6991668</v>
+        <v>6991750</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4076,7 +4061,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4086,7 +4071,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4113,10 +4098,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124753594</v>
+        <v>124756691</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4125,38 +4110,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454351</v>
+        <v>454339</v>
       </c>
       <c r="R34" t="n">
-        <v>6991627</v>
+        <v>6991639</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4186,14 +4183,24 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Min antal</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4202,28 +4209,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124753589</v>
+        <v>124753600</v>
       </c>
       <c r="B35" t="n">
-        <v>91700</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4232,25 +4240,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4260,10 +4268,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454148</v>
+        <v>454147</v>
       </c>
       <c r="R35" t="n">
-        <v>6991844</v>
+        <v>6991908</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4296,6 +4304,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4322,10 +4335,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124753572</v>
+        <v>124753590</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4338,34 +4351,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454156</v>
+        <v>454096</v>
       </c>
       <c r="R36" t="n">
-        <v>6991902</v>
+        <v>6991720</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4398,6 +4419,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Bohål 5m upp i död gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4424,7 +4450,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124753601</v>
+        <v>124753594</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4464,10 +4490,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454103</v>
+        <v>454351</v>
       </c>
       <c r="R37" t="n">
-        <v>6991735</v>
+        <v>6991627</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4531,10 +4557,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124753603</v>
+        <v>124756709</v>
       </c>
       <c r="B38" t="n">
-        <v>91705</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4543,38 +4569,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454234</v>
+        <v>454040</v>
       </c>
       <c r="R38" t="n">
-        <v>6991643</v>
+        <v>6991636</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4604,9 +4630,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4621,22 +4657,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124753596</v>
+        <v>124756701</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4649,34 +4685,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454245</v>
+        <v>454115</v>
       </c>
       <c r="R39" t="n">
-        <v>6991630</v>
+        <v>6991653</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4706,14 +4742,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4728,22 +4769,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124753600</v>
+        <v>124756703</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>77743</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4756,34 +4797,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454147</v>
+        <v>454100</v>
       </c>
       <c r="R40" t="n">
-        <v>6991908</v>
+        <v>6991668</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4813,14 +4854,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4835,22 +4881,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124753573</v>
+        <v>124753603</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>91705</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4859,25 +4905,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4887,10 +4933,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454135</v>
+        <v>454234</v>
       </c>
       <c r="R41" t="n">
-        <v>6991889</v>
+        <v>6991643</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4949,10 +4995,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124753574</v>
+        <v>124756702</v>
       </c>
       <c r="B42" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4965,34 +5011,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454086</v>
+        <v>454100</v>
       </c>
       <c r="R42" t="n">
-        <v>6991732</v>
+        <v>6991668</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5022,9 +5068,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5039,22 +5095,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124753598</v>
+        <v>124756698</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5067,34 +5123,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454169</v>
+        <v>454144</v>
       </c>
       <c r="R43" t="n">
-        <v>6991914</v>
+        <v>6991886</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5124,14 +5180,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5146,22 +5207,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124756697</v>
+        <v>124753572</v>
       </c>
       <c r="B44" t="n">
-        <v>74892</v>
+        <v>91012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5170,38 +5231,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454177</v>
+        <v>454156</v>
       </c>
       <c r="R44" t="n">
-        <v>6991911</v>
+        <v>6991902</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5231,21 +5292,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5254,41 +5305,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124756700</v>
+        <v>124753589</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>91700</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5297,38 +5333,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454086</v>
+        <v>454148</v>
       </c>
       <c r="R45" t="n">
-        <v>6991750</v>
+        <v>6991844</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5358,19 +5394,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5385,12 +5411,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5499,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124756709</v>
+        <v>124753593</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5515,34 +5541,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454040</v>
+        <v>454406</v>
       </c>
       <c r="R47" t="n">
-        <v>6991636</v>
+        <v>6991545</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5572,19 +5598,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:56</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5599,22 +5620,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124756691</v>
+        <v>124753573</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5623,50 +5644,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454339</v>
+        <v>454135</v>
       </c>
       <c r="R48" t="n">
-        <v>6991639</v>
+        <v>6991889</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5696,55 +5705,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Min antal</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124756698</v>
+        <v>124753597</v>
       </c>
       <c r="B49" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5757,34 +5750,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454144</v>
+        <v>454208</v>
       </c>
       <c r="R49" t="n">
-        <v>6991886</v>
+        <v>6991866</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5814,19 +5807,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>17:48</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5841,19 +5829,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124756692</v>
+        <v>124756693</v>
       </c>
       <c r="B50" t="n">
         <v>78810</v>
@@ -5893,10 +5881,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454256</v>
+        <v>454196</v>
       </c>
       <c r="R50" t="n">
-        <v>6991683</v>
+        <v>6991703</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5928,7 +5916,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5938,7 +5926,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5965,10 +5953,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124753590</v>
+        <v>124756706</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5981,42 +5969,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454096</v>
+        <v>454071</v>
       </c>
       <c r="R51" t="n">
-        <v>6991720</v>
+        <v>6991672</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6046,14 +6026,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Bohål 5m upp i död gran</t>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6068,22 +6053,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124756702</v>
+        <v>124756697</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>74892</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6092,25 +6077,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6120,10 +6105,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454100</v>
+        <v>454177</v>
       </c>
       <c r="R52" t="n">
-        <v>6991668</v>
+        <v>6991911</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,7 +6140,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6165,7 +6150,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6176,6 +6161,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6192,10 +6192,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124753593</v>
+        <v>124753574</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6208,21 +6208,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454406</v>
+        <v>454086</v>
       </c>
       <c r="R53" t="n">
-        <v>6991545</v>
+        <v>6991732</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6268,11 +6268,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6299,7 +6294,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124753597</v>
+        <v>124753601</v>
       </c>
       <c r="B54" t="n">
         <v>57513</v>
@@ -6339,10 +6334,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454208</v>
+        <v>454103</v>
       </c>
       <c r="R54" t="n">
-        <v>6991866</v>
+        <v>6991735</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,10 +6401,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124753602</v>
+        <v>124756692</v>
       </c>
       <c r="B55" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6422,34 +6417,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454105</v>
+        <v>454256</v>
       </c>
       <c r="R55" t="n">
-        <v>6991740</v>
+        <v>6991683</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6479,14 +6474,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6501,12 +6501,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124714580</v>
+        <v>124716162</v>
       </c>
       <c r="B2" t="n">
-        <v>74892</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454124</v>
+        <v>454310</v>
       </c>
       <c r="R2" t="n">
-        <v>6991906</v>
+        <v>6991630</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rinfhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124714894</v>
+        <v>124716366</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -818,14 +828,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454168</v>
+        <v>454349</v>
       </c>
       <c r="R3" t="n">
-        <v>6991883</v>
+        <v>6991623</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124715903</v>
+        <v>124713617</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>79851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,43 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454272</v>
+        <v>454129</v>
       </c>
       <c r="R4" t="n">
-        <v>6991636</v>
+        <v>6991741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,11 +975,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124715943</v>
+        <v>124716113</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1037,7 +1037,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454281</v>
+        <v>454311</v>
       </c>
       <c r="R5" t="n">
-        <v>6991629</v>
+        <v>6991632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124716057</v>
+        <v>124713829</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,39 +1129,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454290</v>
+        <v>454078</v>
       </c>
       <c r="R6" t="n">
-        <v>6991649</v>
+        <v>6991761</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,11 +1189,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124716073</v>
+        <v>124714283</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,42 +1227,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454289</v>
+        <v>454102</v>
       </c>
       <c r="R7" t="n">
-        <v>6991650</v>
+        <v>6991834</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124716113</v>
+        <v>124716057</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1376,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454311</v>
+        <v>454290</v>
       </c>
       <c r="R8" t="n">
-        <v>6991632</v>
+        <v>6991649</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124711120</v>
+        <v>124715915</v>
       </c>
       <c r="B9" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,34 +1445,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454041</v>
+        <v>454272</v>
       </c>
       <c r="R9" t="n">
-        <v>6991635</v>
+        <v>6991637</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,6 +1510,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124712610</v>
+        <v>124712512</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1590,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454099</v>
+        <v>454093</v>
       </c>
       <c r="R10" t="n">
-        <v>6991631</v>
+        <v>6991632</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1657,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124715915</v>
+        <v>124714775</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,39 +1669,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454272</v>
+        <v>454161</v>
       </c>
       <c r="R11" t="n">
-        <v>6991637</v>
+        <v>6991910</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,11 +1729,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124713617</v>
+        <v>124715043</v>
       </c>
       <c r="B12" t="n">
-        <v>79851</v>
+        <v>91299</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,25 +1767,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1809,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454129</v>
+        <v>454203</v>
       </c>
       <c r="R12" t="n">
-        <v>6991741</v>
+        <v>6991872</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124714299</v>
+        <v>124714580</v>
       </c>
       <c r="B13" t="n">
-        <v>82597</v>
+        <v>74892</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,25 +1869,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>492</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454102</v>
+        <v>454124</v>
       </c>
       <c r="R13" t="n">
-        <v>6991834</v>
+        <v>6991906</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1973,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124712709</v>
+        <v>124712610</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1989,34 +1975,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454108</v>
+        <v>454099</v>
       </c>
       <c r="R14" t="n">
-        <v>6991616</v>
+        <v>6991631</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,6 +2040,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124715043</v>
+        <v>124712709</v>
       </c>
       <c r="B15" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2091,21 +2087,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2115,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454203</v>
+        <v>454108</v>
       </c>
       <c r="R15" t="n">
-        <v>6991872</v>
+        <v>6991616</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2177,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124713188</v>
+        <v>124712037</v>
       </c>
       <c r="B16" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2193,21 +2189,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2217,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454120</v>
+        <v>454053</v>
       </c>
       <c r="R16" t="n">
-        <v>6991707</v>
+        <v>6991664</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2279,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124712512</v>
+        <v>124714299</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2295,39 +2291,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454093</v>
+        <v>454102</v>
       </c>
       <c r="R17" t="n">
-        <v>6991632</v>
+        <v>6991834</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,11 +2351,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2391,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124714283</v>
+        <v>124715903</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,34 +2393,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454102</v>
+        <v>454272</v>
       </c>
       <c r="R18" t="n">
-        <v>6991834</v>
+        <v>6991636</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,6 +2458,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2493,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124716162</v>
+        <v>124712085</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2534,14 +2530,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454310</v>
+        <v>454054</v>
       </c>
       <c r="R19" t="n">
-        <v>6991630</v>
+        <v>6991662</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2578,7 +2574,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rinfhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124714775</v>
+        <v>124713664</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,21 +2617,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454161</v>
+        <v>454129</v>
       </c>
       <c r="R20" t="n">
-        <v>6991910</v>
+        <v>6991741</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124713664</v>
+        <v>124716063</v>
       </c>
       <c r="B21" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2723,34 +2719,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454129</v>
+        <v>454289</v>
       </c>
       <c r="R21" t="n">
-        <v>6991741</v>
+        <v>6991647</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,6 +2784,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2809,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124713829</v>
+        <v>124713606</v>
       </c>
       <c r="B22" t="n">
         <v>79891</v>
@@ -2849,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454078</v>
+        <v>454129</v>
       </c>
       <c r="R22" t="n">
-        <v>6991761</v>
+        <v>6991741</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2911,7 +2917,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124712828</v>
+        <v>124715943</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2947,19 +2953,19 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454150</v>
+        <v>454281</v>
       </c>
       <c r="R23" t="n">
-        <v>6991620</v>
+        <v>6991629</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3023,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124716063</v>
+        <v>124713188</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3039,39 +3045,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454289</v>
+        <v>454120</v>
       </c>
       <c r="R24" t="n">
-        <v>6991647</v>
+        <v>6991707</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,11 +3105,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3135,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124714230</v>
+        <v>124712828</v>
       </c>
       <c r="B25" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3151,34 +3147,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454102</v>
+        <v>454150</v>
       </c>
       <c r="R25" t="n">
-        <v>6991834</v>
+        <v>6991620</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,6 +3212,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3237,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124712037</v>
+        <v>124711120</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>78889</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3253,21 +3259,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3277,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454053</v>
+        <v>454041</v>
       </c>
       <c r="R26" t="n">
-        <v>6991664</v>
+        <v>6991635</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3339,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124716366</v>
+        <v>124716073</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3351,31 +3357,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3384,10 +3389,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454349</v>
+        <v>454289</v>
       </c>
       <c r="R27" t="n">
-        <v>6991623</v>
+        <v>6991650</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,11 +3425,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3451,10 +3451,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124712085</v>
+        <v>124714230</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3467,39 +3467,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454054</v>
+        <v>454102</v>
       </c>
       <c r="R28" t="n">
-        <v>6991662</v>
+        <v>6991834</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,11 +3527,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3563,10 +3553,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124713606</v>
+        <v>124714894</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3579,34 +3569,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454129</v>
+        <v>454168</v>
       </c>
       <c r="R29" t="n">
-        <v>6991741</v>
+        <v>6991883</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,6 +3634,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3665,7 +3665,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124753602</v>
+        <v>124753593</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454105</v>
+        <v>454406</v>
       </c>
       <c r="R30" t="n">
-        <v>6991740</v>
+        <v>6991545</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124753596</v>
+        <v>124756692</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3788,34 +3788,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454245</v>
+        <v>454256</v>
       </c>
       <c r="R31" t="n">
-        <v>6991630</v>
+        <v>6991683</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3845,14 +3845,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3867,19 +3872,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124753598</v>
+        <v>124753600</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -3919,10 +3924,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454169</v>
+        <v>454147</v>
       </c>
       <c r="R32" t="n">
-        <v>6991914</v>
+        <v>6991908</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3986,10 +3991,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124756700</v>
+        <v>124753594</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4002,34 +4007,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454086</v>
+        <v>454351</v>
       </c>
       <c r="R33" t="n">
-        <v>6991750</v>
+        <v>6991627</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4059,19 +4064,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>17:30</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4086,22 +4086,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124756691</v>
+        <v>124753602</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4110,50 +4110,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454339</v>
+        <v>454105</v>
       </c>
       <c r="R34" t="n">
-        <v>6991639</v>
+        <v>6991740</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4183,24 +4171,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Min antal</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4209,29 +4187,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124753600</v>
+        <v>124756697</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>74892</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4240,38 +4217,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454147</v>
+        <v>454177</v>
       </c>
       <c r="R35" t="n">
-        <v>6991908</v>
+        <v>6991911</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4301,14 +4278,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4319,26 +4301,41 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124753590</v>
+        <v>124753603</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4347,46 +4344,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454096</v>
+        <v>454234</v>
       </c>
       <c r="R36" t="n">
-        <v>6991720</v>
+        <v>6991643</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4419,11 +4408,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Bohål 5m upp i död gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4450,10 +4434,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124753594</v>
+        <v>124756702</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4466,34 +4450,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454351</v>
+        <v>454100</v>
       </c>
       <c r="R37" t="n">
-        <v>6991627</v>
+        <v>6991668</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4523,14 +4507,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4545,22 +4534,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124756709</v>
+        <v>124756706</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4573,21 +4562,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4597,10 +4586,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454040</v>
+        <v>454071</v>
       </c>
       <c r="R38" t="n">
-        <v>6991636</v>
+        <v>6991672</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4632,7 +4621,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4642,7 +4631,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4669,7 +4658,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124756701</v>
+        <v>124753572</v>
       </c>
       <c r="B39" t="n">
         <v>91012</v>
@@ -4705,14 +4694,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454115</v>
+        <v>454156</v>
       </c>
       <c r="R39" t="n">
-        <v>6991653</v>
+        <v>6991902</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4742,19 +4731,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>17:09</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>17:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4769,22 +4748,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124756703</v>
+        <v>124756691</v>
       </c>
       <c r="B40" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4793,38 +4772,50 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454100</v>
+        <v>454339</v>
       </c>
       <c r="R40" t="n">
-        <v>6991668</v>
+        <v>6991639</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4856,7 +4847,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4866,7 +4857,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Min antal</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4875,6 +4871,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4893,10 +4890,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124753603</v>
+        <v>124756698</v>
       </c>
       <c r="B41" t="n">
-        <v>91705</v>
+        <v>82597</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4905,38 +4902,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>67</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454234</v>
+        <v>454144</v>
       </c>
       <c r="R41" t="n">
-        <v>6991643</v>
+        <v>6991886</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4966,9 +4963,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4983,22 +4990,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124756702</v>
+        <v>124753574</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5011,34 +5018,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454100</v>
+        <v>454086</v>
       </c>
       <c r="R42" t="n">
-        <v>6991668</v>
+        <v>6991732</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5068,19 +5075,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>17:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5095,22 +5092,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124756698</v>
+        <v>124756701</v>
       </c>
       <c r="B43" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5123,21 +5120,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5147,10 +5144,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454144</v>
+        <v>454115</v>
       </c>
       <c r="R43" t="n">
-        <v>6991886</v>
+        <v>6991653</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5182,7 +5179,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5192,7 +5189,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5219,10 +5216,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124753572</v>
+        <v>124753590</v>
       </c>
       <c r="B44" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5235,34 +5232,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454156</v>
+        <v>454096</v>
       </c>
       <c r="R44" t="n">
-        <v>6991902</v>
+        <v>6991720</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5295,6 +5300,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Bohål 5m upp i död gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5321,10 +5331,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124753589</v>
+        <v>124753573</v>
       </c>
       <c r="B45" t="n">
-        <v>91700</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5333,25 +5343,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5361,10 +5371,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454148</v>
+        <v>454135</v>
       </c>
       <c r="R45" t="n">
-        <v>6991844</v>
+        <v>6991889</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5423,10 +5433,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124753636</v>
+        <v>124753589</v>
       </c>
       <c r="B46" t="n">
-        <v>91030</v>
+        <v>91700</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5435,25 +5445,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5463,10 +5473,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454089</v>
+        <v>454148</v>
       </c>
       <c r="R46" t="n">
-        <v>6991655</v>
+        <v>6991844</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5525,10 +5535,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124753593</v>
+        <v>124756700</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5541,34 +5551,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454406</v>
+        <v>454086</v>
       </c>
       <c r="R47" t="n">
-        <v>6991545</v>
+        <v>6991750</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5598,14 +5608,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5620,22 +5635,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124753573</v>
+        <v>124756703</v>
       </c>
       <c r="B48" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5648,34 +5663,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454135</v>
+        <v>454100</v>
       </c>
       <c r="R48" t="n">
-        <v>6991889</v>
+        <v>6991668</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5705,9 +5720,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,19 +5747,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124753597</v>
+        <v>124753598</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -5774,10 +5799,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454208</v>
+        <v>454169</v>
       </c>
       <c r="R49" t="n">
-        <v>6991866</v>
+        <v>6991914</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5814,7 +5839,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5953,10 +5978,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124756706</v>
+        <v>124753601</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5969,34 +5994,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454071</v>
+        <v>454103</v>
       </c>
       <c r="R51" t="n">
-        <v>6991672</v>
+        <v>6991735</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6026,19 +6051,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>17:00</t>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6053,22 +6073,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124756697</v>
+        <v>124753596</v>
       </c>
       <c r="B52" t="n">
-        <v>74892</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6077,38 +6097,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454177</v>
+        <v>454245</v>
       </c>
       <c r="R52" t="n">
-        <v>6991911</v>
+        <v>6991630</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6138,19 +6158,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>17:55</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6161,38 +6176,23 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124753574</v>
+        <v>124756709</v>
       </c>
       <c r="B53" t="n">
         <v>91012</v>
@@ -6228,14 +6228,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454086</v>
+        <v>454040</v>
       </c>
       <c r="R53" t="n">
-        <v>6991732</v>
+        <v>6991636</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6265,9 +6265,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6282,19 +6292,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124753601</v>
+        <v>124753597</v>
       </c>
       <c r="B54" t="n">
         <v>57513</v>
@@ -6334,10 +6344,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454103</v>
+        <v>454208</v>
       </c>
       <c r="R54" t="n">
-        <v>6991735</v>
+        <v>6991866</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6401,10 +6411,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124756692</v>
+        <v>124753636</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6417,34 +6427,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454256</v>
+        <v>454089</v>
       </c>
       <c r="R55" t="n">
-        <v>6991683</v>
+        <v>6991655</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6474,19 +6484,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>18:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6501,12 +6501,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124715043</v>
+        <v>124714580</v>
       </c>
       <c r="B12" t="n">
-        <v>91299</v>
+        <v>74892</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,25 +1767,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>492</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454203</v>
+        <v>454124</v>
       </c>
       <c r="R12" t="n">
-        <v>6991872</v>
+        <v>6991906</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124714580</v>
+        <v>124715043</v>
       </c>
       <c r="B13" t="n">
-        <v>74892</v>
+        <v>91299</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1869,25 +1869,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>492</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454124</v>
+        <v>454203</v>
       </c>
       <c r="R13" t="n">
-        <v>6991906</v>
+        <v>6991872</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124753598</v>
+        <v>124756693</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5775,34 +5775,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454169</v>
+        <v>454196</v>
       </c>
       <c r="R49" t="n">
-        <v>6991914</v>
+        <v>6991703</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5832,14 +5832,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5854,22 +5859,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124756693</v>
+        <v>124753598</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5882,34 +5887,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454196</v>
+        <v>454169</v>
       </c>
       <c r="R50" t="n">
-        <v>6991703</v>
+        <v>6991914</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5939,19 +5944,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>18:12</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>18:12</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5966,12 +5966,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6192,10 +6192,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124756709</v>
+        <v>124753597</v>
       </c>
       <c r="B53" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6208,34 +6208,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454040</v>
+        <v>454208</v>
       </c>
       <c r="R53" t="n">
-        <v>6991636</v>
+        <v>6991866</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6265,19 +6265,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>16:56</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6292,22 +6287,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124753597</v>
+        <v>124756709</v>
       </c>
       <c r="B54" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6320,34 +6315,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454208</v>
+        <v>454040</v>
       </c>
       <c r="R54" t="n">
-        <v>6991866</v>
+        <v>6991636</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6377,14 +6372,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6399,12 +6399,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124716162</v>
+        <v>124716113</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454310</v>
+        <v>454311</v>
       </c>
       <c r="R2" t="n">
-        <v>6991630</v>
+        <v>6991632</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rinfhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124716366</v>
+        <v>124713829</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454349</v>
+        <v>454078</v>
       </c>
       <c r="R3" t="n">
-        <v>6991623</v>
+        <v>6991761</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124713617</v>
+        <v>124715903</v>
       </c>
       <c r="B4" t="n">
-        <v>79851</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +901,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454129</v>
+        <v>454272</v>
       </c>
       <c r="R4" t="n">
-        <v>6991741</v>
+        <v>6991636</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,6 +970,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124716113</v>
+        <v>124716162</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1037,7 +1037,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454311</v>
+        <v>454310</v>
       </c>
       <c r="R5" t="n">
-        <v>6991632</v>
+        <v>6991630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rinfhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124713829</v>
+        <v>124716366</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,34 +1129,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454078</v>
+        <v>454349</v>
       </c>
       <c r="R6" t="n">
-        <v>6991761</v>
+        <v>6991623</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,6 +1194,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124716057</v>
+        <v>124713664</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,39 +1343,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454290</v>
+        <v>454129</v>
       </c>
       <c r="R8" t="n">
-        <v>6991649</v>
+        <v>6991741</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,11 +1403,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124715915</v>
+        <v>124714230</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,39 +1445,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454272</v>
+        <v>454102</v>
       </c>
       <c r="R9" t="n">
-        <v>6991637</v>
+        <v>6991834</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,11 +1505,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124712512</v>
+        <v>124714299</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,39 +1547,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454093</v>
+        <v>454102</v>
       </c>
       <c r="R10" t="n">
-        <v>6991632</v>
+        <v>6991834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,11 +1607,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124714775</v>
+        <v>124711120</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>78889</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454161</v>
+        <v>454041</v>
       </c>
       <c r="R11" t="n">
-        <v>6991910</v>
+        <v>6991635</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1755,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124714580</v>
+        <v>124712512</v>
       </c>
       <c r="B12" t="n">
-        <v>74892</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,38 +1747,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454124</v>
+        <v>454093</v>
       </c>
       <c r="R12" t="n">
-        <v>6991906</v>
+        <v>6991632</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,6 +1816,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124715043</v>
+        <v>124712037</v>
       </c>
       <c r="B13" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454203</v>
+        <v>454053</v>
       </c>
       <c r="R13" t="n">
-        <v>6991872</v>
+        <v>6991664</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124712610</v>
+        <v>124714775</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,39 +1965,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454099</v>
+        <v>454161</v>
       </c>
       <c r="R14" t="n">
-        <v>6991631</v>
+        <v>6991910</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,11 +2025,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124712709</v>
+        <v>124712085</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2087,34 +2067,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454108</v>
+        <v>454054</v>
       </c>
       <c r="R15" t="n">
-        <v>6991616</v>
+        <v>6991662</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,6 +2132,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124712037</v>
+        <v>124712610</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2189,34 +2179,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454053</v>
+        <v>454099</v>
       </c>
       <c r="R16" t="n">
-        <v>6991664</v>
+        <v>6991631</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,6 +2244,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124714299</v>
+        <v>124716063</v>
       </c>
       <c r="B17" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,34 +2291,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454102</v>
+        <v>454289</v>
       </c>
       <c r="R17" t="n">
-        <v>6991834</v>
+        <v>6991647</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,6 +2356,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124715903</v>
+        <v>124713606</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,39 +2403,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454272</v>
+        <v>454129</v>
       </c>
       <c r="R18" t="n">
-        <v>6991636</v>
+        <v>6991741</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2458,11 +2463,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124712085</v>
+        <v>124714894</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2525,7 +2525,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454054</v>
+        <v>454168</v>
       </c>
       <c r="R19" t="n">
-        <v>6991662</v>
+        <v>6991883</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124713664</v>
+        <v>124715915</v>
       </c>
       <c r="B20" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2617,34 +2617,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454129</v>
+        <v>454272</v>
       </c>
       <c r="R20" t="n">
-        <v>6991741</v>
+        <v>6991637</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2677,6 +2682,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,7 +2713,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124716063</v>
+        <v>124716057</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2739,7 +2749,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2748,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454289</v>
+        <v>454290</v>
       </c>
       <c r="R21" t="n">
-        <v>6991647</v>
+        <v>6991649</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124713606</v>
+        <v>124716073</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2827,38 +2837,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454129</v>
+        <v>454289</v>
       </c>
       <c r="R22" t="n">
-        <v>6991741</v>
+        <v>6991650</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2917,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124715943</v>
+        <v>124714580</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>74892</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2929,43 +2943,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454281</v>
+        <v>454124</v>
       </c>
       <c r="R23" t="n">
-        <v>6991629</v>
+        <v>6991906</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2998,11 +3007,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3243,10 +3247,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124711120</v>
+        <v>124715943</v>
       </c>
       <c r="B26" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3259,34 +3263,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454041</v>
+        <v>454281</v>
       </c>
       <c r="R26" t="n">
-        <v>6991635</v>
+        <v>6991629</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3319,6 +3328,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,10 +3359,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124716073</v>
+        <v>124712709</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3357,42 +3371,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454289</v>
+        <v>454108</v>
       </c>
       <c r="R27" t="n">
-        <v>6991650</v>
+        <v>6991616</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3451,7 +3461,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124714230</v>
+        <v>124715043</v>
       </c>
       <c r="B28" t="n">
         <v>91299</v>
@@ -3491,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454102</v>
+        <v>454203</v>
       </c>
       <c r="R28" t="n">
-        <v>6991834</v>
+        <v>6991872</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3553,10 +3563,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124714894</v>
+        <v>124713617</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>79851</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3565,43 +3575,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454168</v>
+        <v>454129</v>
       </c>
       <c r="R29" t="n">
-        <v>6991883</v>
+        <v>6991741</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,11 +3639,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3665,10 +3665,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124753593</v>
+        <v>124753589</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>91700</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3677,25 +3677,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454406</v>
+        <v>454148</v>
       </c>
       <c r="R30" t="n">
-        <v>6991545</v>
+        <v>6991844</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,11 +3741,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3772,10 +3767,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124756692</v>
+        <v>124753597</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3788,34 +3783,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454256</v>
+        <v>454208</v>
       </c>
       <c r="R31" t="n">
-        <v>6991683</v>
+        <v>6991866</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3845,19 +3840,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>18:19</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3872,12 +3862,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3991,10 +3981,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124753594</v>
+        <v>124756691</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4003,38 +3993,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454351</v>
+        <v>454339</v>
       </c>
       <c r="R33" t="n">
-        <v>6991627</v>
+        <v>6991639</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4064,14 +4066,24 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Min antal</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4080,25 +4092,26 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124753602</v>
+        <v>124753596</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4138,10 +4151,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454105</v>
+        <v>454245</v>
       </c>
       <c r="R34" t="n">
-        <v>6991740</v>
+        <v>6991630</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4178,7 +4191,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4205,10 +4218,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124756697</v>
+        <v>124753590</v>
       </c>
       <c r="B35" t="n">
-        <v>74892</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4217,38 +4230,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454177</v>
+        <v>454096</v>
       </c>
       <c r="R35" t="n">
-        <v>6991911</v>
+        <v>6991720</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4278,19 +4299,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>17:55</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Bohål 5m upp i död gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4301,31 +4317,16 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4546,10 +4547,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124756706</v>
+        <v>124753602</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4562,34 +4563,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454071</v>
+        <v>454105</v>
       </c>
       <c r="R38" t="n">
-        <v>6991672</v>
+        <v>6991740</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4619,19 +4620,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>17:00</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4646,22 +4642,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124753572</v>
+        <v>124756703</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4674,34 +4670,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454156</v>
+        <v>454100</v>
       </c>
       <c r="R39" t="n">
-        <v>6991902</v>
+        <v>6991668</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4731,9 +4727,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4748,22 +4754,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124756691</v>
+        <v>124756698</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4772,50 +4778,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454339</v>
+        <v>454144</v>
       </c>
       <c r="R40" t="n">
-        <v>6991639</v>
+        <v>6991886</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4847,7 +4841,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4857,12 +4851,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Min antal</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4871,7 +4860,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4890,10 +4878,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124756698</v>
+        <v>124753601</v>
       </c>
       <c r="B41" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4906,34 +4894,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454144</v>
+        <v>454103</v>
       </c>
       <c r="R41" t="n">
-        <v>6991886</v>
+        <v>6991735</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4963,19 +4951,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>17:48</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4990,19 +4973,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124753574</v>
+        <v>124756701</v>
       </c>
       <c r="B42" t="n">
         <v>91012</v>
@@ -5038,14 +5021,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454086</v>
+        <v>454115</v>
       </c>
       <c r="R42" t="n">
-        <v>6991732</v>
+        <v>6991653</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5075,9 +5058,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5092,22 +5085,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124756701</v>
+        <v>124753594</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5120,34 +5113,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454115</v>
+        <v>454351</v>
       </c>
       <c r="R43" t="n">
-        <v>6991653</v>
+        <v>6991627</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5177,19 +5170,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>17:09</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>17:09</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5204,22 +5192,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124753590</v>
+        <v>124756700</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5232,42 +5220,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454096</v>
+        <v>454086</v>
       </c>
       <c r="R44" t="n">
-        <v>6991720</v>
+        <v>6991750</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5297,14 +5277,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Bohål 5m upp i död gran</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5319,22 +5304,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124753573</v>
+        <v>124756706</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5347,34 +5332,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454135</v>
+        <v>454071</v>
       </c>
       <c r="R45" t="n">
-        <v>6991889</v>
+        <v>6991672</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5404,9 +5389,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5421,22 +5416,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124753589</v>
+        <v>124756709</v>
       </c>
       <c r="B46" t="n">
-        <v>91700</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5445,38 +5440,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454148</v>
+        <v>454040</v>
       </c>
       <c r="R46" t="n">
-        <v>6991844</v>
+        <v>6991636</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5506,9 +5501,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5523,22 +5528,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124756700</v>
+        <v>124753573</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5551,34 +5556,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454086</v>
+        <v>454135</v>
       </c>
       <c r="R47" t="n">
-        <v>6991750</v>
+        <v>6991889</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5608,19 +5613,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5635,22 +5630,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124756703</v>
+        <v>124756697</v>
       </c>
       <c r="B48" t="n">
-        <v>77743</v>
+        <v>74892</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5659,25 +5654,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228579</v>
+        <v>492</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5687,10 +5682,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454100</v>
+        <v>454177</v>
       </c>
       <c r="R48" t="n">
-        <v>6991668</v>
+        <v>6991911</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5722,7 +5717,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5732,7 +5727,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5743,6 +5738,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5871,10 +5881,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124753598</v>
+        <v>124753572</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5887,21 +5897,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5911,10 +5921,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454169</v>
+        <v>454156</v>
       </c>
       <c r="R50" t="n">
-        <v>6991914</v>
+        <v>6991902</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5947,11 +5957,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5978,10 +5983,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124753601</v>
+        <v>124753636</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5994,21 +5999,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6018,10 +6023,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454103</v>
+        <v>454089</v>
       </c>
       <c r="R51" t="n">
-        <v>6991735</v>
+        <v>6991655</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6054,11 +6059,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6085,7 +6085,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124753596</v>
+        <v>124753593</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454245</v>
+        <v>454406</v>
       </c>
       <c r="R52" t="n">
-        <v>6991630</v>
+        <v>6991545</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6192,7 +6192,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124753597</v>
+        <v>124753598</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454208</v>
+        <v>454169</v>
       </c>
       <c r="R53" t="n">
-        <v>6991866</v>
+        <v>6991914</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6299,10 +6299,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124756709</v>
+        <v>124756692</v>
       </c>
       <c r="B54" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6315,21 +6315,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454040</v>
+        <v>454256</v>
       </c>
       <c r="R54" t="n">
-        <v>6991636</v>
+        <v>6991683</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6411,10 +6411,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124753636</v>
+        <v>124753574</v>
       </c>
       <c r="B55" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6427,21 +6427,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6451,10 +6451,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454089</v>
+        <v>454086</v>
       </c>
       <c r="R55" t="n">
-        <v>6991655</v>
+        <v>6991732</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124711120</v>
+        <v>124712512</v>
       </c>
       <c r="B11" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,34 +1649,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454041</v>
+        <v>454093</v>
       </c>
       <c r="R11" t="n">
-        <v>6991635</v>
+        <v>6991632</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1714,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124712512</v>
+        <v>124711120</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,39 +1761,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454093</v>
+        <v>454041</v>
       </c>
       <c r="R12" t="n">
-        <v>6991632</v>
+        <v>6991635</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,11 +1821,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2713,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124716057</v>
+        <v>124716073</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2725,31 +2725,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2758,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454290</v>
+        <v>454289</v>
       </c>
       <c r="R21" t="n">
-        <v>6991649</v>
+        <v>6991650</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2794,11 +2793,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2825,10 +2819,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124716073</v>
+        <v>124716057</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2837,30 +2831,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2869,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454289</v>
+        <v>454290</v>
       </c>
       <c r="R22" t="n">
-        <v>6991650</v>
+        <v>6991649</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,6 +2900,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124714580</v>
+        <v>124712828</v>
       </c>
       <c r="B23" t="n">
-        <v>74892</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2943,38 +2943,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454124</v>
+        <v>454150</v>
       </c>
       <c r="R23" t="n">
-        <v>6991906</v>
+        <v>6991620</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,6 +3012,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3033,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124713188</v>
+        <v>124714580</v>
       </c>
       <c r="B24" t="n">
-        <v>82597</v>
+        <v>74892</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3045,25 +3055,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>492</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3073,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454120</v>
+        <v>454124</v>
       </c>
       <c r="R24" t="n">
-        <v>6991707</v>
+        <v>6991906</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3135,10 +3145,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124712828</v>
+        <v>124713188</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3151,39 +3161,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454150</v>
+        <v>454120</v>
       </c>
       <c r="R25" t="n">
-        <v>6991620</v>
+        <v>6991707</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,11 +3221,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4985,10 +4985,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124756701</v>
+        <v>124753594</v>
       </c>
       <c r="B42" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5001,34 +5001,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454115</v>
+        <v>454351</v>
       </c>
       <c r="R42" t="n">
-        <v>6991653</v>
+        <v>6991627</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5058,19 +5058,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>17:09</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>17:09</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5085,22 +5080,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124753594</v>
+        <v>124756701</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5113,34 +5108,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454351</v>
+        <v>454115</v>
       </c>
       <c r="R43" t="n">
-        <v>6991627</v>
+        <v>6991653</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5170,14 +5165,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5192,12 +5192,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5769,10 +5769,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124756693</v>
+        <v>124753572</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5785,34 +5785,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454196</v>
+        <v>454156</v>
       </c>
       <c r="R49" t="n">
-        <v>6991703</v>
+        <v>6991902</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5842,19 +5842,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>18:12</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>18:12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5869,22 +5859,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124753572</v>
+        <v>124756693</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5897,34 +5887,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454156</v>
+        <v>454196</v>
       </c>
       <c r="R50" t="n">
-        <v>6991902</v>
+        <v>6991703</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5954,9 +5944,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5971,12 +5971,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124716113</v>
+        <v>124716123</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454311</v>
+        <v>454310</v>
       </c>
       <c r="R2" t="n">
-        <v>6991632</v>
+        <v>6991630</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124713829</v>
+        <v>124716366</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454078</v>
+        <v>454349</v>
       </c>
       <c r="R3" t="n">
-        <v>6991761</v>
+        <v>6991623</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124715903</v>
+        <v>124712037</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454272</v>
+        <v>454053</v>
       </c>
       <c r="R4" t="n">
-        <v>6991636</v>
+        <v>6991664</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,11 +975,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124716162</v>
+        <v>124715043</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,39 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454310</v>
+        <v>454203</v>
       </c>
       <c r="R5" t="n">
-        <v>6991630</v>
+        <v>6991872</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,11 +1077,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rinfhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124716366</v>
+        <v>124714230</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454349</v>
+        <v>454102</v>
       </c>
       <c r="R6" t="n">
-        <v>6991623</v>
+        <v>6991834</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124714283</v>
+        <v>124714580</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>74892</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454102</v>
+        <v>454124</v>
       </c>
       <c r="R7" t="n">
-        <v>6991834</v>
+        <v>6991906</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124713664</v>
+        <v>124716063</v>
       </c>
       <c r="B8" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,34 +1323,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454129</v>
+        <v>454289</v>
       </c>
       <c r="R8" t="n">
-        <v>6991741</v>
+        <v>6991647</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124714230</v>
+        <v>124714299</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>82597</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1531,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124714299</v>
+        <v>124713188</v>
       </c>
       <c r="B10" t="n">
         <v>82597</v>
@@ -1571,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454102</v>
+        <v>454120</v>
       </c>
       <c r="R10" t="n">
-        <v>6991834</v>
+        <v>6991707</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124712512</v>
+        <v>124713664</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,39 +1639,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454093</v>
+        <v>454129</v>
       </c>
       <c r="R11" t="n">
-        <v>6991632</v>
+        <v>6991741</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124711120</v>
+        <v>124712085</v>
       </c>
       <c r="B12" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,34 +1741,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454041</v>
+        <v>454054</v>
       </c>
       <c r="R12" t="n">
-        <v>6991635</v>
+        <v>6991662</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,6 +1806,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124712037</v>
+        <v>124714283</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454053</v>
+        <v>454102</v>
       </c>
       <c r="R13" t="n">
-        <v>6991664</v>
+        <v>6991834</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124714775</v>
+        <v>124712828</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,34 +1955,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454161</v>
+        <v>454150</v>
       </c>
       <c r="R14" t="n">
-        <v>6991910</v>
+        <v>6991620</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,6 +2020,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124712085</v>
+        <v>124715903</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2087,19 +2087,19 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454054</v>
+        <v>454272</v>
       </c>
       <c r="R15" t="n">
-        <v>6991662</v>
+        <v>6991636</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124712610</v>
+        <v>124713617</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>79851</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,43 +2175,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454099</v>
+        <v>454129</v>
       </c>
       <c r="R16" t="n">
-        <v>6991631</v>
+        <v>6991741</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,11 +2239,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124716063</v>
+        <v>124712709</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,39 +2281,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454289</v>
+        <v>454108</v>
       </c>
       <c r="R17" t="n">
-        <v>6991647</v>
+        <v>6991616</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,11 +2341,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124713606</v>
+        <v>124711120</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>78889</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2427,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454129</v>
+        <v>454041</v>
       </c>
       <c r="R18" t="n">
-        <v>6991741</v>
+        <v>6991635</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,7 +2469,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124714894</v>
+        <v>124712512</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2525,7 +2505,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2534,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454168</v>
+        <v>454093</v>
       </c>
       <c r="R19" t="n">
-        <v>6991883</v>
+        <v>6991632</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124715915</v>
+        <v>124715943</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2646,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454272</v>
+        <v>454281</v>
       </c>
       <c r="R20" t="n">
-        <v>6991637</v>
+        <v>6991629</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2713,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124716073</v>
+        <v>124712610</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2725,42 +2705,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454289</v>
+        <v>454099</v>
       </c>
       <c r="R21" t="n">
-        <v>6991650</v>
+        <v>6991631</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,6 +2774,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2931,7 +2917,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124712828</v>
+        <v>124716113</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2972,14 +2958,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454150</v>
+        <v>454311</v>
       </c>
       <c r="R23" t="n">
-        <v>6991620</v>
+        <v>6991632</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124714580</v>
+        <v>124714775</v>
       </c>
       <c r="B24" t="n">
-        <v>74892</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,25 +3041,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>492</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454124</v>
+        <v>454161</v>
       </c>
       <c r="R24" t="n">
-        <v>6991906</v>
+        <v>6991910</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3145,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124713188</v>
+        <v>124713829</v>
       </c>
       <c r="B25" t="n">
-        <v>82597</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3161,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3185,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454120</v>
+        <v>454078</v>
       </c>
       <c r="R25" t="n">
-        <v>6991707</v>
+        <v>6991761</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3247,7 +3233,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124715943</v>
+        <v>124715915</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3292,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454281</v>
+        <v>454272</v>
       </c>
       <c r="R26" t="n">
-        <v>6991629</v>
+        <v>6991637</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3359,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124712709</v>
+        <v>124716073</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3371,38 +3357,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454108</v>
+        <v>454289</v>
       </c>
       <c r="R27" t="n">
-        <v>6991616</v>
+        <v>6991650</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3461,10 +3451,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124715043</v>
+        <v>124713606</v>
       </c>
       <c r="B28" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3477,21 +3467,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3501,10 +3491,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454203</v>
+        <v>454129</v>
       </c>
       <c r="R28" t="n">
-        <v>6991872</v>
+        <v>6991741</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3563,10 +3553,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124713617</v>
+        <v>124714894</v>
       </c>
       <c r="B29" t="n">
-        <v>79851</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3575,38 +3565,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454129</v>
+        <v>454168</v>
       </c>
       <c r="R29" t="n">
-        <v>6991741</v>
+        <v>6991883</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,6 +3634,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3665,10 +3665,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124753589</v>
+        <v>124753572</v>
       </c>
       <c r="B30" t="n">
-        <v>91700</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3677,25 +3677,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454148</v>
+        <v>454156</v>
       </c>
       <c r="R30" t="n">
-        <v>6991844</v>
+        <v>6991902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3767,7 +3767,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124753597</v>
+        <v>124753598</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454208</v>
+        <v>454169</v>
       </c>
       <c r="R31" t="n">
-        <v>6991866</v>
+        <v>6991914</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3874,10 +3874,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124753600</v>
+        <v>124753589</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>91700</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3886,25 +3886,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454147</v>
+        <v>454148</v>
       </c>
       <c r="R32" t="n">
-        <v>6991908</v>
+        <v>6991844</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,11 +3950,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3981,10 +3976,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124756691</v>
+        <v>124756702</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3993,50 +3988,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454339</v>
+        <v>454100</v>
       </c>
       <c r="R33" t="n">
-        <v>6991639</v>
+        <v>6991668</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4068,7 +4051,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4078,12 +4061,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Min antal</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4092,7 +4070,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4111,7 +4088,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124753596</v>
+        <v>124753593</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4151,10 +4128,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454245</v>
+        <v>454406</v>
       </c>
       <c r="R34" t="n">
-        <v>6991630</v>
+        <v>6991545</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4191,7 +4168,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4333,10 +4310,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124753603</v>
+        <v>124756692</v>
       </c>
       <c r="B36" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4345,38 +4322,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454234</v>
+        <v>454256</v>
       </c>
       <c r="R36" t="n">
-        <v>6991643</v>
+        <v>6991683</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4406,9 +4383,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4423,19 +4410,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124756702</v>
+        <v>124756706</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4475,10 +4462,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454100</v>
+        <v>454071</v>
       </c>
       <c r="R37" t="n">
-        <v>6991668</v>
+        <v>6991672</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4510,7 +4497,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4520,7 +4507,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4547,7 +4534,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124753602</v>
+        <v>124753594</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4587,10 +4574,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454105</v>
+        <v>454351</v>
       </c>
       <c r="R38" t="n">
-        <v>6991740</v>
+        <v>6991627</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4654,10 +4641,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124756703</v>
+        <v>124753574</v>
       </c>
       <c r="B39" t="n">
-        <v>77743</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4670,34 +4657,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454100</v>
+        <v>454086</v>
       </c>
       <c r="R39" t="n">
-        <v>6991668</v>
+        <v>6991732</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4727,19 +4714,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>17:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4754,12 +4731,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4878,10 +4855,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124753601</v>
+        <v>124753603</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4890,25 +4867,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4918,10 +4895,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454103</v>
+        <v>454234</v>
       </c>
       <c r="R41" t="n">
-        <v>6991735</v>
+        <v>6991643</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4954,11 +4931,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4985,10 +4957,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124753594</v>
+        <v>124756703</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>77743</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5001,34 +4973,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454351</v>
+        <v>454100</v>
       </c>
       <c r="R42" t="n">
-        <v>6991627</v>
+        <v>6991668</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5058,14 +5030,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5080,22 +5057,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124756701</v>
+        <v>124753601</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5108,34 +5085,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454115</v>
+        <v>454103</v>
       </c>
       <c r="R43" t="n">
-        <v>6991653</v>
+        <v>6991735</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5165,19 +5142,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>17:09</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>17:09</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5192,19 +5164,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124756700</v>
+        <v>124756693</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5244,10 +5216,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454086</v>
+        <v>454196</v>
       </c>
       <c r="R44" t="n">
-        <v>6991750</v>
+        <v>6991703</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5279,7 +5251,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5289,7 +5261,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5316,10 +5288,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124756706</v>
+        <v>124756701</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5332,21 +5304,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5356,10 +5328,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454071</v>
+        <v>454115</v>
       </c>
       <c r="R45" t="n">
-        <v>6991672</v>
+        <v>6991653</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5391,7 +5363,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5401,7 +5373,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5769,10 +5741,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124753572</v>
+        <v>124753636</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5785,21 +5757,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5809,10 +5781,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454156</v>
+        <v>454089</v>
       </c>
       <c r="R49" t="n">
-        <v>6991902</v>
+        <v>6991655</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5871,10 +5843,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124756693</v>
+        <v>124753600</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5887,34 +5859,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454196</v>
+        <v>454147</v>
       </c>
       <c r="R50" t="n">
-        <v>6991703</v>
+        <v>6991908</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5944,19 +5916,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>18:12</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>18:12</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5971,22 +5938,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124753636</v>
+        <v>124756700</v>
       </c>
       <c r="B51" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5999,34 +5966,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454089</v>
+        <v>454086</v>
       </c>
       <c r="R51" t="n">
-        <v>6991655</v>
+        <v>6991750</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6056,9 +6023,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6073,19 +6050,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124753593</v>
+        <v>124753597</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -6125,10 +6102,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454406</v>
+        <v>454208</v>
       </c>
       <c r="R52" t="n">
-        <v>6991545</v>
+        <v>6991866</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6192,7 +6169,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124753598</v>
+        <v>124753602</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6232,10 +6209,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454169</v>
+        <v>454105</v>
       </c>
       <c r="R53" t="n">
-        <v>6991914</v>
+        <v>6991740</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6272,7 +6249,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6299,10 +6276,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124756692</v>
+        <v>124756691</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6311,38 +6288,50 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454256</v>
+        <v>454339</v>
       </c>
       <c r="R54" t="n">
-        <v>6991683</v>
+        <v>6991639</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6374,7 +6363,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6384,7 +6373,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Min antal</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6393,6 +6387,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6411,10 +6406,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124753574</v>
+        <v>124753596</v>
       </c>
       <c r="B55" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6427,21 +6422,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6451,10 +6446,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454086</v>
+        <v>454245</v>
       </c>
       <c r="R55" t="n">
-        <v>6991732</v>
+        <v>6991630</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6487,6 +6482,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124716123</v>
+        <v>124712828</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -711,19 +711,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454310</v>
+        <v>454150</v>
       </c>
       <c r="R2" t="n">
-        <v>6991630</v>
+        <v>6991620</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124716366</v>
+        <v>124713188</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454349</v>
+        <v>454120</v>
       </c>
       <c r="R3" t="n">
-        <v>6991623</v>
+        <v>6991707</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1001,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124715043</v>
+        <v>124715915</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454203</v>
+        <v>454272</v>
       </c>
       <c r="R5" t="n">
-        <v>6991872</v>
+        <v>6991637</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124714230</v>
+        <v>124715943</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,34 +1119,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454102</v>
+        <v>454281</v>
       </c>
       <c r="R6" t="n">
-        <v>6991834</v>
+        <v>6991629</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1184,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124716063</v>
+        <v>124714299</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,39 +1333,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454289</v>
+        <v>454102</v>
       </c>
       <c r="R8" t="n">
-        <v>6991647</v>
+        <v>6991834</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124714299</v>
+        <v>124716057</v>
       </c>
       <c r="B9" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,34 +1435,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454102</v>
+        <v>454290</v>
       </c>
       <c r="R9" t="n">
-        <v>6991834</v>
+        <v>6991649</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1500,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124713188</v>
+        <v>124714894</v>
       </c>
       <c r="B10" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,34 +1547,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454120</v>
+        <v>454168</v>
       </c>
       <c r="R10" t="n">
-        <v>6991707</v>
+        <v>6991883</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1612,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124713664</v>
+        <v>124716366</v>
       </c>
       <c r="B11" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,34 +1659,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454129</v>
+        <v>454349</v>
       </c>
       <c r="R11" t="n">
-        <v>6991741</v>
+        <v>6991623</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,6 +1724,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124712085</v>
+        <v>124714230</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,39 +1771,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454054</v>
+        <v>454102</v>
       </c>
       <c r="R12" t="n">
-        <v>6991662</v>
+        <v>6991834</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,11 +1831,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124714283</v>
+        <v>124711120</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>78889</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454102</v>
+        <v>454041</v>
       </c>
       <c r="R13" t="n">
-        <v>6991834</v>
+        <v>6991635</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124712828</v>
+        <v>124714775</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,39 +1975,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454150</v>
+        <v>454161</v>
       </c>
       <c r="R14" t="n">
-        <v>6991620</v>
+        <v>6991910</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,11 +2035,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124715903</v>
+        <v>124712085</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2087,19 +2097,19 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454272</v>
+        <v>454054</v>
       </c>
       <c r="R15" t="n">
-        <v>6991636</v>
+        <v>6991662</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124713617</v>
+        <v>124713664</v>
       </c>
       <c r="B16" t="n">
-        <v>79851</v>
+        <v>79892</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,25 +2185,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2265,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124712709</v>
+        <v>124715043</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454108</v>
+        <v>454203</v>
       </c>
       <c r="R17" t="n">
-        <v>6991616</v>
+        <v>6991872</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124711120</v>
+        <v>124716063</v>
       </c>
       <c r="B18" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,34 +2393,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454041</v>
+        <v>454289</v>
       </c>
       <c r="R18" t="n">
-        <v>6991635</v>
+        <v>6991647</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,6 +2458,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2581,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124715943</v>
+        <v>124716162</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2626,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454281</v>
+        <v>454310</v>
       </c>
       <c r="R20" t="n">
-        <v>6991629</v>
+        <v>6991630</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,7 +2686,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rinfhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124712610</v>
+        <v>124716073</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,43 +2725,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454099</v>
+        <v>454289</v>
       </c>
       <c r="R21" t="n">
-        <v>6991631</v>
+        <v>6991650</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,11 +2793,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,10 +2819,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124716057</v>
+        <v>124713606</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,39 +2835,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454290</v>
+        <v>454129</v>
       </c>
       <c r="R22" t="n">
-        <v>6991649</v>
+        <v>6991741</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2886,11 +2895,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3029,7 +3033,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124714775</v>
+        <v>124713829</v>
       </c>
       <c r="B24" t="n">
         <v>79891</v>
@@ -3069,10 +3073,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454161</v>
+        <v>454078</v>
       </c>
       <c r="R24" t="n">
-        <v>6991910</v>
+        <v>6991761</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,10 +3135,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124713829</v>
+        <v>124712709</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3147,21 +3151,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3175,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454078</v>
+        <v>454108</v>
       </c>
       <c r="R25" t="n">
-        <v>6991761</v>
+        <v>6991616</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3233,10 +3237,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124715915</v>
+        <v>124714283</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3249,39 +3253,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454272</v>
+        <v>454102</v>
       </c>
       <c r="R26" t="n">
-        <v>6991637</v>
+        <v>6991834</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,11 +3313,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,10 +3339,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124716073</v>
+        <v>124712610</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3357,42 +3351,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454289</v>
+        <v>454099</v>
       </c>
       <c r="R27" t="n">
-        <v>6991650</v>
+        <v>6991631</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,6 +3420,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3451,10 +3451,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124713606</v>
+        <v>124715903</v>
       </c>
       <c r="B28" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3467,34 +3467,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454129</v>
+        <v>454272</v>
       </c>
       <c r="R28" t="n">
-        <v>6991741</v>
+        <v>6991636</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,6 +3532,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3553,10 +3563,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124714894</v>
+        <v>124713617</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>79851</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3565,43 +3575,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454168</v>
+        <v>454129</v>
       </c>
       <c r="R29" t="n">
-        <v>6991883</v>
+        <v>6991741</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,11 +3639,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3665,10 +3665,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124753572</v>
+        <v>124756702</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3681,34 +3681,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454156</v>
+        <v>454100</v>
       </c>
       <c r="R30" t="n">
-        <v>6991902</v>
+        <v>6991668</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3738,9 +3738,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3755,22 +3765,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124753598</v>
+        <v>124753636</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3783,21 +3793,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3807,10 +3817,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454169</v>
+        <v>454089</v>
       </c>
       <c r="R31" t="n">
-        <v>6991914</v>
+        <v>6991655</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,11 +3853,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3874,10 +3879,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124753589</v>
+        <v>124756706</v>
       </c>
       <c r="B32" t="n">
-        <v>91700</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3886,38 +3891,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454148</v>
+        <v>454071</v>
       </c>
       <c r="R32" t="n">
-        <v>6991844</v>
+        <v>6991672</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3947,9 +3952,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3964,22 +3979,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124756702</v>
+        <v>124753600</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3992,34 +4007,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454100</v>
+        <v>454147</v>
       </c>
       <c r="R33" t="n">
-        <v>6991668</v>
+        <v>6991908</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4049,19 +4064,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>17:07</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4076,22 +4086,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124753593</v>
+        <v>124753574</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4104,21 +4114,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4128,10 +4138,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454406</v>
+        <v>454086</v>
       </c>
       <c r="R34" t="n">
-        <v>6991545</v>
+        <v>6991732</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4164,11 +4174,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4195,7 +4200,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124753590</v>
+        <v>124753597</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4229,24 +4234,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454096</v>
+        <v>454208</v>
       </c>
       <c r="R35" t="n">
-        <v>6991720</v>
+        <v>6991866</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,7 +4280,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Bohål 5m upp i död gran</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4310,10 +4307,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124756692</v>
+        <v>124756701</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4326,21 +4323,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4350,10 +4347,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454256</v>
+        <v>454115</v>
       </c>
       <c r="R36" t="n">
-        <v>6991683</v>
+        <v>6991653</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4385,7 +4382,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4395,7 +4392,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4422,7 +4419,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124756706</v>
+        <v>124756693</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4462,10 +4459,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454071</v>
+        <v>454196</v>
       </c>
       <c r="R37" t="n">
-        <v>6991672</v>
+        <v>6991703</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4497,7 +4494,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4507,7 +4504,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4534,7 +4531,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124753594</v>
+        <v>124753598</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4574,10 +4571,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454351</v>
+        <v>454169</v>
       </c>
       <c r="R38" t="n">
-        <v>6991627</v>
+        <v>6991914</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4614,7 +4611,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4641,7 +4638,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124753574</v>
+        <v>124753572</v>
       </c>
       <c r="B39" t="n">
         <v>91012</v>
@@ -4681,10 +4678,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454086</v>
+        <v>454156</v>
       </c>
       <c r="R39" t="n">
-        <v>6991732</v>
+        <v>6991902</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4743,10 +4740,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124756698</v>
+        <v>124753601</v>
       </c>
       <c r="B40" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4759,34 +4756,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454144</v>
+        <v>454103</v>
       </c>
       <c r="R40" t="n">
-        <v>6991886</v>
+        <v>6991735</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,19 +4813,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>17:48</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4843,22 +4835,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124753603</v>
+        <v>124756700</v>
       </c>
       <c r="B41" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4867,38 +4859,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454234</v>
+        <v>454086</v>
       </c>
       <c r="R41" t="n">
-        <v>6991643</v>
+        <v>6991750</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4928,9 +4920,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4945,22 +4947,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124756703</v>
+        <v>124753593</v>
       </c>
       <c r="B42" t="n">
-        <v>77743</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4973,34 +4975,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454100</v>
+        <v>454406</v>
       </c>
       <c r="R42" t="n">
-        <v>6991668</v>
+        <v>6991545</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5030,19 +5032,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>17:06</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5057,19 +5054,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124753601</v>
+        <v>124753594</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -5109,10 +5106,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454103</v>
+        <v>454351</v>
       </c>
       <c r="R43" t="n">
-        <v>6991735</v>
+        <v>6991627</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5176,10 +5173,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124756693</v>
+        <v>124753596</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5192,34 +5189,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454196</v>
+        <v>454245</v>
       </c>
       <c r="R44" t="n">
-        <v>6991703</v>
+        <v>6991630</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5249,19 +5246,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>18:12</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>18:12</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,22 +5268,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124756701</v>
+        <v>124753590</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5304,34 +5296,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454115</v>
+        <v>454096</v>
       </c>
       <c r="R45" t="n">
-        <v>6991653</v>
+        <v>6991720</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5361,19 +5361,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>17:09</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>17:09</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Bohål 5m upp i död gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5388,22 +5383,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124756709</v>
+        <v>124756691</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5412,38 +5407,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454040</v>
+        <v>454339</v>
       </c>
       <c r="R46" t="n">
-        <v>6991636</v>
+        <v>6991639</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5475,7 +5482,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5485,7 +5492,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Min antal</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5494,6 +5506,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5512,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124753573</v>
+        <v>124756703</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5528,34 +5541,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454135</v>
+        <v>454100</v>
       </c>
       <c r="R47" t="n">
-        <v>6991889</v>
+        <v>6991668</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5585,9 +5598,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5602,22 +5625,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124756697</v>
+        <v>124753603</v>
       </c>
       <c r="B48" t="n">
-        <v>74892</v>
+        <v>91705</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5630,34 +5653,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>492</v>
+        <v>67</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454177</v>
+        <v>454234</v>
       </c>
       <c r="R48" t="n">
-        <v>6991911</v>
+        <v>6991643</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5687,21 +5710,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5710,41 +5723,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124753636</v>
+        <v>124756697</v>
       </c>
       <c r="B49" t="n">
-        <v>91030</v>
+        <v>74892</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5753,38 +5751,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454089</v>
+        <v>454177</v>
       </c>
       <c r="R49" t="n">
-        <v>6991655</v>
+        <v>6991911</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5814,11 +5812,21 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5827,26 +5835,41 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124753600</v>
+        <v>124756698</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5859,34 +5882,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454147</v>
+        <v>454144</v>
       </c>
       <c r="R50" t="n">
-        <v>6991908</v>
+        <v>6991886</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5916,14 +5939,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5938,19 +5966,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124756700</v>
+        <v>124756692</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -5990,10 +6018,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454086</v>
+        <v>454256</v>
       </c>
       <c r="R51" t="n">
-        <v>6991750</v>
+        <v>6991683</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6025,7 +6053,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6035,7 +6063,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6062,7 +6090,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124753597</v>
+        <v>124753602</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -6102,10 +6130,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454208</v>
+        <v>454105</v>
       </c>
       <c r="R52" t="n">
-        <v>6991866</v>
+        <v>6991740</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6169,10 +6197,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124753602</v>
+        <v>124756709</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6185,34 +6213,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454105</v>
+        <v>454040</v>
       </c>
       <c r="R53" t="n">
-        <v>6991740</v>
+        <v>6991636</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6242,14 +6270,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6264,22 +6297,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124756691</v>
+        <v>124753589</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>91700</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6288,50 +6321,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454339</v>
+        <v>454148</v>
       </c>
       <c r="R54" t="n">
-        <v>6991639</v>
+        <v>6991844</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6361,55 +6382,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Min antal</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124753596</v>
+        <v>124753573</v>
       </c>
       <c r="B55" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6422,21 +6427,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6446,10 +6451,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454245</v>
+        <v>454135</v>
       </c>
       <c r="R55" t="n">
-        <v>6991630</v>
+        <v>6991889</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6482,11 +6487,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -3237,10 +3237,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124714283</v>
+        <v>124713617</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>79851</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3249,25 +3249,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454102</v>
+        <v>454129</v>
       </c>
       <c r="R26" t="n">
-        <v>6991834</v>
+        <v>6991741</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3339,10 +3339,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124712610</v>
+        <v>124714283</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3355,39 +3355,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454099</v>
+        <v>454102</v>
       </c>
       <c r="R27" t="n">
-        <v>6991631</v>
+        <v>6991834</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,11 +3415,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3451,7 +3441,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124715903</v>
+        <v>124712610</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3487,19 +3477,19 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454272</v>
+        <v>454099</v>
       </c>
       <c r="R28" t="n">
-        <v>6991636</v>
+        <v>6991631</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3563,10 +3553,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124713617</v>
+        <v>124715903</v>
       </c>
       <c r="B29" t="n">
-        <v>79851</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3575,38 +3565,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454129</v>
+        <v>454272</v>
       </c>
       <c r="R29" t="n">
-        <v>6991741</v>
+        <v>6991636</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,6 +3634,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4638,10 +4638,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124753572</v>
+        <v>124753601</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4654,21 +4654,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454156</v>
+        <v>454103</v>
       </c>
       <c r="R39" t="n">
-        <v>6991902</v>
+        <v>6991735</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4714,6 +4714,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4740,10 +4745,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124753601</v>
+        <v>124753572</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4756,21 +4761,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4780,10 +4785,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454103</v>
+        <v>454156</v>
       </c>
       <c r="R40" t="n">
-        <v>6991735</v>
+        <v>6991902</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,11 +4821,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124712828</v>
+        <v>124712037</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454150</v>
+        <v>454053</v>
       </c>
       <c r="R2" t="n">
-        <v>6991620</v>
+        <v>6991664</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124713188</v>
+        <v>124714299</v>
       </c>
       <c r="B3" t="n">
         <v>82597</v>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454120</v>
+        <v>454102</v>
       </c>
       <c r="R3" t="n">
-        <v>6991707</v>
+        <v>6991834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124712037</v>
+        <v>124716057</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454053</v>
+        <v>454290</v>
       </c>
       <c r="R4" t="n">
-        <v>6991664</v>
+        <v>6991649</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124715915</v>
+        <v>124712085</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1032,14 +1032,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454272</v>
+        <v>454054</v>
       </c>
       <c r="R5" t="n">
-        <v>6991637</v>
+        <v>6991662</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124715943</v>
+        <v>124712610</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1144,14 +1144,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454281</v>
+        <v>454099</v>
       </c>
       <c r="R6" t="n">
-        <v>6991629</v>
+        <v>6991631</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124714580</v>
+        <v>124716123</v>
       </c>
       <c r="B7" t="n">
-        <v>74892</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,38 +1227,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454124</v>
+        <v>454310</v>
       </c>
       <c r="R7" t="n">
-        <v>6991906</v>
+        <v>6991630</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,6 +1296,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124714299</v>
+        <v>124716366</v>
       </c>
       <c r="B8" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,34 +1343,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454102</v>
+        <v>454349</v>
       </c>
       <c r="R8" t="n">
-        <v>6991834</v>
+        <v>6991623</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1408,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1439,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124716057</v>
+        <v>124716063</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1455,7 +1475,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1464,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454290</v>
+        <v>454289</v>
       </c>
       <c r="R9" t="n">
-        <v>6991649</v>
+        <v>6991647</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124714894</v>
+        <v>124716073</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,43 +1563,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454168</v>
+        <v>454289</v>
       </c>
       <c r="R10" t="n">
-        <v>6991883</v>
+        <v>6991650</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,11 +1631,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124716366</v>
+        <v>124713829</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,39 +1673,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454349</v>
+        <v>454078</v>
       </c>
       <c r="R11" t="n">
-        <v>6991623</v>
+        <v>6991761</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,11 +1733,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124714230</v>
+        <v>124712512</v>
       </c>
       <c r="B12" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,34 +1775,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454102</v>
+        <v>454093</v>
       </c>
       <c r="R12" t="n">
-        <v>6991834</v>
+        <v>6991632</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,6 +1840,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124711120</v>
+        <v>124715903</v>
       </c>
       <c r="B13" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,34 +1887,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454041</v>
+        <v>454272</v>
       </c>
       <c r="R13" t="n">
-        <v>6991635</v>
+        <v>6991636</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,6 +1952,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124714775</v>
+        <v>124715915</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,34 +1999,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454161</v>
+        <v>454272</v>
       </c>
       <c r="R14" t="n">
-        <v>6991910</v>
+        <v>6991637</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,6 +2064,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124712085</v>
+        <v>124714230</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,39 +2111,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454054</v>
+        <v>454102</v>
       </c>
       <c r="R15" t="n">
-        <v>6991662</v>
+        <v>6991834</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,11 +2171,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124713664</v>
+        <v>124716113</v>
       </c>
       <c r="B16" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2189,34 +2213,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454129</v>
+        <v>454311</v>
       </c>
       <c r="R16" t="n">
-        <v>6991741</v>
+        <v>6991632</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,6 +2278,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2309,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124715043</v>
+        <v>124715943</v>
       </c>
       <c r="B17" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,34 +2325,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454203</v>
+        <v>454281</v>
       </c>
       <c r="R17" t="n">
-        <v>6991872</v>
+        <v>6991629</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,6 +2390,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124716063</v>
+        <v>124713606</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,39 +2437,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454289</v>
+        <v>454129</v>
       </c>
       <c r="R18" t="n">
-        <v>6991647</v>
+        <v>6991741</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2458,11 +2497,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,10 +2523,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124712512</v>
+        <v>124713188</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,39 +2539,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454093</v>
+        <v>454120</v>
       </c>
       <c r="R19" t="n">
-        <v>6991632</v>
+        <v>6991707</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2570,11 +2599,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,7 +2625,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124716162</v>
+        <v>124712828</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2637,19 +2661,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454310</v>
+        <v>454150</v>
       </c>
       <c r="R20" t="n">
-        <v>6991630</v>
+        <v>6991620</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,7 +2710,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rinfhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2713,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124716073</v>
+        <v>124714775</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2725,42 +2749,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454289</v>
+        <v>454161</v>
       </c>
       <c r="R21" t="n">
-        <v>6991650</v>
+        <v>6991910</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2819,10 +2839,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124713606</v>
+        <v>124714283</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2835,21 +2855,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2859,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454129</v>
+        <v>454102</v>
       </c>
       <c r="R22" t="n">
-        <v>6991741</v>
+        <v>6991834</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2921,10 +2941,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124716113</v>
+        <v>124713664</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2937,39 +2957,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454311</v>
+        <v>454129</v>
       </c>
       <c r="R23" t="n">
-        <v>6991632</v>
+        <v>6991741</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,11 +3017,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3033,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124713829</v>
+        <v>124715043</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3049,21 +3059,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3073,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454078</v>
+        <v>454203</v>
       </c>
       <c r="R24" t="n">
-        <v>6991761</v>
+        <v>6991872</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3135,10 +3145,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124712709</v>
+        <v>124713617</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>79851</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3147,25 +3157,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3175,10 +3185,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454108</v>
+        <v>454129</v>
       </c>
       <c r="R25" t="n">
-        <v>6991616</v>
+        <v>6991741</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,10 +3247,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124713617</v>
+        <v>124714894</v>
       </c>
       <c r="B26" t="n">
-        <v>79851</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3249,38 +3259,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454129</v>
+        <v>454168</v>
       </c>
       <c r="R26" t="n">
-        <v>6991741</v>
+        <v>6991883</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,6 +3328,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3339,7 +3359,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124714283</v>
+        <v>124712709</v>
       </c>
       <c r="B27" t="n">
         <v>91012</v>
@@ -3379,10 +3399,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454102</v>
+        <v>454108</v>
       </c>
       <c r="R27" t="n">
-        <v>6991834</v>
+        <v>6991616</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,10 +3461,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124712610</v>
+        <v>124711120</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3457,39 +3477,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454099</v>
+        <v>454041</v>
       </c>
       <c r="R28" t="n">
-        <v>6991631</v>
+        <v>6991635</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,11 +3537,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3553,10 +3563,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124715903</v>
+        <v>124714580</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>74892</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3565,43 +3575,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454272</v>
+        <v>454124</v>
       </c>
       <c r="R29" t="n">
-        <v>6991636</v>
+        <v>6991906</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,11 +3639,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3665,7 +3665,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124756702</v>
+        <v>124756700</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454100</v>
+        <v>454086</v>
       </c>
       <c r="R30" t="n">
-        <v>6991668</v>
+        <v>6991750</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3879,10 +3879,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124756706</v>
+        <v>124753597</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3895,34 +3895,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454071</v>
+        <v>454208</v>
       </c>
       <c r="R32" t="n">
-        <v>6991672</v>
+        <v>6991866</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3952,19 +3952,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>17:00</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3979,22 +3974,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124753600</v>
+        <v>124756693</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4007,34 +4002,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454147</v>
+        <v>454196</v>
       </c>
       <c r="R33" t="n">
-        <v>6991908</v>
+        <v>6991703</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4064,14 +4059,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4086,19 +4086,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124753574</v>
+        <v>124753572</v>
       </c>
       <c r="B34" t="n">
         <v>91012</v>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454086</v>
+        <v>454156</v>
       </c>
       <c r="R34" t="n">
-        <v>6991732</v>
+        <v>6991902</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4200,7 +4200,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124753597</v>
+        <v>124753596</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4240,10 +4240,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454208</v>
+        <v>454245</v>
       </c>
       <c r="R35" t="n">
-        <v>6991866</v>
+        <v>6991630</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4307,10 +4307,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124756701</v>
+        <v>124756691</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4319,38 +4319,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454115</v>
+        <v>454339</v>
       </c>
       <c r="R36" t="n">
-        <v>6991653</v>
+        <v>6991639</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4382,7 +4394,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4392,7 +4404,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Min antal</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4401,6 +4418,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4419,10 +4437,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124756693</v>
+        <v>124756709</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4435,21 +4453,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4459,10 +4477,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454196</v>
+        <v>454040</v>
       </c>
       <c r="R37" t="n">
-        <v>6991703</v>
+        <v>6991636</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4494,7 +4512,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4504,7 +4522,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4531,7 +4549,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124753598</v>
+        <v>124753600</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4571,10 +4589,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454169</v>
+        <v>454147</v>
       </c>
       <c r="R38" t="n">
-        <v>6991914</v>
+        <v>6991908</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4638,10 +4656,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124753601</v>
+        <v>124756701</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4654,34 +4672,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454103</v>
+        <v>454115</v>
       </c>
       <c r="R39" t="n">
-        <v>6991735</v>
+        <v>6991653</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4711,14 +4729,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4733,19 +4756,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124753572</v>
+        <v>124753574</v>
       </c>
       <c r="B40" t="n">
         <v>91012</v>
@@ -4785,10 +4808,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454156</v>
+        <v>454086</v>
       </c>
       <c r="R40" t="n">
-        <v>6991902</v>
+        <v>6991732</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4847,10 +4870,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124756700</v>
+        <v>124756697</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>74892</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4859,25 +4882,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4887,10 +4910,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454086</v>
+        <v>454177</v>
       </c>
       <c r="R41" t="n">
-        <v>6991750</v>
+        <v>6991911</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4922,7 +4945,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4932,7 +4955,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4943,6 +4966,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4959,7 +4997,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124753593</v>
+        <v>124753590</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -4993,16 +5031,24 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454406</v>
+        <v>454096</v>
       </c>
       <c r="R42" t="n">
-        <v>6991545</v>
+        <v>6991720</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5039,7 +5085,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Bohål 5m upp i död gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5066,7 +5112,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124753594</v>
+        <v>124753598</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -5106,10 +5152,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454351</v>
+        <v>454169</v>
       </c>
       <c r="R43" t="n">
-        <v>6991627</v>
+        <v>6991914</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5146,7 +5192,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5173,7 +5219,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124753596</v>
+        <v>124753602</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5213,10 +5259,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454245</v>
+        <v>454105</v>
       </c>
       <c r="R44" t="n">
-        <v>6991630</v>
+        <v>6991740</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5253,7 +5299,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5280,10 +5326,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124753590</v>
+        <v>124756702</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5296,42 +5342,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454096</v>
+        <v>454100</v>
       </c>
       <c r="R45" t="n">
-        <v>6991720</v>
+        <v>6991668</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5361,14 +5399,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Bohål 5m upp i död gran</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,22 +5426,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124756691</v>
+        <v>124753589</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>91700</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5407,50 +5450,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454339</v>
+        <v>454148</v>
       </c>
       <c r="R46" t="n">
-        <v>6991639</v>
+        <v>6991844</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5480,55 +5511,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Min antal</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124756703</v>
+        <v>124753593</v>
       </c>
       <c r="B47" t="n">
-        <v>77743</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5541,34 +5556,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454100</v>
+        <v>454406</v>
       </c>
       <c r="R47" t="n">
-        <v>6991668</v>
+        <v>6991545</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5598,19 +5613,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>17:06</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5625,22 +5635,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124753603</v>
+        <v>124753573</v>
       </c>
       <c r="B48" t="n">
-        <v>91705</v>
+        <v>91012</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5649,25 +5659,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5677,10 +5687,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454234</v>
+        <v>454135</v>
       </c>
       <c r="R48" t="n">
-        <v>6991643</v>
+        <v>6991889</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5739,10 +5749,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124756697</v>
+        <v>124753603</v>
       </c>
       <c r="B49" t="n">
-        <v>74892</v>
+        <v>91705</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5755,34 +5765,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>492</v>
+        <v>67</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454177</v>
+        <v>454234</v>
       </c>
       <c r="R49" t="n">
-        <v>6991911</v>
+        <v>6991643</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5812,21 +5822,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5835,41 +5835,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124756698</v>
+        <v>124756703</v>
       </c>
       <c r="B50" t="n">
-        <v>82597</v>
+        <v>77743</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5882,21 +5867,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>228579</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5906,10 +5891,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454144</v>
+        <v>454100</v>
       </c>
       <c r="R50" t="n">
-        <v>6991886</v>
+        <v>6991668</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5941,7 +5926,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5951,7 +5936,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5978,10 +5963,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124756692</v>
+        <v>124753601</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5994,34 +5979,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454256</v>
+        <v>454103</v>
       </c>
       <c r="R51" t="n">
-        <v>6991683</v>
+        <v>6991735</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6051,19 +6036,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>18:19</t>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6078,19 +6058,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124753602</v>
+        <v>124753594</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -6130,10 +6110,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454105</v>
+        <v>454351</v>
       </c>
       <c r="R52" t="n">
-        <v>6991740</v>
+        <v>6991627</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6197,10 +6177,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124756709</v>
+        <v>124756692</v>
       </c>
       <c r="B53" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6213,21 +6193,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6237,10 +6217,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454040</v>
+        <v>454256</v>
       </c>
       <c r="R53" t="n">
-        <v>6991636</v>
+        <v>6991683</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6272,7 +6252,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6282,7 +6262,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6309,10 +6289,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124753589</v>
+        <v>124756698</v>
       </c>
       <c r="B54" t="n">
-        <v>91700</v>
+        <v>82597</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6321,38 +6301,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454148</v>
+        <v>454144</v>
       </c>
       <c r="R54" t="n">
-        <v>6991844</v>
+        <v>6991886</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6382,9 +6362,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6399,22 +6389,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124753573</v>
+        <v>124756706</v>
       </c>
       <c r="B55" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6427,34 +6417,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454135</v>
+        <v>454071</v>
       </c>
       <c r="R55" t="n">
-        <v>6991889</v>
+        <v>6991672</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6484,9 +6474,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6501,12 +6501,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124712037</v>
+        <v>124712085</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454053</v>
+        <v>454054</v>
       </c>
       <c r="R2" t="n">
-        <v>6991664</v>
+        <v>6991662</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124716057</v>
+        <v>124714230</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454290</v>
+        <v>454102</v>
       </c>
       <c r="R4" t="n">
-        <v>6991649</v>
+        <v>6991834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124712085</v>
+        <v>124716057</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1027,19 +1027,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454054</v>
+        <v>454290</v>
       </c>
       <c r="R5" t="n">
-        <v>6991662</v>
+        <v>6991649</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124712610</v>
+        <v>124711120</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454099</v>
+        <v>454041</v>
       </c>
       <c r="R6" t="n">
-        <v>6991631</v>
+        <v>6991635</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124716123</v>
+        <v>124712828</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1251,19 +1241,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454310</v>
+        <v>454150</v>
       </c>
       <c r="R7" t="n">
-        <v>6991630</v>
+        <v>6991620</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124716366</v>
+        <v>124715903</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1372,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454349</v>
+        <v>454272</v>
       </c>
       <c r="R8" t="n">
-        <v>6991623</v>
+        <v>6991636</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1551,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124716073</v>
+        <v>124713664</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>79892</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,42 +1553,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454289</v>
+        <v>454129</v>
       </c>
       <c r="R10" t="n">
-        <v>6991650</v>
+        <v>6991741</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1657,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124713829</v>
+        <v>124712610</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,34 +1659,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454078</v>
+        <v>454099</v>
       </c>
       <c r="R11" t="n">
-        <v>6991761</v>
+        <v>6991631</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,6 +1724,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124712512</v>
+        <v>124714894</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1795,7 +1791,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1804,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454093</v>
+        <v>454168</v>
       </c>
       <c r="R12" t="n">
-        <v>6991632</v>
+        <v>6991883</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124715903</v>
+        <v>124714283</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,39 +1883,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454272</v>
+        <v>454102</v>
       </c>
       <c r="R13" t="n">
-        <v>6991636</v>
+        <v>6991834</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,11 +1943,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124715915</v>
+        <v>124714580</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>74892</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,43 +1981,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454272</v>
+        <v>454124</v>
       </c>
       <c r="R14" t="n">
-        <v>6991637</v>
+        <v>6991906</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,11 +2045,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124714230</v>
+        <v>124713617</v>
       </c>
       <c r="B15" t="n">
-        <v>91299</v>
+        <v>79851</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2107,25 +2083,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2135,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454102</v>
+        <v>454129</v>
       </c>
       <c r="R15" t="n">
-        <v>6991834</v>
+        <v>6991741</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2197,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124716113</v>
+        <v>124715943</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2233,7 +2209,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2242,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454311</v>
+        <v>454281</v>
       </c>
       <c r="R16" t="n">
-        <v>6991632</v>
+        <v>6991629</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2309,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124715943</v>
+        <v>124715043</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2325,39 +2301,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454281</v>
+        <v>454203</v>
       </c>
       <c r="R17" t="n">
-        <v>6991629</v>
+        <v>6991872</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2390,11 +2361,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2421,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124713606</v>
+        <v>124712709</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2437,21 +2403,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2461,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454129</v>
+        <v>454108</v>
       </c>
       <c r="R18" t="n">
-        <v>6991741</v>
+        <v>6991616</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2523,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124713188</v>
+        <v>124716113</v>
       </c>
       <c r="B19" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2539,34 +2505,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454120</v>
+        <v>454311</v>
       </c>
       <c r="R19" t="n">
-        <v>6991707</v>
+        <v>6991632</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,6 +2570,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124712828</v>
+        <v>124712512</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2661,7 +2637,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2670,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454150</v>
+        <v>454093</v>
       </c>
       <c r="R20" t="n">
-        <v>6991620</v>
+        <v>6991632</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2737,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124714775</v>
+        <v>124716162</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2753,34 +2729,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454161</v>
+        <v>454310</v>
       </c>
       <c r="R21" t="n">
-        <v>6991910</v>
+        <v>6991630</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2813,6 +2794,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rinfhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124714283</v>
+        <v>124715915</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2855,34 +2841,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454102</v>
+        <v>454272</v>
       </c>
       <c r="R22" t="n">
-        <v>6991834</v>
+        <v>6991637</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,6 +2906,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2941,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124713664</v>
+        <v>124713188</v>
       </c>
       <c r="B23" t="n">
-        <v>79892</v>
+        <v>82597</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2957,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2981,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454129</v>
+        <v>454120</v>
       </c>
       <c r="R23" t="n">
-        <v>6991741</v>
+        <v>6991707</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124715043</v>
+        <v>124712037</v>
       </c>
       <c r="B24" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3059,21 +3055,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454203</v>
+        <v>454053</v>
       </c>
       <c r="R24" t="n">
-        <v>6991872</v>
+        <v>6991664</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3145,10 +3141,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124713617</v>
+        <v>124716073</v>
       </c>
       <c r="B25" t="n">
-        <v>79851</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3157,38 +3153,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454129</v>
+        <v>454289</v>
       </c>
       <c r="R25" t="n">
-        <v>6991741</v>
+        <v>6991650</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3247,7 +3247,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124714894</v>
+        <v>124716366</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3288,14 +3288,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454168</v>
+        <v>454349</v>
       </c>
       <c r="R26" t="n">
-        <v>6991883</v>
+        <v>6991623</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3359,10 +3359,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124712709</v>
+        <v>124714775</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3375,21 +3375,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454108</v>
+        <v>454161</v>
       </c>
       <c r="R27" t="n">
-        <v>6991616</v>
+        <v>6991910</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124711120</v>
+        <v>124713606</v>
       </c>
       <c r="B28" t="n">
-        <v>78889</v>
+        <v>79891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454041</v>
+        <v>454129</v>
       </c>
       <c r="R28" t="n">
-        <v>6991635</v>
+        <v>6991741</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3563,10 +3563,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124714580</v>
+        <v>124713829</v>
       </c>
       <c r="B29" t="n">
-        <v>74892</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3575,25 +3575,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>492</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3603,10 +3603,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454124</v>
+        <v>454078</v>
       </c>
       <c r="R29" t="n">
-        <v>6991906</v>
+        <v>6991761</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124756700</v>
+        <v>124753572</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3681,34 +3681,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454086</v>
+        <v>454156</v>
       </c>
       <c r="R30" t="n">
-        <v>6991750</v>
+        <v>6991902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3738,19 +3738,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3765,22 +3755,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124753636</v>
+        <v>124756693</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3793,34 +3783,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454089</v>
+        <v>454196</v>
       </c>
       <c r="R31" t="n">
-        <v>6991655</v>
+        <v>6991703</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3850,9 +3840,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3867,22 +3867,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124753597</v>
+        <v>124756692</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3895,34 +3895,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454208</v>
+        <v>454256</v>
       </c>
       <c r="R32" t="n">
-        <v>6991866</v>
+        <v>6991683</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3952,14 +3952,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3974,22 +3979,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124756693</v>
+        <v>124756697</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>74892</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3998,25 +4003,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4026,10 +4031,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454196</v>
+        <v>454177</v>
       </c>
       <c r="R33" t="n">
-        <v>6991703</v>
+        <v>6991911</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4061,7 +4066,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4071,7 +4076,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4082,6 +4087,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4098,10 +4118,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124753572</v>
+        <v>124756698</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>82597</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4114,34 +4134,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454156</v>
+        <v>454144</v>
       </c>
       <c r="R34" t="n">
-        <v>6991902</v>
+        <v>6991886</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4171,9 +4191,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4188,22 +4218,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124753596</v>
+        <v>124753636</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4216,21 +4246,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4240,10 +4270,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454245</v>
+        <v>454089</v>
       </c>
       <c r="R35" t="n">
-        <v>6991630</v>
+        <v>6991655</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4276,11 +4306,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4307,10 +4332,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124756691</v>
+        <v>124756703</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>77743</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4319,50 +4344,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454339</v>
+        <v>454100</v>
       </c>
       <c r="R36" t="n">
-        <v>6991639</v>
+        <v>6991668</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4394,7 +4407,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4404,12 +4417,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Min antal</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4418,7 +4426,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4437,10 +4444,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124756709</v>
+        <v>124753600</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4453,34 +4460,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454040</v>
+        <v>454147</v>
       </c>
       <c r="R37" t="n">
-        <v>6991636</v>
+        <v>6991908</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4510,19 +4517,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:56</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4537,19 +4539,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124753600</v>
+        <v>124753598</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4589,10 +4591,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454147</v>
+        <v>454169</v>
       </c>
       <c r="R38" t="n">
-        <v>6991908</v>
+        <v>6991914</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4656,10 +4658,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124756701</v>
+        <v>124753594</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4672,34 +4674,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454115</v>
+        <v>454351</v>
       </c>
       <c r="R39" t="n">
-        <v>6991653</v>
+        <v>6991627</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4729,19 +4731,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>17:09</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>17:09</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4756,22 +4753,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124753574</v>
+        <v>124756706</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4784,34 +4781,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454086</v>
+        <v>454071</v>
       </c>
       <c r="R40" t="n">
-        <v>6991732</v>
+        <v>6991672</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4841,9 +4838,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4858,22 +4865,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124756697</v>
+        <v>124753574</v>
       </c>
       <c r="B41" t="n">
-        <v>74892</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4882,38 +4889,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454177</v>
+        <v>454086</v>
       </c>
       <c r="R41" t="n">
-        <v>6991911</v>
+        <v>6991732</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4943,21 +4950,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4966,38 +4963,23 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124753590</v>
+        <v>124753601</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -5031,24 +5013,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454096</v>
+        <v>454103</v>
       </c>
       <c r="R42" t="n">
-        <v>6991720</v>
+        <v>6991735</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5085,7 +5059,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Bohål 5m upp i död gran</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5112,10 +5086,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124753598</v>
+        <v>124756709</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5128,34 +5102,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454169</v>
+        <v>454040</v>
       </c>
       <c r="R43" t="n">
-        <v>6991914</v>
+        <v>6991636</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5185,14 +5159,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5207,22 +5186,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124753602</v>
+        <v>124753573</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5235,21 +5214,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5259,10 +5238,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454105</v>
+        <v>454135</v>
       </c>
       <c r="R44" t="n">
-        <v>6991740</v>
+        <v>6991889</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5295,11 +5274,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5326,10 +5300,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124756702</v>
+        <v>124753589</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>91700</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5338,38 +5312,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454100</v>
+        <v>454148</v>
       </c>
       <c r="R45" t="n">
-        <v>6991668</v>
+        <v>6991844</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5399,19 +5373,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>17:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5426,22 +5390,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124753589</v>
+        <v>124756701</v>
       </c>
       <c r="B46" t="n">
-        <v>91700</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5450,38 +5414,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454148</v>
+        <v>454115</v>
       </c>
       <c r="R46" t="n">
-        <v>6991844</v>
+        <v>6991653</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5511,9 +5475,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5528,22 +5502,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124753593</v>
+        <v>124753603</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5552,25 +5526,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5580,10 +5554,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454406</v>
+        <v>454234</v>
       </c>
       <c r="R47" t="n">
-        <v>6991545</v>
+        <v>6991643</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5616,11 +5590,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5647,10 +5616,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124753573</v>
+        <v>124753590</v>
       </c>
       <c r="B48" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5663,34 +5632,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454135</v>
+        <v>454096</v>
       </c>
       <c r="R48" t="n">
-        <v>6991889</v>
+        <v>6991720</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5723,6 +5700,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Bohål 5m upp i död gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5749,10 +5731,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124753603</v>
+        <v>124756702</v>
       </c>
       <c r="B49" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5761,38 +5743,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454234</v>
+        <v>454100</v>
       </c>
       <c r="R49" t="n">
-        <v>6991643</v>
+        <v>6991668</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5822,9 +5804,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5839,22 +5831,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124756703</v>
+        <v>124753597</v>
       </c>
       <c r="B50" t="n">
-        <v>77743</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5867,34 +5859,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454100</v>
+        <v>454208</v>
       </c>
       <c r="R50" t="n">
-        <v>6991668</v>
+        <v>6991866</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5924,19 +5916,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>17:06</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5951,22 +5938,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124753601</v>
+        <v>124756700</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5979,34 +5966,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454103</v>
+        <v>454086</v>
       </c>
       <c r="R51" t="n">
-        <v>6991735</v>
+        <v>6991750</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6036,14 +6023,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6058,19 +6050,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124753594</v>
+        <v>124753602</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -6110,10 +6102,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454351</v>
+        <v>454105</v>
       </c>
       <c r="R52" t="n">
-        <v>6991627</v>
+        <v>6991740</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6177,10 +6169,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124756692</v>
+        <v>124756691</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6189,38 +6181,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454256</v>
+        <v>454339</v>
       </c>
       <c r="R53" t="n">
-        <v>6991683</v>
+        <v>6991639</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6252,7 +6256,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6262,7 +6266,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Min antal</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6271,6 +6280,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6289,10 +6299,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124756698</v>
+        <v>124753593</v>
       </c>
       <c r="B54" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6305,34 +6315,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454144</v>
+        <v>454406</v>
       </c>
       <c r="R54" t="n">
-        <v>6991886</v>
+        <v>6991545</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6362,19 +6372,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>17:48</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6389,22 +6394,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124756706</v>
+        <v>124753596</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6417,34 +6422,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454071</v>
+        <v>454245</v>
       </c>
       <c r="R55" t="n">
-        <v>6991672</v>
+        <v>6991630</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6474,19 +6479,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>17:00</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6501,12 +6501,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124712085</v>
+        <v>124714230</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454054</v>
+        <v>454102</v>
       </c>
       <c r="R2" t="n">
-        <v>6991662</v>
+        <v>6991834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124714299</v>
+        <v>124713829</v>
       </c>
       <c r="B3" t="n">
-        <v>82597</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454102</v>
+        <v>454078</v>
       </c>
       <c r="R3" t="n">
-        <v>6991834</v>
+        <v>6991761</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124714230</v>
+        <v>124714283</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -991,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124716057</v>
+        <v>124716123</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1027,7 +1017,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454290</v>
+        <v>454310</v>
       </c>
       <c r="R5" t="n">
-        <v>6991649</v>
+        <v>6991630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124711120</v>
+        <v>124715903</v>
       </c>
       <c r="B6" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,34 +1109,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454041</v>
+        <v>454272</v>
       </c>
       <c r="R6" t="n">
-        <v>6991635</v>
+        <v>6991636</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124712828</v>
+        <v>124714775</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,39 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454150</v>
+        <v>454161</v>
       </c>
       <c r="R7" t="n">
-        <v>6991620</v>
+        <v>6991910</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124715903</v>
+        <v>124714580</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>74892</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,43 +1319,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454272</v>
+        <v>454124</v>
       </c>
       <c r="R8" t="n">
-        <v>6991636</v>
+        <v>6991906</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124716063</v>
+        <v>124712610</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1470,14 +1450,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454289</v>
+        <v>454099</v>
       </c>
       <c r="R9" t="n">
-        <v>6991647</v>
+        <v>6991631</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124713664</v>
+        <v>124716073</v>
       </c>
       <c r="B10" t="n">
-        <v>79892</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,38 +1533,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454129</v>
+        <v>454289</v>
       </c>
       <c r="R10" t="n">
-        <v>6991741</v>
+        <v>6991650</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124712610</v>
+        <v>124713664</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,39 +1643,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454099</v>
+        <v>454129</v>
       </c>
       <c r="R11" t="n">
-        <v>6991631</v>
+        <v>6991741</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,11 +1703,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,7 +1729,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124714894</v>
+        <v>124716063</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1791,19 +1765,19 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454168</v>
+        <v>454289</v>
       </c>
       <c r="R12" t="n">
-        <v>6991883</v>
+        <v>6991647</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124714283</v>
+        <v>124715943</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,34 +1857,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454102</v>
+        <v>454281</v>
       </c>
       <c r="R13" t="n">
-        <v>6991834</v>
+        <v>6991629</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,6 +1922,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124714580</v>
+        <v>124713188</v>
       </c>
       <c r="B14" t="n">
-        <v>74892</v>
+        <v>82597</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1981,25 +1965,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>492</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,10 +1993,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454124</v>
+        <v>454120</v>
       </c>
       <c r="R14" t="n">
-        <v>6991906</v>
+        <v>6991707</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124713617</v>
+        <v>124712085</v>
       </c>
       <c r="B15" t="n">
-        <v>79851</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,38 +2067,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454129</v>
+        <v>454054</v>
       </c>
       <c r="R15" t="n">
-        <v>6991741</v>
+        <v>6991662</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,6 +2136,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2167,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124715943</v>
+        <v>124713617</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>79851</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,43 +2179,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454281</v>
+        <v>454129</v>
       </c>
       <c r="R16" t="n">
-        <v>6991629</v>
+        <v>6991741</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,11 +2243,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124712709</v>
+        <v>124716366</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,34 +2387,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454108</v>
+        <v>454349</v>
       </c>
       <c r="R18" t="n">
-        <v>6991616</v>
+        <v>6991623</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,6 +2452,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124716113</v>
+        <v>124714299</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,39 +2499,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454311</v>
+        <v>454102</v>
       </c>
       <c r="R19" t="n">
-        <v>6991632</v>
+        <v>6991834</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2570,11 +2559,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124712512</v>
+        <v>124712037</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2617,39 +2601,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454093</v>
+        <v>454053</v>
       </c>
       <c r="R20" t="n">
-        <v>6991632</v>
+        <v>6991664</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2682,11 +2661,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2713,7 +2687,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124716162</v>
+        <v>124715915</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2758,10 +2732,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454310</v>
+        <v>454272</v>
       </c>
       <c r="R21" t="n">
-        <v>6991630</v>
+        <v>6991637</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,7 +2772,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rinfhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2825,7 +2799,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124715915</v>
+        <v>124714894</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2861,19 +2835,19 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454272</v>
+        <v>454168</v>
       </c>
       <c r="R22" t="n">
-        <v>6991637</v>
+        <v>6991883</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2911,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124713188</v>
+        <v>124716057</v>
       </c>
       <c r="B23" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2953,34 +2927,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454120</v>
+        <v>454290</v>
       </c>
       <c r="R23" t="n">
-        <v>6991707</v>
+        <v>6991649</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3013,6 +2992,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3039,10 +3023,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124712037</v>
+        <v>124713606</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,21 +3039,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3079,10 +3063,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454053</v>
+        <v>454129</v>
       </c>
       <c r="R24" t="n">
-        <v>6991664</v>
+        <v>6991741</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124716073</v>
+        <v>124712709</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3153,42 +3137,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454289</v>
+        <v>454108</v>
       </c>
       <c r="R25" t="n">
-        <v>6991650</v>
+        <v>6991616</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3247,10 +3227,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124716366</v>
+        <v>124711120</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3263,39 +3243,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454349</v>
+        <v>454041</v>
       </c>
       <c r="R26" t="n">
-        <v>6991623</v>
+        <v>6991635</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3328,11 +3303,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3359,10 +3329,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124714775</v>
+        <v>124712512</v>
       </c>
       <c r="B27" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3375,34 +3345,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454161</v>
+        <v>454093</v>
       </c>
       <c r="R27" t="n">
-        <v>6991910</v>
+        <v>6991632</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,6 +3410,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3461,10 +3441,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124713606</v>
+        <v>124716113</v>
       </c>
       <c r="B28" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3477,34 +3457,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454129</v>
+        <v>454311</v>
       </c>
       <c r="R28" t="n">
-        <v>6991741</v>
+        <v>6991632</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,6 +3522,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3563,10 +3553,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124713829</v>
+        <v>124712828</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3579,34 +3569,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454078</v>
+        <v>454150</v>
       </c>
       <c r="R29" t="n">
-        <v>6991761</v>
+        <v>6991620</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,6 +3634,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3665,7 +3665,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124753572</v>
+        <v>124753574</v>
       </c>
       <c r="B30" t="n">
         <v>91012</v>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454156</v>
+        <v>454086</v>
       </c>
       <c r="R30" t="n">
-        <v>6991902</v>
+        <v>6991732</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124756693</v>
+        <v>124753601</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3783,34 +3783,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454196</v>
+        <v>454103</v>
       </c>
       <c r="R31" t="n">
-        <v>6991703</v>
+        <v>6991735</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3840,19 +3840,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>18:12</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>18:12</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3867,22 +3862,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124756692</v>
+        <v>124756701</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3895,21 +3890,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3919,10 +3914,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454256</v>
+        <v>454115</v>
       </c>
       <c r="R32" t="n">
-        <v>6991683</v>
+        <v>6991653</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3954,7 +3949,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3964,7 +3959,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3991,10 +3986,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124756697</v>
+        <v>124753600</v>
       </c>
       <c r="B33" t="n">
-        <v>74892</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4003,38 +3998,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454177</v>
+        <v>454147</v>
       </c>
       <c r="R33" t="n">
-        <v>6991911</v>
+        <v>6991908</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4064,19 +4059,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>17:55</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4087,41 +4077,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124756698</v>
+        <v>124756697</v>
       </c>
       <c r="B34" t="n">
-        <v>82597</v>
+        <v>74892</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4130,25 +4105,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>492</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4158,10 +4133,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454144</v>
+        <v>454177</v>
       </c>
       <c r="R34" t="n">
-        <v>6991886</v>
+        <v>6991911</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4193,7 +4168,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4203,7 +4178,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4214,6 +4189,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4230,10 +4220,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124753636</v>
+        <v>124753602</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4246,21 +4236,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4270,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454089</v>
+        <v>454105</v>
       </c>
       <c r="R35" t="n">
-        <v>6991655</v>
+        <v>6991740</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4306,6 +4296,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4332,10 +4327,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124756703</v>
+        <v>124753603</v>
       </c>
       <c r="B36" t="n">
-        <v>77743</v>
+        <v>91705</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4344,38 +4339,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>67</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454100</v>
+        <v>454234</v>
       </c>
       <c r="R36" t="n">
-        <v>6991668</v>
+        <v>6991643</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4405,19 +4400,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>17:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4432,22 +4417,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124753600</v>
+        <v>124756709</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4460,34 +4445,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454147</v>
+        <v>454040</v>
       </c>
       <c r="R37" t="n">
-        <v>6991908</v>
+        <v>6991636</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4517,14 +4502,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4539,19 +4529,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124753598</v>
+        <v>124753596</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4591,10 +4581,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454169</v>
+        <v>454245</v>
       </c>
       <c r="R38" t="n">
-        <v>6991914</v>
+        <v>6991630</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4631,7 +4621,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4658,7 +4648,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124753594</v>
+        <v>124753593</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -4698,10 +4688,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454351</v>
+        <v>454406</v>
       </c>
       <c r="R39" t="n">
-        <v>6991627</v>
+        <v>6991545</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4765,10 +4755,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124756706</v>
+        <v>124756703</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4781,21 +4771,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4805,10 +4795,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454071</v>
+        <v>454100</v>
       </c>
       <c r="R40" t="n">
-        <v>6991672</v>
+        <v>6991668</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4840,7 +4830,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4850,7 +4840,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4877,10 +4867,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124753574</v>
+        <v>124756693</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4893,34 +4883,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454086</v>
+        <v>454196</v>
       </c>
       <c r="R41" t="n">
-        <v>6991732</v>
+        <v>6991703</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4950,9 +4940,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4967,22 +4967,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124753601</v>
+        <v>124756706</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4995,34 +4995,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454103</v>
+        <v>454071</v>
       </c>
       <c r="R42" t="n">
-        <v>6991735</v>
+        <v>6991672</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5052,14 +5052,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5074,22 +5079,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124756709</v>
+        <v>124756702</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5102,21 +5107,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5126,10 +5131,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454040</v>
+        <v>454100</v>
       </c>
       <c r="R43" t="n">
-        <v>6991636</v>
+        <v>6991668</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5161,7 +5166,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5171,7 +5176,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5198,10 +5203,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124753573</v>
+        <v>124756691</v>
       </c>
       <c r="B44" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5210,38 +5215,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454135</v>
+        <v>454339</v>
       </c>
       <c r="R44" t="n">
-        <v>6991889</v>
+        <v>6991639</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5271,39 +5288,55 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Min antal</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124753589</v>
+        <v>124756700</v>
       </c>
       <c r="B45" t="n">
-        <v>91700</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5312,38 +5345,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454148</v>
+        <v>454086</v>
       </c>
       <c r="R45" t="n">
-        <v>6991844</v>
+        <v>6991750</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5373,9 +5406,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5390,22 +5433,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124756701</v>
+        <v>124753598</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5418,34 +5461,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454115</v>
+        <v>454169</v>
       </c>
       <c r="R46" t="n">
-        <v>6991653</v>
+        <v>6991914</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5475,19 +5518,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>17:09</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>17:09</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5502,22 +5540,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124753603</v>
+        <v>124753594</v>
       </c>
       <c r="B47" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5526,25 +5564,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5554,10 +5592,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454234</v>
+        <v>454351</v>
       </c>
       <c r="R47" t="n">
-        <v>6991643</v>
+        <v>6991627</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5590,6 +5628,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5616,10 +5659,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124753590</v>
+        <v>124756698</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5632,42 +5675,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454096</v>
+        <v>454144</v>
       </c>
       <c r="R48" t="n">
-        <v>6991720</v>
+        <v>6991886</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5697,14 +5732,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Bohål 5m upp i död gran</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5719,19 +5759,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124756702</v>
+        <v>124756692</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5771,10 +5811,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454100</v>
+        <v>454256</v>
       </c>
       <c r="R49" t="n">
-        <v>6991668</v>
+        <v>6991683</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5806,7 +5846,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5816,7 +5856,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5843,7 +5883,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124753597</v>
+        <v>124753590</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -5877,16 +5917,24 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454208</v>
+        <v>454096</v>
       </c>
       <c r="R50" t="n">
-        <v>6991866</v>
+        <v>6991720</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5923,7 +5971,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Bohål 5m upp i död gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5950,10 +5998,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124756700</v>
+        <v>124753572</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5966,34 +6014,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454086</v>
+        <v>454156</v>
       </c>
       <c r="R51" t="n">
-        <v>6991750</v>
+        <v>6991902</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6023,19 +6071,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6050,22 +6088,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124753602</v>
+        <v>124753573</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6078,21 +6116,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6102,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454105</v>
+        <v>454135</v>
       </c>
       <c r="R52" t="n">
-        <v>6991740</v>
+        <v>6991889</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6138,11 +6176,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6169,10 +6202,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124756691</v>
+        <v>124753589</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>91700</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6181,50 +6214,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454339</v>
+        <v>454148</v>
       </c>
       <c r="R53" t="n">
-        <v>6991639</v>
+        <v>6991844</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6254,52 +6275,36 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Min antal</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124753593</v>
+        <v>124753597</v>
       </c>
       <c r="B54" t="n">
         <v>57513</v>
@@ -6339,10 +6344,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454406</v>
+        <v>454208</v>
       </c>
       <c r="R54" t="n">
-        <v>6991545</v>
+        <v>6991866</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6406,10 +6411,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124753596</v>
+        <v>124753636</v>
       </c>
       <c r="B55" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6422,21 +6427,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6446,10 +6451,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454245</v>
+        <v>454089</v>
       </c>
       <c r="R55" t="n">
-        <v>6991630</v>
+        <v>6991655</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6482,11 +6487,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124714230</v>
+        <v>124714580</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>74892</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>492</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454102</v>
+        <v>454124</v>
       </c>
       <c r="R2" t="n">
-        <v>6991834</v>
+        <v>6991906</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124713829</v>
+        <v>124714894</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454078</v>
+        <v>454168</v>
       </c>
       <c r="R3" t="n">
-        <v>6991761</v>
+        <v>6991883</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124714283</v>
+        <v>124713606</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454102</v>
+        <v>454129</v>
       </c>
       <c r="R4" t="n">
-        <v>6991834</v>
+        <v>6991741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124716123</v>
+        <v>124714775</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454310</v>
+        <v>454161</v>
       </c>
       <c r="R5" t="n">
-        <v>6991630</v>
+        <v>6991910</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124715903</v>
+        <v>124716123</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1129,7 +1129,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454272</v>
+        <v>454310</v>
       </c>
       <c r="R6" t="n">
-        <v>6991636</v>
+        <v>6991630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124714775</v>
+        <v>124714230</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454161</v>
+        <v>454102</v>
       </c>
       <c r="R7" t="n">
-        <v>6991910</v>
+        <v>6991834</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124714580</v>
+        <v>124713664</v>
       </c>
       <c r="B8" t="n">
-        <v>74892</v>
+        <v>79892</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>492</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454124</v>
+        <v>454129</v>
       </c>
       <c r="R8" t="n">
-        <v>6991906</v>
+        <v>6991741</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124712610</v>
+        <v>124716366</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1445,19 +1445,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454099</v>
+        <v>454349</v>
       </c>
       <c r="R9" t="n">
-        <v>6991631</v>
+        <v>6991623</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124716073</v>
+        <v>124715043</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,42 +1533,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454289</v>
+        <v>454203</v>
       </c>
       <c r="R10" t="n">
-        <v>6991650</v>
+        <v>6991872</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124713664</v>
+        <v>124713188</v>
       </c>
       <c r="B11" t="n">
-        <v>79892</v>
+        <v>82597</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454129</v>
+        <v>454120</v>
       </c>
       <c r="R11" t="n">
-        <v>6991741</v>
+        <v>6991707</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124716063</v>
+        <v>124712037</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1745,39 +1741,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454289</v>
+        <v>454053</v>
       </c>
       <c r="R12" t="n">
-        <v>6991647</v>
+        <v>6991664</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,11 +1801,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,7 +1827,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124715943</v>
+        <v>124716057</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1877,7 +1863,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1886,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454281</v>
+        <v>454290</v>
       </c>
       <c r="R13" t="n">
-        <v>6991629</v>
+        <v>6991649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124713188</v>
+        <v>124713829</v>
       </c>
       <c r="B14" t="n">
-        <v>82597</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1993,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454120</v>
+        <v>454078</v>
       </c>
       <c r="R14" t="n">
-        <v>6991707</v>
+        <v>6991761</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,7 +2041,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124712085</v>
+        <v>124715915</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2096,14 +2082,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454054</v>
+        <v>454272</v>
       </c>
       <c r="R15" t="n">
-        <v>6991662</v>
+        <v>6991637</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124713617</v>
+        <v>124712709</v>
       </c>
       <c r="B16" t="n">
-        <v>79851</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,25 +2165,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2207,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454129</v>
+        <v>454108</v>
       </c>
       <c r="R16" t="n">
-        <v>6991741</v>
+        <v>6991616</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124715043</v>
+        <v>124714283</v>
       </c>
       <c r="B17" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2285,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2309,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454203</v>
+        <v>454102</v>
       </c>
       <c r="R17" t="n">
-        <v>6991872</v>
+        <v>6991834</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124716366</v>
+        <v>124711120</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,39 +2373,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454349</v>
+        <v>454041</v>
       </c>
       <c r="R18" t="n">
-        <v>6991623</v>
+        <v>6991635</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,11 +2433,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124714299</v>
+        <v>124713617</v>
       </c>
       <c r="B19" t="n">
-        <v>82597</v>
+        <v>79851</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,25 +2471,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2523,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454102</v>
+        <v>454129</v>
       </c>
       <c r="R19" t="n">
-        <v>6991834</v>
+        <v>6991741</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2585,10 +2561,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124712037</v>
+        <v>124712512</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2601,34 +2577,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454053</v>
+        <v>454093</v>
       </c>
       <c r="R20" t="n">
-        <v>6991664</v>
+        <v>6991632</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,6 +2642,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2687,7 +2673,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124715915</v>
+        <v>124715903</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2723,7 +2709,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2735,7 +2721,7 @@
         <v>454272</v>
       </c>
       <c r="R21" t="n">
-        <v>6991637</v>
+        <v>6991636</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,7 +2785,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124714894</v>
+        <v>124712085</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2835,7 +2821,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2844,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454168</v>
+        <v>454054</v>
       </c>
       <c r="R22" t="n">
-        <v>6991883</v>
+        <v>6991662</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2911,7 +2897,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124716057</v>
+        <v>124716113</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2956,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454290</v>
+        <v>454311</v>
       </c>
       <c r="R23" t="n">
-        <v>6991649</v>
+        <v>6991632</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3023,10 +3009,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124713606</v>
+        <v>124716073</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3035,38 +3021,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454129</v>
+        <v>454289</v>
       </c>
       <c r="R24" t="n">
-        <v>6991741</v>
+        <v>6991650</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3125,10 +3115,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124712709</v>
+        <v>124716063</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3141,34 +3131,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454108</v>
+        <v>454289</v>
       </c>
       <c r="R25" t="n">
-        <v>6991616</v>
+        <v>6991647</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,6 +3196,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3227,10 +3227,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124711120</v>
+        <v>124712610</v>
       </c>
       <c r="B26" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3243,34 +3243,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454041</v>
+        <v>454099</v>
       </c>
       <c r="R26" t="n">
-        <v>6991635</v>
+        <v>6991631</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,6 +3308,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3329,7 +3339,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124712512</v>
+        <v>124712828</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3365,7 +3375,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3374,10 +3384,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454093</v>
+        <v>454150</v>
       </c>
       <c r="R27" t="n">
-        <v>6991632</v>
+        <v>6991620</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,10 +3451,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124716113</v>
+        <v>124714299</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3457,39 +3467,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454311</v>
+        <v>454102</v>
       </c>
       <c r="R28" t="n">
-        <v>6991632</v>
+        <v>6991834</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,11 +3527,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3553,7 +3553,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124712828</v>
+        <v>124715943</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3589,19 +3589,19 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454150</v>
+        <v>454281</v>
       </c>
       <c r="R29" t="n">
-        <v>6991620</v>
+        <v>6991629</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124714580</v>
+        <v>124715903</v>
       </c>
       <c r="B2" t="n">
-        <v>74892</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454124</v>
+        <v>454272</v>
       </c>
       <c r="R2" t="n">
-        <v>6991906</v>
+        <v>6991636</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124714894</v>
+        <v>124714775</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454168</v>
+        <v>454161</v>
       </c>
       <c r="R3" t="n">
-        <v>6991883</v>
+        <v>6991910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124713606</v>
+        <v>124715043</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454129</v>
+        <v>454203</v>
       </c>
       <c r="R4" t="n">
-        <v>6991741</v>
+        <v>6991872</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124714775</v>
+        <v>124716057</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454161</v>
+        <v>454290</v>
       </c>
       <c r="R5" t="n">
-        <v>6991910</v>
+        <v>6991649</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124716123</v>
+        <v>124713664</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454310</v>
+        <v>454129</v>
       </c>
       <c r="R6" t="n">
-        <v>6991630</v>
+        <v>6991741</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124714230</v>
+        <v>124712037</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454102</v>
+        <v>454053</v>
       </c>
       <c r="R7" t="n">
-        <v>6991834</v>
+        <v>6991664</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124713664</v>
+        <v>124716073</v>
       </c>
       <c r="B8" t="n">
-        <v>79892</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,38 +1319,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454129</v>
+        <v>454289</v>
       </c>
       <c r="R8" t="n">
-        <v>6991741</v>
+        <v>6991650</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124716366</v>
+        <v>124713188</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,39 +1429,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454349</v>
+        <v>454120</v>
       </c>
       <c r="R9" t="n">
-        <v>6991623</v>
+        <v>6991707</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1489,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124715043</v>
+        <v>124716063</v>
       </c>
       <c r="B10" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,34 +1531,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454203</v>
+        <v>454289</v>
       </c>
       <c r="R10" t="n">
-        <v>6991872</v>
+        <v>6991647</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1596,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124713188</v>
+        <v>124712085</v>
       </c>
       <c r="B11" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,34 +1643,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454120</v>
+        <v>454054</v>
       </c>
       <c r="R11" t="n">
-        <v>6991707</v>
+        <v>6991662</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,6 +1708,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124712037</v>
+        <v>124716113</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,34 +1755,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454053</v>
+        <v>454311</v>
       </c>
       <c r="R12" t="n">
-        <v>6991664</v>
+        <v>6991632</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,6 +1820,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124716057</v>
+        <v>124714299</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,39 +1867,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454290</v>
+        <v>454102</v>
       </c>
       <c r="R13" t="n">
-        <v>6991649</v>
+        <v>6991834</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1927,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,7 +2055,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124715915</v>
+        <v>124714894</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2077,19 +2091,19 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454272</v>
+        <v>454168</v>
       </c>
       <c r="R15" t="n">
-        <v>6991637</v>
+        <v>6991883</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,10 +2167,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124712709</v>
+        <v>124714230</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,21 +2183,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454108</v>
+        <v>454102</v>
       </c>
       <c r="R16" t="n">
-        <v>6991616</v>
+        <v>6991834</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2269,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124714283</v>
+        <v>124716162</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,34 +2285,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454102</v>
+        <v>454310</v>
       </c>
       <c r="R17" t="n">
-        <v>6991834</v>
+        <v>6991630</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,6 +2350,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rinfhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124711120</v>
+        <v>124714283</v>
       </c>
       <c r="B18" t="n">
-        <v>78889</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2373,21 +2397,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2397,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454041</v>
+        <v>454102</v>
       </c>
       <c r="R18" t="n">
-        <v>6991635</v>
+        <v>6991834</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2459,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124713617</v>
+        <v>124712709</v>
       </c>
       <c r="B19" t="n">
-        <v>79851</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2471,25 +2495,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2523,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454129</v>
+        <v>454108</v>
       </c>
       <c r="R19" t="n">
-        <v>6991741</v>
+        <v>6991616</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124712512</v>
+        <v>124714580</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>74892</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2573,43 +2597,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454093</v>
+        <v>454124</v>
       </c>
       <c r="R20" t="n">
-        <v>6991632</v>
+        <v>6991906</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,11 +2661,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2673,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124715903</v>
+        <v>124713617</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>79851</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2685,43 +2699,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454272</v>
+        <v>454129</v>
       </c>
       <c r="R21" t="n">
-        <v>6991636</v>
+        <v>6991741</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,11 +2763,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,7 +2789,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124712085</v>
+        <v>124712512</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2830,10 +2834,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454054</v>
+        <v>454093</v>
       </c>
       <c r="R22" t="n">
-        <v>6991662</v>
+        <v>6991632</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2897,7 +2901,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124716113</v>
+        <v>124716317</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2933,7 +2937,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2942,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454311</v>
+        <v>454349</v>
       </c>
       <c r="R23" t="n">
-        <v>6991632</v>
+        <v>6991623</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,10 +3013,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124716073</v>
+        <v>124713606</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3021,42 +3025,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454289</v>
+        <v>454129</v>
       </c>
       <c r="R24" t="n">
-        <v>6991650</v>
+        <v>6991741</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124716063</v>
+        <v>124715915</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454289</v>
+        <v>454272</v>
       </c>
       <c r="R25" t="n">
-        <v>6991647</v>
+        <v>6991637</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124712610</v>
+        <v>124715943</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3268,14 +3268,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454099</v>
+        <v>454281</v>
       </c>
       <c r="R26" t="n">
-        <v>6991631</v>
+        <v>6991629</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3451,10 +3451,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124714299</v>
+        <v>124711120</v>
       </c>
       <c r="B28" t="n">
-        <v>82597</v>
+        <v>78889</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3467,21 +3467,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454102</v>
+        <v>454041</v>
       </c>
       <c r="R28" t="n">
-        <v>6991834</v>
+        <v>6991635</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3553,7 +3553,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124715943</v>
+        <v>124712610</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3594,14 +3594,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454281</v>
+        <v>454099</v>
       </c>
       <c r="R29" t="n">
-        <v>6991629</v>
+        <v>6991631</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124753574</v>
+        <v>124753596</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3681,21 +3681,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454086</v>
+        <v>454245</v>
       </c>
       <c r="R30" t="n">
-        <v>6991732</v>
+        <v>6991630</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,6 +3741,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3767,10 +3772,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124753601</v>
+        <v>124756691</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3779,38 +3784,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454103</v>
+        <v>454339</v>
       </c>
       <c r="R31" t="n">
-        <v>6991735</v>
+        <v>6991639</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3840,14 +3857,24 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Min antal</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3856,28 +3883,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124756701</v>
+        <v>124756692</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3890,21 +3918,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3914,10 +3942,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454115</v>
+        <v>454256</v>
       </c>
       <c r="R32" t="n">
-        <v>6991653</v>
+        <v>6991683</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3949,7 +3977,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3959,7 +3987,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3986,7 +4014,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124753600</v>
+        <v>124753597</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -4026,10 +4054,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454147</v>
+        <v>454208</v>
       </c>
       <c r="R33" t="n">
-        <v>6991908</v>
+        <v>6991866</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4066,7 +4094,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4093,10 +4121,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124756697</v>
+        <v>124753594</v>
       </c>
       <c r="B34" t="n">
-        <v>74892</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4105,38 +4133,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454177</v>
+        <v>454351</v>
       </c>
       <c r="R34" t="n">
-        <v>6991911</v>
+        <v>6991627</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4166,19 +4194,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>17:55</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4189,41 +4212,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124753602</v>
+        <v>124756702</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4236,34 +4244,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454105</v>
+        <v>454100</v>
       </c>
       <c r="R35" t="n">
-        <v>6991740</v>
+        <v>6991668</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4293,14 +4301,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4315,22 +4328,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124753603</v>
+        <v>124756698</v>
       </c>
       <c r="B36" t="n">
-        <v>91705</v>
+        <v>82597</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4339,38 +4352,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>67</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454234</v>
+        <v>454144</v>
       </c>
       <c r="R36" t="n">
-        <v>6991643</v>
+        <v>6991886</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4400,9 +4413,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4417,19 +4440,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124756709</v>
+        <v>124753574</v>
       </c>
       <c r="B37" t="n">
         <v>91012</v>
@@ -4465,14 +4488,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454040</v>
+        <v>454086</v>
       </c>
       <c r="R37" t="n">
-        <v>6991636</v>
+        <v>6991732</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4502,19 +4525,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4529,22 +4542,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124753596</v>
+        <v>124753572</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4557,21 +4570,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4581,10 +4594,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454245</v>
+        <v>454156</v>
       </c>
       <c r="R38" t="n">
-        <v>6991630</v>
+        <v>6991902</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4617,11 +4630,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4648,10 +4656,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124753593</v>
+        <v>124753589</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>91700</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4660,25 +4668,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4688,10 +4696,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454406</v>
+        <v>454148</v>
       </c>
       <c r="R39" t="n">
-        <v>6991545</v>
+        <v>6991844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4724,11 +4732,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4755,10 +4758,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124756703</v>
+        <v>124753598</v>
       </c>
       <c r="B40" t="n">
-        <v>77743</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4771,34 +4774,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454100</v>
+        <v>454169</v>
       </c>
       <c r="R40" t="n">
-        <v>6991668</v>
+        <v>6991914</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4828,19 +4831,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>17:06</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4855,22 +4853,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124756693</v>
+        <v>124753600</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4883,34 +4881,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454196</v>
+        <v>454147</v>
       </c>
       <c r="R41" t="n">
-        <v>6991703</v>
+        <v>6991908</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4940,19 +4938,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>18:12</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>18:12</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4967,22 +4960,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124756706</v>
+        <v>124753573</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4995,34 +4988,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454071</v>
+        <v>454135</v>
       </c>
       <c r="R42" t="n">
-        <v>6991672</v>
+        <v>6991889</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5052,19 +5045,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>17:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5079,22 +5062,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124756702</v>
+        <v>124753593</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5107,34 +5090,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454100</v>
+        <v>454406</v>
       </c>
       <c r="R43" t="n">
-        <v>6991668</v>
+        <v>6991545</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5164,19 +5147,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>17:07</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5191,22 +5169,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124756691</v>
+        <v>124753602</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5215,50 +5193,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454339</v>
+        <v>454105</v>
       </c>
       <c r="R44" t="n">
-        <v>6991639</v>
+        <v>6991740</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5288,24 +5254,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Min antal</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5314,29 +5270,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124756700</v>
+        <v>124756701</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5349,21 +5304,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5373,10 +5328,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454086</v>
+        <v>454115</v>
       </c>
       <c r="R45" t="n">
-        <v>6991750</v>
+        <v>6991653</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5408,7 +5363,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5418,7 +5373,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5445,7 +5400,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124753598</v>
+        <v>124753590</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -5479,16 +5434,24 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454169</v>
+        <v>454096</v>
       </c>
       <c r="R46" t="n">
-        <v>6991914</v>
+        <v>6991720</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5525,7 +5488,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål 5m upp i död gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5552,10 +5515,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124753594</v>
+        <v>124756709</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5568,34 +5531,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454351</v>
+        <v>454040</v>
       </c>
       <c r="R47" t="n">
-        <v>6991627</v>
+        <v>6991636</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5625,14 +5588,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5647,22 +5615,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124756698</v>
+        <v>124756693</v>
       </c>
       <c r="B48" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5675,21 +5643,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5699,10 +5667,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454144</v>
+        <v>454196</v>
       </c>
       <c r="R48" t="n">
-        <v>6991886</v>
+        <v>6991703</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5734,7 +5702,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5744,7 +5712,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5771,7 +5739,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124756692</v>
+        <v>124756700</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5811,10 +5779,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454256</v>
+        <v>454086</v>
       </c>
       <c r="R49" t="n">
-        <v>6991683</v>
+        <v>6991750</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5846,7 +5814,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5856,7 +5824,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5883,10 +5851,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124753590</v>
+        <v>124756703</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>77743</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5899,42 +5867,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454096</v>
+        <v>454100</v>
       </c>
       <c r="R50" t="n">
-        <v>6991720</v>
+        <v>6991668</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5964,14 +5924,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Bohål 5m upp i död gran</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5986,22 +5951,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124753572</v>
+        <v>124756706</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6014,34 +5979,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454156</v>
+        <v>454071</v>
       </c>
       <c r="R51" t="n">
-        <v>6991902</v>
+        <v>6991672</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6071,9 +6036,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6088,22 +6063,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124753573</v>
+        <v>124753636</v>
       </c>
       <c r="B52" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,21 +6091,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6140,10 +6115,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454135</v>
+        <v>454089</v>
       </c>
       <c r="R52" t="n">
-        <v>6991889</v>
+        <v>6991655</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6202,10 +6177,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124753589</v>
+        <v>124753601</v>
       </c>
       <c r="B53" t="n">
-        <v>91700</v>
+        <v>57513</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6214,25 +6189,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6242,10 +6217,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454148</v>
+        <v>454103</v>
       </c>
       <c r="R53" t="n">
-        <v>6991844</v>
+        <v>6991735</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6278,6 +6253,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6304,10 +6284,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124753597</v>
+        <v>124756697</v>
       </c>
       <c r="B54" t="n">
-        <v>57513</v>
+        <v>74892</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6316,38 +6296,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454208</v>
+        <v>454177</v>
       </c>
       <c r="R54" t="n">
-        <v>6991866</v>
+        <v>6991911</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6377,14 +6357,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6395,26 +6380,41 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124753636</v>
+        <v>124753603</v>
       </c>
       <c r="B55" t="n">
-        <v>91030</v>
+        <v>91705</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6423,25 +6423,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>67</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6451,10 +6451,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454089</v>
+        <v>454234</v>
       </c>
       <c r="R55" t="n">
-        <v>6991655</v>
+        <v>6991643</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124714299</v>
+        <v>124713829</v>
       </c>
       <c r="B13" t="n">
-        <v>82597</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,21 +1867,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454102</v>
+        <v>454078</v>
       </c>
       <c r="R13" t="n">
-        <v>6991834</v>
+        <v>6991761</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124713829</v>
+        <v>124714894</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,34 +1969,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454078</v>
+        <v>454168</v>
       </c>
       <c r="R14" t="n">
-        <v>6991761</v>
+        <v>6991883</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,6 +2034,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2055,10 +2065,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124714894</v>
+        <v>124714299</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2071,39 +2081,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454168</v>
+        <v>454102</v>
       </c>
       <c r="R15" t="n">
-        <v>6991883</v>
+        <v>6991834</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,11 +2141,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3902,10 +3902,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124756692</v>
+        <v>124753597</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3918,34 +3918,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454256</v>
+        <v>454208</v>
       </c>
       <c r="R32" t="n">
-        <v>6991683</v>
+        <v>6991866</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3975,19 +3975,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>18:19</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4002,19 +3997,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124753597</v>
+        <v>124753594</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -4054,10 +4049,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454208</v>
+        <v>454351</v>
       </c>
       <c r="R33" t="n">
-        <v>6991866</v>
+        <v>6991627</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4121,10 +4116,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124753594</v>
+        <v>124756692</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4137,34 +4132,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454351</v>
+        <v>454256</v>
       </c>
       <c r="R34" t="n">
-        <v>6991627</v>
+        <v>6991683</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4194,14 +4189,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4216,12 +4216,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4972,10 +4972,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124753573</v>
+        <v>124753593</v>
       </c>
       <c r="B42" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4988,21 +4988,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454135</v>
+        <v>454406</v>
       </c>
       <c r="R42" t="n">
-        <v>6991889</v>
+        <v>6991545</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5048,6 +5048,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5074,10 +5079,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124753593</v>
+        <v>124753573</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5090,21 +5095,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5114,10 +5119,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454406</v>
+        <v>454135</v>
       </c>
       <c r="R43" t="n">
-        <v>6991545</v>
+        <v>6991889</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5150,11 +5155,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5288,10 +5288,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124756701</v>
+        <v>124753590</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5304,34 +5304,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454115</v>
+        <v>454096</v>
       </c>
       <c r="R45" t="n">
-        <v>6991653</v>
+        <v>6991720</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5361,19 +5369,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>17:09</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>17:09</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Bohål 5m upp i död gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5388,22 +5391,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124753590</v>
+        <v>124756701</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5416,42 +5419,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454096</v>
+        <v>454115</v>
       </c>
       <c r="R46" t="n">
-        <v>6991720</v>
+        <v>6991653</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5481,14 +5476,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Bohål 5m upp i död gran</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5503,12 +5503,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124753601</v>
+        <v>124756697</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>74892</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6189,38 +6189,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454103</v>
+        <v>454177</v>
       </c>
       <c r="R53" t="n">
-        <v>6991735</v>
+        <v>6991911</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6250,14 +6250,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6268,26 +6273,41 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124756697</v>
+        <v>124753603</v>
       </c>
       <c r="B54" t="n">
-        <v>74892</v>
+        <v>91705</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6300,34 +6320,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>492</v>
+        <v>67</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454177</v>
+        <v>454234</v>
       </c>
       <c r="R54" t="n">
-        <v>6991911</v>
+        <v>6991643</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6357,21 +6377,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6380,41 +6390,26 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124753603</v>
+        <v>124753601</v>
       </c>
       <c r="B55" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6423,25 +6418,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6451,10 +6446,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454234</v>
+        <v>454103</v>
       </c>
       <c r="R55" t="n">
-        <v>6991643</v>
+        <v>6991735</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6487,6 +6482,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124715903</v>
+        <v>124712709</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454272</v>
+        <v>454108</v>
       </c>
       <c r="R2" t="n">
-        <v>6991636</v>
+        <v>6991616</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124714775</v>
+        <v>124714580</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>74892</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454161</v>
+        <v>454124</v>
       </c>
       <c r="R3" t="n">
-        <v>6991910</v>
+        <v>6991906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124715043</v>
+        <v>124716366</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454203</v>
+        <v>454349</v>
       </c>
       <c r="R4" t="n">
-        <v>6991872</v>
+        <v>6991623</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124716057</v>
+        <v>124715943</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1027,7 +1027,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454290</v>
+        <v>454281</v>
       </c>
       <c r="R5" t="n">
-        <v>6991649</v>
+        <v>6991629</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124713664</v>
+        <v>124713606</v>
       </c>
       <c r="B6" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124712037</v>
+        <v>124714894</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454053</v>
+        <v>454168</v>
       </c>
       <c r="R7" t="n">
-        <v>6991664</v>
+        <v>6991883</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124716073</v>
+        <v>124712610</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,42 +1329,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454289</v>
+        <v>454099</v>
       </c>
       <c r="R8" t="n">
-        <v>6991650</v>
+        <v>6991631</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,6 +1398,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124713188</v>
+        <v>124714299</v>
       </c>
       <c r="B9" t="n">
         <v>82597</v>
@@ -1453,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454120</v>
+        <v>454102</v>
       </c>
       <c r="R9" t="n">
-        <v>6991707</v>
+        <v>6991834</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124716063</v>
+        <v>124714283</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,39 +1547,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454289</v>
+        <v>454102</v>
       </c>
       <c r="R10" t="n">
-        <v>6991647</v>
+        <v>6991834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,11 +1607,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1627,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124712085</v>
+        <v>124713664</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,39 +1649,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454054</v>
+        <v>454129</v>
       </c>
       <c r="R11" t="n">
-        <v>6991662</v>
+        <v>6991741</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1739,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124716113</v>
+        <v>124711120</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,39 +1751,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454311</v>
+        <v>454041</v>
       </c>
       <c r="R12" t="n">
-        <v>6991632</v>
+        <v>6991635</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,11 +1811,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124713829</v>
+        <v>124715915</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,34 +1853,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454078</v>
+        <v>454272</v>
       </c>
       <c r="R13" t="n">
-        <v>6991761</v>
+        <v>6991637</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,6 +1918,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1953,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124714894</v>
+        <v>124712512</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1989,7 +1985,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1998,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454168</v>
+        <v>454093</v>
       </c>
       <c r="R14" t="n">
-        <v>6991883</v>
+        <v>6991632</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2065,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124714299</v>
+        <v>124716162</v>
       </c>
       <c r="B15" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,34 +2077,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454102</v>
+        <v>454310</v>
       </c>
       <c r="R15" t="n">
-        <v>6991834</v>
+        <v>6991630</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,6 +2142,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rinfhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2167,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124714230</v>
+        <v>124712037</v>
       </c>
       <c r="B16" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,21 +2189,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2207,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454102</v>
+        <v>454053</v>
       </c>
       <c r="R16" t="n">
-        <v>6991834</v>
+        <v>6991664</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124716162</v>
+        <v>124715903</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2305,7 +2311,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2314,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454310</v>
+        <v>454272</v>
       </c>
       <c r="R17" t="n">
-        <v>6991630</v>
+        <v>6991636</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rinfhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2381,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124714283</v>
+        <v>124713188</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>82597</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,21 +2403,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2421,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454102</v>
+        <v>454120</v>
       </c>
       <c r="R18" t="n">
-        <v>6991834</v>
+        <v>6991707</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124712709</v>
+        <v>124715043</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2499,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2523,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454108</v>
+        <v>454203</v>
       </c>
       <c r="R19" t="n">
-        <v>6991616</v>
+        <v>6991872</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2585,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124714580</v>
+        <v>124716057</v>
       </c>
       <c r="B20" t="n">
-        <v>74892</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,38 +2603,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454124</v>
+        <v>454290</v>
       </c>
       <c r="R20" t="n">
-        <v>6991906</v>
+        <v>6991649</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,6 +2672,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2687,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124713617</v>
+        <v>124716073</v>
       </c>
       <c r="B21" t="n">
-        <v>79851</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2699,38 +2715,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454129</v>
+        <v>454289</v>
       </c>
       <c r="R21" t="n">
-        <v>6991741</v>
+        <v>6991650</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,7 +2809,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124712512</v>
+        <v>124716113</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2825,16 +2845,16 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454093</v>
+        <v>454311</v>
       </c>
       <c r="R22" t="n">
         <v>6991632</v>
@@ -2901,7 +2921,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124716317</v>
+        <v>124712085</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2942,14 +2962,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454349</v>
+        <v>454054</v>
       </c>
       <c r="R23" t="n">
-        <v>6991623</v>
+        <v>6991662</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3013,10 +3033,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124713606</v>
+        <v>124713617</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>79851</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3025,25 +3045,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3115,10 +3135,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124715915</v>
+        <v>124714230</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3131,39 +3151,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454272</v>
+        <v>454102</v>
       </c>
       <c r="R25" t="n">
-        <v>6991637</v>
+        <v>6991834</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,11 +3211,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3227,10 +3237,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124715943</v>
+        <v>124714775</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3243,39 +3253,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454281</v>
+        <v>454161</v>
       </c>
       <c r="R26" t="n">
-        <v>6991629</v>
+        <v>6991910</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,11 +3313,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3451,10 +3451,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124711120</v>
+        <v>124716063</v>
       </c>
       <c r="B28" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3467,34 +3467,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454041</v>
+        <v>454289</v>
       </c>
       <c r="R28" t="n">
-        <v>6991635</v>
+        <v>6991647</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,6 +3532,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3553,10 +3563,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124712610</v>
+        <v>124713829</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3569,39 +3579,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454099</v>
+        <v>454078</v>
       </c>
       <c r="R29" t="n">
-        <v>6991631</v>
+        <v>6991761</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,11 +3639,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3665,10 +3665,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124753596</v>
+        <v>124756698</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3681,34 +3681,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454245</v>
+        <v>454144</v>
       </c>
       <c r="R30" t="n">
-        <v>6991630</v>
+        <v>6991886</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3738,14 +3738,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3760,22 +3765,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124756691</v>
+        <v>124753600</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3784,50 +3789,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454339</v>
+        <v>454147</v>
       </c>
       <c r="R31" t="n">
-        <v>6991639</v>
+        <v>6991908</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,24 +3850,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Min antal</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,29 +3866,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124753597</v>
+        <v>124753574</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3918,21 +3900,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3942,10 +3924,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454208</v>
+        <v>454086</v>
       </c>
       <c r="R32" t="n">
-        <v>6991866</v>
+        <v>6991732</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3978,11 +3960,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4009,10 +3986,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124753594</v>
+        <v>124753603</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4021,25 +3998,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4049,10 +4026,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454351</v>
+        <v>454234</v>
       </c>
       <c r="R33" t="n">
-        <v>6991627</v>
+        <v>6991643</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4085,11 +4062,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4116,10 +4088,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124756692</v>
+        <v>124753589</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>91700</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4128,38 +4100,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454256</v>
+        <v>454148</v>
       </c>
       <c r="R34" t="n">
-        <v>6991683</v>
+        <v>6991844</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4189,19 +4161,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>18:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4216,22 +4178,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124756702</v>
+        <v>124756697</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>74892</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4240,25 +4202,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4268,10 +4230,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454100</v>
+        <v>454177</v>
       </c>
       <c r="R35" t="n">
-        <v>6991668</v>
+        <v>6991911</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4303,7 +4265,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4313,7 +4275,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4324,6 +4286,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4340,10 +4317,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124756698</v>
+        <v>124753593</v>
       </c>
       <c r="B36" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4356,34 +4333,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454144</v>
+        <v>454406</v>
       </c>
       <c r="R36" t="n">
-        <v>6991886</v>
+        <v>6991545</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4413,19 +4390,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>17:48</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4440,22 +4412,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124753574</v>
+        <v>124756692</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4468,34 +4440,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454086</v>
+        <v>454256</v>
       </c>
       <c r="R37" t="n">
-        <v>6991732</v>
+        <v>6991683</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4525,9 +4497,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4542,22 +4524,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124753572</v>
+        <v>124753594</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4570,21 +4552,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4594,10 +4576,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454156</v>
+        <v>454351</v>
       </c>
       <c r="R38" t="n">
-        <v>6991902</v>
+        <v>6991627</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4630,6 +4612,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4656,10 +4643,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124753589</v>
+        <v>124756706</v>
       </c>
       <c r="B39" t="n">
-        <v>91700</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4668,38 +4655,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454148</v>
+        <v>454071</v>
       </c>
       <c r="R39" t="n">
-        <v>6991844</v>
+        <v>6991672</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4729,9 +4716,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4746,19 +4743,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124753598</v>
+        <v>124753596</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -4798,10 +4795,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454169</v>
+        <v>454245</v>
       </c>
       <c r="R40" t="n">
-        <v>6991914</v>
+        <v>6991630</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4838,7 +4835,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,7 +4862,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124753600</v>
+        <v>124753590</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -4899,16 +4896,24 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454147</v>
+        <v>454096</v>
       </c>
       <c r="R41" t="n">
-        <v>6991908</v>
+        <v>6991720</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4945,7 +4950,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål 5m upp i död gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4972,7 +4977,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124753593</v>
+        <v>124753597</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -5012,10 +5017,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454406</v>
+        <v>454208</v>
       </c>
       <c r="R42" t="n">
-        <v>6991545</v>
+        <v>6991866</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5079,10 +5084,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124753573</v>
+        <v>124756691</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5091,38 +5096,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454135</v>
+        <v>454339</v>
       </c>
       <c r="R43" t="n">
-        <v>6991889</v>
+        <v>6991639</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5152,39 +5169,55 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Min antal</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124753602</v>
+        <v>124756700</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5197,34 +5230,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454105</v>
+        <v>454086</v>
       </c>
       <c r="R44" t="n">
-        <v>6991740</v>
+        <v>6991750</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5254,14 +5287,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,22 +5314,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124753590</v>
+        <v>124753636</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5304,42 +5342,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454096</v>
+        <v>454089</v>
       </c>
       <c r="R45" t="n">
-        <v>6991720</v>
+        <v>6991655</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5372,11 +5402,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Bohål 5m upp i död gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5403,7 +5428,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124756701</v>
+        <v>124756709</v>
       </c>
       <c r="B46" t="n">
         <v>91012</v>
@@ -5443,10 +5468,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454115</v>
+        <v>454040</v>
       </c>
       <c r="R46" t="n">
-        <v>6991653</v>
+        <v>6991636</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5478,7 +5503,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5488,7 +5513,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5515,10 +5540,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124756709</v>
+        <v>124753598</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5531,34 +5556,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454040</v>
+        <v>454169</v>
       </c>
       <c r="R47" t="n">
-        <v>6991636</v>
+        <v>6991914</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5588,19 +5613,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:56</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5615,19 +5635,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124756693</v>
+        <v>124756702</v>
       </c>
       <c r="B48" t="n">
         <v>78810</v>
@@ -5667,10 +5687,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454196</v>
+        <v>454100</v>
       </c>
       <c r="R48" t="n">
-        <v>6991703</v>
+        <v>6991668</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5702,7 +5722,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5712,7 +5732,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5739,10 +5759,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124756700</v>
+        <v>124753573</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5755,34 +5775,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454086</v>
+        <v>454135</v>
       </c>
       <c r="R49" t="n">
-        <v>6991750</v>
+        <v>6991889</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5812,19 +5832,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5839,22 +5849,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124756703</v>
+        <v>124753601</v>
       </c>
       <c r="B50" t="n">
-        <v>77743</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5867,34 +5877,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454100</v>
+        <v>454103</v>
       </c>
       <c r="R50" t="n">
-        <v>6991668</v>
+        <v>6991735</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5924,19 +5934,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>17:06</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5951,22 +5956,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124756706</v>
+        <v>124753572</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5979,34 +5984,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454071</v>
+        <v>454156</v>
       </c>
       <c r="R51" t="n">
-        <v>6991672</v>
+        <v>6991902</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6036,19 +6041,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>17:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6063,22 +6058,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124753636</v>
+        <v>124753602</v>
       </c>
       <c r="B52" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6091,21 +6086,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6115,10 +6110,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454089</v>
+        <v>454105</v>
       </c>
       <c r="R52" t="n">
-        <v>6991655</v>
+        <v>6991740</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6151,6 +6146,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6177,10 +6177,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124756697</v>
+        <v>124756703</v>
       </c>
       <c r="B53" t="n">
-        <v>74892</v>
+        <v>77743</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6189,25 +6189,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>492</v>
+        <v>228579</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6217,10 +6217,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454177</v>
+        <v>454100</v>
       </c>
       <c r="R53" t="n">
-        <v>6991911</v>
+        <v>6991668</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6273,21 +6273,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6304,10 +6289,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124753603</v>
+        <v>124756701</v>
       </c>
       <c r="B54" t="n">
-        <v>91705</v>
+        <v>91012</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6316,38 +6301,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454234</v>
+        <v>454115</v>
       </c>
       <c r="R54" t="n">
-        <v>6991643</v>
+        <v>6991653</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6377,9 +6362,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6394,22 +6389,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124753601</v>
+        <v>124756693</v>
       </c>
       <c r="B55" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6422,34 +6417,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454103</v>
+        <v>454196</v>
       </c>
       <c r="R55" t="n">
-        <v>6991735</v>
+        <v>6991703</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6479,14 +6474,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6501,12 +6501,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124712709</v>
+        <v>124714299</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>82737</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454108</v>
+        <v>454102</v>
       </c>
       <c r="R2" t="n">
-        <v>6991616</v>
+        <v>6991834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124714580</v>
+        <v>124713188</v>
       </c>
       <c r="B3" t="n">
-        <v>74892</v>
+        <v>82737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>492</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454124</v>
+        <v>454120</v>
       </c>
       <c r="R3" t="n">
-        <v>6991906</v>
+        <v>6991707</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124716366</v>
+        <v>124712512</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454349</v>
+        <v>454093</v>
       </c>
       <c r="R4" t="n">
-        <v>6991623</v>
+        <v>6991632</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124715943</v>
+        <v>124712828</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454281</v>
+        <v>454150</v>
       </c>
       <c r="R5" t="n">
-        <v>6991629</v>
+        <v>6991620</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124713606</v>
+        <v>124714775</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454129</v>
+        <v>454161</v>
       </c>
       <c r="R6" t="n">
-        <v>6991741</v>
+        <v>6991910</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124714894</v>
+        <v>124716063</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454168</v>
+        <v>454289</v>
       </c>
       <c r="R7" t="n">
-        <v>6991883</v>
+        <v>6991647</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124712610</v>
+        <v>124713617</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>79988</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,43 +1329,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454099</v>
+        <v>454129</v>
       </c>
       <c r="R8" t="n">
-        <v>6991631</v>
+        <v>6991741</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124714299</v>
+        <v>124716317</v>
       </c>
       <c r="B9" t="n">
-        <v>82597</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,34 +1435,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454102</v>
+        <v>454349</v>
       </c>
       <c r="R9" t="n">
-        <v>6991834</v>
+        <v>6991623</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,6 +1500,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124714283</v>
+        <v>124714894</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,34 +1547,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454102</v>
+        <v>454168</v>
       </c>
       <c r="R10" t="n">
-        <v>6991834</v>
+        <v>6991883</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,6 +1612,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124713664</v>
+        <v>124713606</v>
       </c>
       <c r="B11" t="n">
-        <v>79892</v>
+        <v>80028</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1735,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124711120</v>
+        <v>124715903</v>
       </c>
       <c r="B12" t="n">
-        <v>78889</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,34 +1761,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454041</v>
+        <v>454272</v>
       </c>
       <c r="R12" t="n">
-        <v>6991635</v>
+        <v>6991637</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1826,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124715915</v>
+        <v>124713664</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>80029</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,39 +1873,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454272</v>
+        <v>454129</v>
       </c>
       <c r="R13" t="n">
-        <v>6991637</v>
+        <v>6991741</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,11 +1933,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124712512</v>
+        <v>124716073</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,43 +1971,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454093</v>
+        <v>454289</v>
       </c>
       <c r="R14" t="n">
-        <v>6991632</v>
+        <v>6991650</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,11 +2039,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,10 +2065,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124716162</v>
+        <v>124712709</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,39 +2081,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454310</v>
+        <v>454108</v>
       </c>
       <c r="R15" t="n">
-        <v>6991630</v>
+        <v>6991616</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,11 +2141,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rinfhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2176,7 +2170,7 @@
         <v>124712037</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>91184</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2275,10 +2269,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124715903</v>
+        <v>124715943</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,7 +2305,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2320,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454272</v>
+        <v>454281</v>
       </c>
       <c r="R17" t="n">
-        <v>6991636</v>
+        <v>6991629</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124713188</v>
+        <v>124715043</v>
       </c>
       <c r="B18" t="n">
-        <v>82597</v>
+        <v>91459</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,21 +2397,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2427,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454120</v>
+        <v>454203</v>
       </c>
       <c r="R18" t="n">
-        <v>6991707</v>
+        <v>6991872</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124715043</v>
+        <v>124716162</v>
       </c>
       <c r="B19" t="n">
-        <v>91299</v>
+        <v>57635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,34 +2499,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Kallseckelån, Kallseckelån, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454203</v>
+        <v>454310</v>
       </c>
       <c r="R19" t="n">
-        <v>6991872</v>
+        <v>6991630</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,6 +2564,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rinfhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124716057</v>
+        <v>124716113</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2636,10 +2640,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454290</v>
+        <v>454311</v>
       </c>
       <c r="R20" t="n">
-        <v>6991649</v>
+        <v>6991632</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,10 +2707,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124716073</v>
+        <v>124714580</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>75016</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2719,38 +2723,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>492</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454289</v>
+        <v>454124</v>
       </c>
       <c r="R21" t="n">
-        <v>6991650</v>
+        <v>6991906</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124716113</v>
+        <v>124716057</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454311</v>
+        <v>454290</v>
       </c>
       <c r="R22" t="n">
-        <v>6991632</v>
+        <v>6991649</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124712085</v>
+        <v>124712610</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454054</v>
+        <v>454099</v>
       </c>
       <c r="R23" t="n">
-        <v>6991662</v>
+        <v>6991631</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124713617</v>
+        <v>124712085</v>
       </c>
       <c r="B24" t="n">
-        <v>79851</v>
+        <v>57635</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3045,38 +3045,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454129</v>
+        <v>454054</v>
       </c>
       <c r="R24" t="n">
-        <v>6991741</v>
+        <v>6991662</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,6 +3114,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3138,7 +3148,7 @@
         <v>124714230</v>
       </c>
       <c r="B25" t="n">
-        <v>91299</v>
+        <v>91459</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3237,10 +3247,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124714775</v>
+        <v>124714283</v>
       </c>
       <c r="B26" t="n">
-        <v>79891</v>
+        <v>91166</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3253,21 +3263,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3277,10 +3287,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454161</v>
+        <v>454102</v>
       </c>
       <c r="R26" t="n">
-        <v>6991910</v>
+        <v>6991834</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3339,10 +3349,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124712828</v>
+        <v>124711120</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>79026</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3355,39 +3365,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454150</v>
+        <v>454041</v>
       </c>
       <c r="R27" t="n">
-        <v>6991620</v>
+        <v>6991635</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,11 +3425,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3451,10 +3451,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124716063</v>
+        <v>124713829</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3467,39 +3467,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kallseckelån, Kallseckelån, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454289</v>
+        <v>454078</v>
       </c>
       <c r="R28" t="n">
-        <v>6991647</v>
+        <v>6991761</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,11 +3527,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3563,10 +3553,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124713829</v>
+        <v>124753597</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3579,34 +3569,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454078</v>
+        <v>454208</v>
       </c>
       <c r="R29" t="n">
-        <v>6991761</v>
+        <v>6991866</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,12 +3623,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3653,22 +3648,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124756698</v>
+        <v>124753601</v>
       </c>
       <c r="B30" t="n">
-        <v>82597</v>
+        <v>57635</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3681,34 +3676,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454144</v>
+        <v>454103</v>
       </c>
       <c r="R30" t="n">
-        <v>6991886</v>
+        <v>6991735</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3738,19 +3733,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:48</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3765,12 +3755,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3780,7 +3770,7 @@
         <v>124753600</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3884,10 +3874,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124753574</v>
+        <v>124753590</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3900,34 +3890,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454086</v>
+        <v>454096</v>
       </c>
       <c r="R32" t="n">
-        <v>6991732</v>
+        <v>6991720</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3960,6 +3958,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Bohål 5m upp i död gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3986,10 +3989,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124753603</v>
+        <v>124753574</v>
       </c>
       <c r="B33" t="n">
-        <v>91705</v>
+        <v>91166</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3998,25 +4001,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4026,10 +4029,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454234</v>
+        <v>454086</v>
       </c>
       <c r="R33" t="n">
-        <v>6991643</v>
+        <v>6991732</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4088,10 +4091,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124753589</v>
+        <v>124756703</v>
       </c>
       <c r="B34" t="n">
-        <v>91700</v>
+        <v>77879</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4100,38 +4103,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454148</v>
+        <v>454100</v>
       </c>
       <c r="R34" t="n">
-        <v>6991844</v>
+        <v>6991668</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4161,9 +4164,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4178,22 +4191,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124756697</v>
+        <v>124756700</v>
       </c>
       <c r="B35" t="n">
-        <v>74892</v>
+        <v>78947</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4202,25 +4215,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4230,10 +4243,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454177</v>
+        <v>454086</v>
       </c>
       <c r="R35" t="n">
-        <v>6991911</v>
+        <v>6991750</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4265,7 +4278,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4275,7 +4288,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4286,21 +4299,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4317,10 +4315,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124753593</v>
+        <v>124756706</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4333,34 +4331,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454406</v>
+        <v>454071</v>
       </c>
       <c r="R36" t="n">
-        <v>6991545</v>
+        <v>6991672</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4390,14 +4388,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4412,22 +4415,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124756692</v>
+        <v>124753593</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4440,34 +4443,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454256</v>
+        <v>454406</v>
       </c>
       <c r="R37" t="n">
-        <v>6991683</v>
+        <v>6991545</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4497,19 +4500,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>18:19</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4524,22 +4522,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124753594</v>
+        <v>124753572</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4552,21 +4550,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4576,10 +4574,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454351</v>
+        <v>454156</v>
       </c>
       <c r="R38" t="n">
-        <v>6991627</v>
+        <v>6991902</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4612,11 +4610,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4643,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124756706</v>
+        <v>124753602</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4659,34 +4652,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454071</v>
+        <v>454105</v>
       </c>
       <c r="R39" t="n">
-        <v>6991672</v>
+        <v>6991740</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,19 +4709,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>17:00</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4743,22 +4731,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124753596</v>
+        <v>124753594</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4795,10 +4783,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454245</v>
+        <v>454351</v>
       </c>
       <c r="R40" t="n">
-        <v>6991630</v>
+        <v>6991627</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4835,7 +4823,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4862,10 +4850,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124753590</v>
+        <v>124756691</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4874,46 +4862,50 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454096</v>
+        <v>454339</v>
       </c>
       <c r="R41" t="n">
-        <v>6991720</v>
+        <v>6991639</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4943,14 +4935,24 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Bohål 5m upp i död gran</t>
+          <t>Min antal</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4959,28 +4961,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124753597</v>
+        <v>124753603</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>91865</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4989,25 +4992,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5017,10 +5020,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454208</v>
+        <v>454234</v>
       </c>
       <c r="R42" t="n">
-        <v>6991866</v>
+        <v>6991643</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5053,11 +5056,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5084,10 +5082,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124756691</v>
+        <v>124756692</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5096,50 +5094,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454339</v>
+        <v>454256</v>
       </c>
       <c r="R43" t="n">
-        <v>6991639</v>
+        <v>6991683</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5171,7 +5157,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5181,12 +5167,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Min antal</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5195,7 +5176,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5214,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124756700</v>
+        <v>124756709</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5230,21 +5210,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5254,10 +5234,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454086</v>
+        <v>454040</v>
       </c>
       <c r="R44" t="n">
-        <v>6991750</v>
+        <v>6991636</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5289,7 +5269,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5299,7 +5279,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5326,10 +5306,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124753636</v>
+        <v>124753573</v>
       </c>
       <c r="B45" t="n">
-        <v>91030</v>
+        <v>91166</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5342,21 +5322,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5366,10 +5346,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454089</v>
+        <v>454135</v>
       </c>
       <c r="R45" t="n">
-        <v>6991655</v>
+        <v>6991889</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5428,10 +5408,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124756709</v>
+        <v>124753589</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>91860</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5440,38 +5420,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454040</v>
+        <v>454148</v>
       </c>
       <c r="R46" t="n">
-        <v>6991636</v>
+        <v>6991844</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5501,19 +5481,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:56</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5528,22 +5498,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124753598</v>
+        <v>124756693</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5556,34 +5526,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454169</v>
+        <v>454196</v>
       </c>
       <c r="R47" t="n">
-        <v>6991914</v>
+        <v>6991703</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5613,14 +5583,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5635,22 +5610,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124756702</v>
+        <v>124753598</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5663,34 +5638,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454100</v>
+        <v>454169</v>
       </c>
       <c r="R48" t="n">
-        <v>6991668</v>
+        <v>6991914</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5720,19 +5695,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>17:07</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>17:07</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5747,22 +5717,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124753573</v>
+        <v>124753596</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5775,21 +5745,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5799,10 +5769,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454135</v>
+        <v>454245</v>
       </c>
       <c r="R49" t="n">
-        <v>6991889</v>
+        <v>6991630</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5835,6 +5805,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5861,10 +5836,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124753601</v>
+        <v>124756697</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>75016</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5873,38 +5848,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454103</v>
+        <v>454177</v>
       </c>
       <c r="R50" t="n">
-        <v>6991735</v>
+        <v>6991911</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5934,14 +5909,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5952,26 +5932,41 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124753572</v>
+        <v>124756701</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6004,14 +5999,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454156</v>
+        <v>454115</v>
       </c>
       <c r="R51" t="n">
-        <v>6991902</v>
+        <v>6991653</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6041,9 +6036,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6058,22 +6063,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124753602</v>
+        <v>124756698</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>82737</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6086,34 +6091,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454105</v>
+        <v>454144</v>
       </c>
       <c r="R52" t="n">
-        <v>6991740</v>
+        <v>6991886</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6143,14 +6148,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6165,22 +6175,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124756703</v>
+        <v>124753636</v>
       </c>
       <c r="B53" t="n">
-        <v>77743</v>
+        <v>91184</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6193,34 +6203,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454100</v>
+        <v>454089</v>
       </c>
       <c r="R53" t="n">
-        <v>6991668</v>
+        <v>6991655</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6250,19 +6260,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>17:06</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6277,22 +6277,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124756701</v>
+        <v>124756702</v>
       </c>
       <c r="B54" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6305,21 +6305,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454115</v>
+        <v>454100</v>
       </c>
       <c r="R54" t="n">
-        <v>6991653</v>
+        <v>6991668</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6398,118 +6398,6 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>124756693</v>
-      </c>
-      <c r="B55" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Tjärnflon Ö, Jmt</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>454196</v>
-      </c>
-      <c r="R55" t="n">
-        <v>6991703</v>
-      </c>
-      <c r="S55" t="n">
-        <v>10</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Oviken</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -6075,10 +6075,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124756698</v>
+        <v>124753636</v>
       </c>
       <c r="B52" t="n">
-        <v>82737</v>
+        <v>91184</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6091,34 +6091,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454144</v>
+        <v>454089</v>
       </c>
       <c r="R52" t="n">
-        <v>6991886</v>
+        <v>6991655</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6148,19 +6148,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6175,22 +6165,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124753636</v>
+        <v>124756702</v>
       </c>
       <c r="B53" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6203,34 +6193,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454089</v>
+        <v>454100</v>
       </c>
       <c r="R53" t="n">
-        <v>6991655</v>
+        <v>6991668</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6260,9 +6250,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6277,22 +6277,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124756702</v>
+        <v>124756698</v>
       </c>
       <c r="B54" t="n">
-        <v>78947</v>
+        <v>82737</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6305,21 +6305,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454100</v>
+        <v>454144</v>
       </c>
       <c r="R54" t="n">
-        <v>6991668</v>
+        <v>6991886</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -3553,7 +3553,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124753597</v>
+        <v>124753601</v>
       </c>
       <c r="B29" t="n">
         <v>57635</v>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454208</v>
+        <v>454103</v>
       </c>
       <c r="R29" t="n">
-        <v>6991866</v>
+        <v>6991735</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124753601</v>
+        <v>124753573</v>
       </c>
       <c r="B30" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3676,21 +3676,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454103</v>
+        <v>454135</v>
       </c>
       <c r="R30" t="n">
-        <v>6991735</v>
+        <v>6991889</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,11 +3736,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3767,10 +3762,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124753600</v>
+        <v>124756698</v>
       </c>
       <c r="B31" t="n">
-        <v>57635</v>
+        <v>82737</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3783,34 +3778,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454147</v>
+        <v>454144</v>
       </c>
       <c r="R31" t="n">
-        <v>6991908</v>
+        <v>6991886</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3840,14 +3835,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3862,19 +3862,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124753590</v>
+        <v>124753598</v>
       </c>
       <c r="B32" t="n">
         <v>57635</v>
@@ -3908,24 +3908,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454096</v>
+        <v>454169</v>
       </c>
       <c r="R32" t="n">
-        <v>6991720</v>
+        <v>6991914</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3962,7 +3954,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Bohål 5m upp i död gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3989,10 +3981,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124753574</v>
+        <v>124756706</v>
       </c>
       <c r="B33" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4005,34 +3997,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454086</v>
+        <v>454071</v>
       </c>
       <c r="R33" t="n">
-        <v>6991732</v>
+        <v>6991672</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,9 +4054,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4079,22 +4081,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124756703</v>
+        <v>124756702</v>
       </c>
       <c r="B34" t="n">
-        <v>77879</v>
+        <v>78947</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4107,21 +4109,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4166,7 +4168,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4176,7 +4178,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4203,10 +4205,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124756700</v>
+        <v>124753572</v>
       </c>
       <c r="B35" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4219,34 +4221,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454086</v>
+        <v>454156</v>
       </c>
       <c r="R35" t="n">
-        <v>6991750</v>
+        <v>6991902</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4276,19 +4278,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,19 +4295,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124756706</v>
+        <v>124756700</v>
       </c>
       <c r="B36" t="n">
         <v>78947</v>
@@ -4355,10 +4347,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454071</v>
+        <v>454086</v>
       </c>
       <c r="R36" t="n">
-        <v>6991672</v>
+        <v>6991750</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4390,7 +4382,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4400,7 +4392,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4427,10 +4419,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124753593</v>
+        <v>124753636</v>
       </c>
       <c r="B37" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4443,21 +4435,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4467,10 +4459,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454406</v>
+        <v>454089</v>
       </c>
       <c r="R37" t="n">
-        <v>6991545</v>
+        <v>6991655</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4503,11 +4495,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4534,10 +4521,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124753572</v>
+        <v>124753602</v>
       </c>
       <c r="B38" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4550,21 +4537,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4574,10 +4561,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454156</v>
+        <v>454105</v>
       </c>
       <c r="R38" t="n">
-        <v>6991902</v>
+        <v>6991740</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4610,6 +4597,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,10 +4628,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124753602</v>
+        <v>124756703</v>
       </c>
       <c r="B39" t="n">
-        <v>57635</v>
+        <v>77879</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4652,34 +4644,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454105</v>
+        <v>454100</v>
       </c>
       <c r="R39" t="n">
-        <v>6991740</v>
+        <v>6991668</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,14 +4701,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4731,19 +4728,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124753594</v>
+        <v>124753596</v>
       </c>
       <c r="B40" t="n">
         <v>57635</v>
@@ -4783,10 +4780,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454351</v>
+        <v>454245</v>
       </c>
       <c r="R40" t="n">
-        <v>6991627</v>
+        <v>6991630</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4823,7 +4820,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4850,10 +4847,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124756691</v>
+        <v>124753590</v>
       </c>
       <c r="B41" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4862,50 +4859,46 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454339</v>
+        <v>454096</v>
       </c>
       <c r="R41" t="n">
-        <v>6991639</v>
+        <v>6991720</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4935,24 +4928,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Min antal</t>
+          <t>Bohål 5m upp i död gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4961,29 +4944,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124753603</v>
+        <v>124753574</v>
       </c>
       <c r="B42" t="n">
-        <v>91865</v>
+        <v>91166</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4992,25 +4974,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5020,10 +5002,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454234</v>
+        <v>454086</v>
       </c>
       <c r="R42" t="n">
-        <v>6991643</v>
+        <v>6991732</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5082,10 +5064,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124756692</v>
+        <v>124753597</v>
       </c>
       <c r="B43" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5098,34 +5080,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454256</v>
+        <v>454208</v>
       </c>
       <c r="R43" t="n">
-        <v>6991683</v>
+        <v>6991866</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5155,19 +5137,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>18:19</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5182,22 +5159,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124756709</v>
+        <v>124756697</v>
       </c>
       <c r="B44" t="n">
-        <v>91166</v>
+        <v>75016</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5206,25 +5183,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5234,10 +5211,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454040</v>
+        <v>454177</v>
       </c>
       <c r="R44" t="n">
-        <v>6991636</v>
+        <v>6991911</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5269,7 +5246,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5279,7 +5256,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5290,6 +5267,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5306,10 +5298,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124753573</v>
+        <v>124753594</v>
       </c>
       <c r="B45" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5322,21 +5314,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5346,10 +5338,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454135</v>
+        <v>454351</v>
       </c>
       <c r="R45" t="n">
-        <v>6991889</v>
+        <v>6991627</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5382,6 +5374,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5408,10 +5405,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124753589</v>
+        <v>124756701</v>
       </c>
       <c r="B46" t="n">
-        <v>91860</v>
+        <v>91166</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5420,38 +5417,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454148</v>
+        <v>454115</v>
       </c>
       <c r="R46" t="n">
-        <v>6991844</v>
+        <v>6991653</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5481,9 +5478,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5498,22 +5505,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124756693</v>
+        <v>124756691</v>
       </c>
       <c r="B47" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5522,38 +5529,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454196</v>
+        <v>454339</v>
       </c>
       <c r="R47" t="n">
-        <v>6991703</v>
+        <v>6991639</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5585,7 +5604,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5595,7 +5614,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Min antal</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5604,6 +5628,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5622,7 +5647,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124753598</v>
+        <v>124753593</v>
       </c>
       <c r="B48" t="n">
         <v>57635</v>
@@ -5662,10 +5687,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454169</v>
+        <v>454406</v>
       </c>
       <c r="R48" t="n">
-        <v>6991914</v>
+        <v>6991545</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5702,7 +5727,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5729,7 +5754,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124753596</v>
+        <v>124753600</v>
       </c>
       <c r="B49" t="n">
         <v>57635</v>
@@ -5769,10 +5794,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454245</v>
+        <v>454147</v>
       </c>
       <c r="R49" t="n">
-        <v>6991630</v>
+        <v>6991908</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5809,7 +5834,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5836,10 +5861,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124756697</v>
+        <v>124753603</v>
       </c>
       <c r="B50" t="n">
-        <v>75016</v>
+        <v>91865</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5852,34 +5877,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>492</v>
+        <v>67</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454177</v>
+        <v>454234</v>
       </c>
       <c r="R50" t="n">
-        <v>6991911</v>
+        <v>6991643</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5909,21 +5934,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>17:55</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5932,41 +5947,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124756701</v>
+        <v>124753589</v>
       </c>
       <c r="B51" t="n">
-        <v>91166</v>
+        <v>91860</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5975,38 +5975,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454115</v>
+        <v>454148</v>
       </c>
       <c r="R51" t="n">
-        <v>6991653</v>
+        <v>6991844</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6036,19 +6036,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>17:09</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>17:09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6063,22 +6053,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124753636</v>
+        <v>124756693</v>
       </c>
       <c r="B52" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6091,34 +6081,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454089</v>
+        <v>454196</v>
       </c>
       <c r="R52" t="n">
-        <v>6991655</v>
+        <v>6991703</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6148,9 +6138,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6165,19 +6165,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124756702</v>
+        <v>124756692</v>
       </c>
       <c r="B53" t="n">
         <v>78947</v>
@@ -6217,10 +6217,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>454100</v>
+        <v>454256</v>
       </c>
       <c r="R53" t="n">
-        <v>6991668</v>
+        <v>6991683</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6289,10 +6289,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124756698</v>
+        <v>124756709</v>
       </c>
       <c r="B54" t="n">
-        <v>82737</v>
+        <v>91166</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6305,21 +6305,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>454144</v>
+        <v>454040</v>
       </c>
       <c r="R54" t="n">
-        <v>6991886</v>
+        <v>6991636</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -1763,7 +1763,7 @@
         <v>454272</v>
       </c>
       <c r="R12" t="n">
-        <v>6991636</v>
+        <v>6991637</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>124712512</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>124712828</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>124716063</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>124716317</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>124714894</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>124715903</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>124715943</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>124716162</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>124716113</v>
       </c>
       <c r="B20" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>124716057</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>124712610</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>124712085</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>124753601</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>124753598</v>
       </c>
       <c r="B32" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>124753602</v>
       </c>
       <c r="B38" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>124753596</v>
       </c>
       <c r="B40" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>124753590</v>
       </c>
       <c r="B41" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>124753597</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>124753594</v>
       </c>
       <c r="B45" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>124753593</v>
       </c>
       <c r="B48" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>124753600</v>
       </c>
       <c r="B49" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -1763,7 +1763,7 @@
         <v>454272</v>
       </c>
       <c r="R12" t="n">
-        <v>6991637</v>
+        <v>6991636</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>124712512</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>124712828</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>124716063</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>124716317</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>124714894</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>124715903</v>
       </c>
       <c r="B12" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>124715943</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>124716162</v>
       </c>
       <c r="B19" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>124716113</v>
       </c>
       <c r="B20" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>124716057</v>
       </c>
       <c r="B22" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>124712610</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>124712085</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>124753601</v>
       </c>
       <c r="B29" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>124753598</v>
       </c>
       <c r="B32" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>124753602</v>
       </c>
       <c r="B38" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>124753596</v>
       </c>
       <c r="B40" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>124753590</v>
       </c>
       <c r="B41" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>124753597</v>
       </c>
       <c r="B43" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>124753594</v>
       </c>
       <c r="B45" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>124753593</v>
       </c>
       <c r="B48" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>124753600</v>
       </c>
       <c r="B49" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>124712512</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>124712828</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>124716063</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>124716317</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>124714894</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>124715903</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>124715943</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>124716162</v>
       </c>
       <c r="B19" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>124716113</v>
       </c>
       <c r="B20" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>124716057</v>
       </c>
       <c r="B22" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>124712610</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>124712085</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>124753601</v>
       </c>
       <c r="B29" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>124753598</v>
       </c>
       <c r="B32" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>124753602</v>
       </c>
       <c r="B38" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>124753596</v>
       </c>
       <c r="B40" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>124753590</v>
       </c>
       <c r="B41" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>124753597</v>
       </c>
       <c r="B43" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>124753594</v>
       </c>
       <c r="B45" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>124753593</v>
       </c>
       <c r="B48" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>124753600</v>
       </c>
       <c r="B49" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 12970-2024 artfynd.xlsx
+++ b/artfynd/A 12970-2024 artfynd.xlsx
@@ -4770,7 +4770,7 @@
         <v>124753590</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>57864</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
